--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -6748,22 +6748,22 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>1778659312652_99</v>
+        <v>1778659312652_108</v>
       </c>
       <c r="B266" t="str">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C266" t="str">
-        <v>236</v>
+        <v>588</v>
       </c>
       <c r="D266" t="str">
-        <v>Batul bai Johar bhai Saroda</v>
+        <v>Bilqis bai Husain bhai Gadi</v>
       </c>
       <c r="E266" t="str">
-        <v>30488741</v>
+        <v>20318760</v>
       </c>
       <c r="F266" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G266" t="str">
         <v/>
@@ -6771,19 +6771,19 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>1778659312652_108</v>
+        <v>1778659312652_326</v>
       </c>
       <c r="B267" t="str">
-        <v>109</v>
+        <v>327</v>
       </c>
       <c r="C267" t="str">
-        <v>588</v>
+        <v>431</v>
       </c>
       <c r="D267" t="str">
-        <v>Bilqis bai Husain bhai Gadi</v>
+        <v>Khadija bai Fakhruddin bhai Peeth</v>
       </c>
       <c r="E267" t="str">
-        <v>20318760</v>
+        <v>30366840</v>
       </c>
       <c r="F267" t="str">
         <v>Pending</v>
@@ -6794,25 +6794,34 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>1778659312652_326</v>
+        <v>1778659312652_99</v>
       </c>
       <c r="B268" t="str">
-        <v>327</v>
+        <v>100</v>
       </c>
       <c r="C268" t="str">
-        <v>431</v>
+        <v>236</v>
       </c>
       <c r="D268" t="str">
-        <v>Khadija bai Fakhruddin bhai Peeth</v>
+        <v>Batul bai Johar bhai Saroda</v>
       </c>
       <c r="E268" t="str">
-        <v>30366840</v>
+        <v>30488741</v>
       </c>
       <c r="F268" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G268" t="str">
-        <v/>
+        <v>Ilyas</v>
+      </c>
+      <c r="H268" t="str">
+        <v>19/05/2026</v>
+      </c>
+      <c r="I268" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="J268" t="str">
+        <v>17:29:45</v>
       </c>
     </row>
     <row r="269">

--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -6748,42 +6748,51 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>1778659312652_108</v>
+        <v>1778659312652_99</v>
       </c>
       <c r="B266" t="str">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C266" t="str">
-        <v>588</v>
+        <v>236</v>
       </c>
       <c r="D266" t="str">
-        <v>Bilqis bai Husain bhai Gadi</v>
+        <v>Batul bai Johar bhai Saroda</v>
       </c>
       <c r="E266" t="str">
-        <v>20318760</v>
+        <v>30488741</v>
       </c>
       <c r="F266" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G266" t="str">
-        <v/>
+        <v>Ilya</v>
+      </c>
+      <c r="H266" t="str">
+        <v>19/05/2026</v>
+      </c>
+      <c r="I266" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="J266" t="str">
+        <v>18:22:57</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>1778659312652_326</v>
+        <v>1778659312652_108</v>
       </c>
       <c r="B267" t="str">
-        <v>327</v>
+        <v>109</v>
       </c>
       <c r="C267" t="str">
-        <v>431</v>
+        <v>588</v>
       </c>
       <c r="D267" t="str">
-        <v>Khadija bai Fakhruddin bhai Peeth</v>
+        <v>Bilqis bai Husain bhai Gadi</v>
       </c>
       <c r="E267" t="str">
-        <v>30366840</v>
+        <v>20318760</v>
       </c>
       <c r="F267" t="str">
         <v>Pending</v>
@@ -6794,34 +6803,25 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>1778659312652_99</v>
+        <v>1778659312652_326</v>
       </c>
       <c r="B268" t="str">
-        <v>100</v>
+        <v>327</v>
       </c>
       <c r="C268" t="str">
-        <v>236</v>
+        <v>431</v>
       </c>
       <c r="D268" t="str">
-        <v>Batul bai Johar bhai Saroda</v>
+        <v>Khadija bai Fakhruddin bhai Peeth</v>
       </c>
       <c r="E268" t="str">
-        <v>30488741</v>
+        <v>30366840</v>
       </c>
       <c r="F268" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G268" t="str">
-        <v>Ilyas</v>
-      </c>
-      <c r="H268" t="str">
-        <v>19/05/2026</v>
-      </c>
-      <c r="I268" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="J268" t="str">
-        <v>17:29:45</v>
+        <v/>
       </c>
     </row>
     <row r="269">

--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -1219,19 +1219,10 @@
         <v>20387894</v>
       </c>
       <c r="F32" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G32" t="str">
-        <v>Ilyas</v>
-      </c>
-      <c r="H32" t="str">
-        <v>24/05/2026</v>
-      </c>
-      <c r="I32" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="J32" t="str">
-        <v>20:53:42</v>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1259,88 +1250,97 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>1778659312652_145</v>
+        <v>1778659312652_154</v>
       </c>
       <c r="B34" t="str">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C34" t="str">
-        <v>1234</v>
+        <v>1339</v>
       </c>
       <c r="D34" t="str">
-        <v>Fakhruddin bhai Talib bhai Najafi</v>
+        <v>Farida bai Mohammedhusain bhai Kothari</v>
       </c>
       <c r="E34" t="str">
-        <v>30368536</v>
+        <v>30367383</v>
       </c>
       <c r="F34" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>Ilyas</v>
+      </c>
+      <c r="H34" t="str">
+        <v>24/05/2026</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Sunday</v>
+      </c>
+      <c r="J34" t="str">
+        <v>22:35:04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>1778659312652_146</v>
+        <v>1778659312652_145</v>
       </c>
       <c r="B35" t="str">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C35" t="str">
-        <v>855</v>
+        <v>1234</v>
       </c>
       <c r="D35" t="str">
-        <v>Fakhruddin bhai Yusuf bhai Kabja</v>
+        <v>Fakhruddin bhai Talib bhai Najafi</v>
       </c>
       <c r="E35" t="str">
-        <v>30367601</v>
+        <v>30368536</v>
       </c>
       <c r="F35" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G35" t="str">
-        <v>Fakhruddin kawja</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>1778659312652_14</v>
+        <v>1778659312652_146</v>
       </c>
       <c r="B36" t="str">
-        <v>15</v>
+        <v>147</v>
       </c>
       <c r="C36" t="str">
-        <v>1452</v>
+        <v>855</v>
       </c>
       <c r="D36" t="str">
-        <v>Abdeali bhai Husain bhai Kika</v>
+        <v>Fakhruddin bhai Yusuf bhai Kabja</v>
       </c>
       <c r="E36" t="str">
-        <v>30367463</v>
+        <v>30367601</v>
       </c>
       <c r="F36" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G36" t="str">
-        <v/>
+        <v>Fakhruddin kawja</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>1778659312652_149</v>
+        <v>1778659312652_14</v>
       </c>
       <c r="B37" t="str">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="C37" t="str">
-        <v>315</v>
+        <v>1452</v>
       </c>
       <c r="D37" t="str">
-        <v>Farida bai Fakhruddin bhai Rustam</v>
+        <v>Abdeali bhai Husain bhai Kika</v>
       </c>
       <c r="E37" t="str">
-        <v>20318201</v>
+        <v>30367463</v>
       </c>
       <c r="F37" t="str">
         <v>Pending</v>
@@ -1351,74 +1351,74 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>1778659312652_150</v>
+        <v>1778659312652_149</v>
       </c>
       <c r="B38" t="str">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C38" t="str">
-        <v>491</v>
+        <v>315</v>
       </c>
       <c r="D38" t="str">
-        <v>Farida bai Husain bhai Galalji</v>
+        <v>Farida bai Fakhruddin bhai Rustam</v>
       </c>
       <c r="E38" t="str">
-        <v>30366897</v>
+        <v>20318201</v>
       </c>
       <c r="F38" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G38" t="str">
-        <v>Zainab ben shabbir bhai Dhambola</v>
-      </c>
-      <c r="H38" t="str">
-        <v>22/05/2026</v>
-      </c>
-      <c r="I38" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J38" t="str">
-        <v>11:31:37</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>1778659312652_151</v>
+        <v>1778659312652_150</v>
       </c>
       <c r="B39" t="str">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C39" t="str">
-        <v>1122</v>
+        <v>491</v>
       </c>
       <c r="D39" t="str">
-        <v>Farida bai Juzer bhai Gyori</v>
+        <v>Farida bai Husain bhai Galalji</v>
       </c>
       <c r="E39" t="str">
-        <v>30367320</v>
+        <v>30366897</v>
       </c>
       <c r="F39" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G39" t="str">
-        <v/>
+        <v>Zainab ben shabbir bhai Dhambola</v>
+      </c>
+      <c r="H39" t="str">
+        <v>22/05/2026</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="J39" t="str">
+        <v>11:31:37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>1778659312652_152</v>
+        <v>1778659312652_151</v>
       </c>
       <c r="B40" t="str">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C40" t="str">
-        <v>970</v>
+        <v>1122</v>
       </c>
       <c r="D40" t="str">
-        <v>Farida bai Khuzaima bhai Obri</v>
+        <v>Farida bai Juzer bhai Gyori</v>
       </c>
       <c r="E40" t="str">
-        <v>30367525</v>
+        <v>30367320</v>
       </c>
       <c r="F40" t="str">
         <v>Pending</v>
@@ -1429,19 +1429,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>1778659312652_153</v>
+        <v>1778659312652_152</v>
       </c>
       <c r="B41" t="str">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C41" t="str">
-        <v>1336</v>
+        <v>970</v>
       </c>
       <c r="D41" t="str">
-        <v>Farida bai Mohammed bhai Maudiwala</v>
+        <v>Farida bai Khuzaima bhai Obri</v>
       </c>
       <c r="E41" t="str">
-        <v>30367788</v>
+        <v>30367525</v>
       </c>
       <c r="F41" t="str">
         <v>Pending</v>
@@ -1452,66 +1452,57 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>1778659312652_391</v>
+        <v>1778659312652_153</v>
       </c>
       <c r="B42" t="str">
-        <v>392</v>
+        <v>154</v>
       </c>
       <c r="C42" t="str">
-        <v>1055</v>
+        <v>1336</v>
       </c>
       <c r="D42" t="str">
-        <v>Mulla Husain bhai Jivaji bhai Pachlasa</v>
+        <v>Farida bai Mohammed bhai Maudiwala</v>
       </c>
       <c r="E42" t="str">
-        <v>20318738</v>
+        <v>30367788</v>
       </c>
       <c r="F42" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G42" t="str">
         <v/>
-      </c>
-      <c r="H42" t="str">
-        <v>22/05/2026</v>
-      </c>
-      <c r="I42" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J42" t="str">
-        <v>11:46:17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>1778659312652_154</v>
+        <v>1778659312652_391</v>
       </c>
       <c r="B43" t="str">
-        <v>155</v>
+        <v>392</v>
       </c>
       <c r="C43" t="str">
-        <v>1339</v>
+        <v>1055</v>
       </c>
       <c r="D43" t="str">
-        <v>Farida bai Mohammedhusain bhai Kothari</v>
+        <v>Mulla Husain bhai Jivaji bhai Pachlasa</v>
       </c>
       <c r="E43" t="str">
-        <v>30367383</v>
+        <v>20318738</v>
       </c>
       <c r="F43" t="str">
         <v>Given</v>
       </c>
       <c r="G43" t="str">
-        <v>Ilyas</v>
+        <v/>
       </c>
       <c r="H43" t="str">
-        <v>16/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="I43" t="str">
-        <v>Saturday</v>
+        <v>Friday</v>
       </c>
       <c r="J43" t="str">
-        <v>11:45:49</v>
+        <v>11:46:17</v>
       </c>
     </row>
     <row r="44">
@@ -5055,106 +5046,97 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>1778659312652_575</v>
+        <v>1778659312652_219</v>
       </c>
       <c r="B183" t="str">
-        <v>576</v>
+        <v>220</v>
       </c>
       <c r="C183" t="str">
-        <v>238</v>
+        <v>813</v>
       </c>
       <c r="D183" t="str">
-        <v>Samina bai Husain bhai Hathai</v>
+        <v>Fatema bai Saifuddin bhai Khand</v>
       </c>
       <c r="E183" t="str">
-        <v>20318771</v>
+        <v>20318516</v>
       </c>
       <c r="F183" t="str">
         <v>Given</v>
       </c>
       <c r="G183" t="str">
-        <v>Ilyas</v>
-      </c>
-      <c r="H183" t="str">
-        <v>24/05/2026</v>
-      </c>
-      <c r="I183" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="J183" t="str">
-        <v>20:53:42</v>
+        <v>Fakhruddin kawja</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>1778659312652_219</v>
+        <v>1778659312652_220</v>
       </c>
       <c r="B184" t="str">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C184" t="str">
-        <v>813</v>
+        <v>415</v>
       </c>
       <c r="D184" t="str">
-        <v>Fatema bai Saifuddin bhai Khand</v>
+        <v>Fatema bai Saifuddin bhai Morawala</v>
       </c>
       <c r="E184" t="str">
-        <v>20318516</v>
+        <v>30366819</v>
       </c>
       <c r="F184" t="str">
         <v>Given</v>
       </c>
       <c r="G184" t="str">
-        <v>Fakhruddin kawja</v>
+        <v>shkh fakhruddin badi</v>
+      </c>
+      <c r="H184" t="str">
+        <v>19/05/2026</v>
+      </c>
+      <c r="I184" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="J184" t="str">
+        <v>11:29:18</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>1778659312652_220</v>
+        <v>1778659312652_241</v>
       </c>
       <c r="B185" t="str">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C185" t="str">
-        <v>415</v>
+        <v>874</v>
       </c>
       <c r="D185" t="str">
-        <v>Fatema bai Saifuddin bhai Morawala</v>
+        <v>Ghulamabbas bhai Mulla Fidahusain bhai Baroda</v>
       </c>
       <c r="E185" t="str">
-        <v>30366819</v>
+        <v>20318553</v>
       </c>
       <c r="F185" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G185" t="str">
-        <v>shkh fakhruddin badi</v>
-      </c>
-      <c r="H185" t="str">
-        <v>19/05/2026</v>
-      </c>
-      <c r="I185" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="J185" t="str">
-        <v>11:29:18</v>
+        <v/>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>1778659312652_241</v>
+        <v>1778659312652_413</v>
       </c>
       <c r="B186" t="str">
-        <v>242</v>
+        <v>414</v>
       </c>
       <c r="C186" t="str">
-        <v>874</v>
+        <v/>
       </c>
       <c r="D186" t="str">
-        <v>Ghulamabbas bhai Mulla Fidahusain bhai Baroda</v>
+        <v>Mustafa bhai Hakimuddin bhai Lodal</v>
       </c>
       <c r="E186" t="str">
-        <v>20318553</v>
+        <v>30493059</v>
       </c>
       <c r="F186" t="str">
         <v>Pending</v>
@@ -5165,19 +5147,19 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>1778659312652_413</v>
+        <v>1778659312652_414</v>
       </c>
       <c r="B187" t="str">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C187" t="str">
         <v/>
       </c>
       <c r="D187" t="str">
-        <v>Mustafa bhai Hakimuddin bhai Lodal</v>
+        <v>Mustafa bhai Taher bhai Bapu</v>
       </c>
       <c r="E187" t="str">
-        <v>30493059</v>
+        <v>20318039</v>
       </c>
       <c r="F187" t="str">
         <v>Pending</v>
@@ -5188,19 +5170,19 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>1778659312652_414</v>
+        <v>1778659312652_415</v>
       </c>
       <c r="B188" t="str">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C188" t="str">
-        <v/>
+        <v>52</v>
       </c>
       <c r="D188" t="str">
-        <v>Mustafa bhai Taher bhai Bapu</v>
+        <v>Mustansir bhai Abbas bhai Ramakda</v>
       </c>
       <c r="E188" t="str">
-        <v>20318039</v>
+        <v>30805007</v>
       </c>
       <c r="F188" t="str">
         <v>Pending</v>
@@ -5211,175 +5193,175 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>1778659312652_415</v>
+        <v>1778659312652_446</v>
       </c>
       <c r="B189" t="str">
-        <v>416</v>
+        <v>447</v>
       </c>
       <c r="C189" t="str">
-        <v>52</v>
+        <v>442</v>
       </c>
       <c r="D189" t="str">
-        <v>Mustansir bhai Abbas bhai Ramakda</v>
+        <v>Qaidjoher bhai Shabbirhusain bhai Ramgarh</v>
       </c>
       <c r="E189" t="str">
-        <v>30805007</v>
+        <v>20342316</v>
       </c>
       <c r="F189" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G189" t="str">
-        <v/>
+        <v>Nasa bhai</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>1778659312652_446</v>
+        <v>1778659312652_447</v>
       </c>
       <c r="B190" t="str">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C190" t="str">
-        <v>442</v>
+        <v>1360</v>
       </c>
       <c r="D190" t="str">
-        <v>Qaidjoher bhai Shabbirhusain bhai Ramgarh</v>
+        <v>Qaidjoher bhai Shaikh Abbas bhai Kothra</v>
       </c>
       <c r="E190" t="str">
-        <v>20342316</v>
+        <v>20406019</v>
       </c>
       <c r="F190" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G190" t="str">
-        <v>Nasa bhai</v>
+        <v/>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>1778659312652_447</v>
+        <v>1778659312652_21</v>
       </c>
       <c r="B191" t="str">
-        <v>448</v>
+        <v>22</v>
       </c>
       <c r="C191" t="str">
-        <v>1360</v>
+        <v>789</v>
       </c>
       <c r="D191" t="str">
-        <v>Qaidjoher bhai Shaikh Abbas bhai Kothra</v>
+        <v>Ajab bai Fakhruddin bhai Wardawala</v>
       </c>
       <c r="E191" t="str">
-        <v>20406019</v>
+        <v>30367453</v>
       </c>
       <c r="F191" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G191" t="str">
         <v/>
+      </c>
+      <c r="H191" t="str">
+        <v>20/05/2026</v>
+      </c>
+      <c r="I191" t="str">
+        <v>Wednesday</v>
+      </c>
+      <c r="J191" t="str">
+        <v>12:24:47</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>1778659312652_21</v>
+        <v>1778659312652_448</v>
       </c>
       <c r="B192" t="str">
-        <v>22</v>
+        <v>449</v>
       </c>
       <c r="C192" t="str">
-        <v>789</v>
+        <v>393</v>
       </c>
       <c r="D192" t="str">
-        <v>Ajab bai Fakhruddin bhai Wardawala</v>
+        <v>Qasimali bhai Taiyebali bhai Kotwal</v>
       </c>
       <c r="E192" t="str">
-        <v>30367453</v>
+        <v>20401345</v>
       </c>
       <c r="F192" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G192" t="str">
         <v/>
-      </c>
-      <c r="H192" t="str">
-        <v>20/05/2026</v>
-      </c>
-      <c r="I192" t="str">
-        <v>Wednesday</v>
-      </c>
-      <c r="J192" t="str">
-        <v>12:24:47</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>1778659312652_448</v>
+        <v>1778659312652_44</v>
       </c>
       <c r="B193" t="str">
-        <v>449</v>
+        <v>45</v>
       </c>
       <c r="C193" t="str">
-        <v>393</v>
+        <v>213</v>
       </c>
       <c r="D193" t="str">
-        <v>Qasimali bhai Taiyebali bhai Kotwal</v>
+        <v>Alefiyah bai Abbasali bhai Fakhri</v>
       </c>
       <c r="E193" t="str">
-        <v>20401345</v>
+        <v>30366726</v>
       </c>
       <c r="F193" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G193" t="str">
-        <v/>
+        <v>shkh fakhruddin badi</v>
+      </c>
+      <c r="H193" t="str">
+        <v>18/05/2026</v>
+      </c>
+      <c r="I193" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J193" t="str">
+        <v>11:33:17</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>1778659312652_44</v>
+        <v>1778659312652_449</v>
       </c>
       <c r="B194" t="str">
-        <v>45</v>
+        <v>450</v>
       </c>
       <c r="C194" t="str">
-        <v>213</v>
+        <v>1497</v>
       </c>
       <c r="D194" t="str">
-        <v>Alefiyah bai Abbasali bhai Fakhri</v>
+        <v>Quraish bhai Shaikh Mohammed bhai Maharaj</v>
       </c>
       <c r="E194" t="str">
-        <v>30366726</v>
+        <v>20387792</v>
       </c>
       <c r="F194" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G194" t="str">
-        <v>shkh fakhruddin badi</v>
-      </c>
-      <c r="H194" t="str">
-        <v>18/05/2026</v>
-      </c>
-      <c r="I194" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="J194" t="str">
-        <v>11:33:17</v>
+        <v/>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>1778659312652_449</v>
+        <v>1778659312652_575</v>
       </c>
       <c r="B195" t="str">
-        <v>450</v>
+        <v>576</v>
       </c>
       <c r="C195" t="str">
-        <v>1497</v>
+        <v>238</v>
       </c>
       <c r="D195" t="str">
-        <v>Quraish bhai Shaikh Mohammed bhai Maharaj</v>
+        <v>Samina bai Husain bhai Hathai</v>
       </c>
       <c r="E195" t="str">
-        <v>20387792</v>
+        <v>20318771</v>
       </c>
       <c r="F195" t="str">
         <v>Pending</v>
@@ -7042,51 +7024,42 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>1778659312652_99</v>
+        <v>1778659312652_103</v>
       </c>
       <c r="B260" t="str">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C260" t="str">
-        <v>236</v>
+        <v>1303</v>
       </c>
       <c r="D260" t="str">
-        <v>Batul bai Johar bhai Saroda</v>
+        <v>Batul bai Qutbuddin bhai Rustam</v>
       </c>
       <c r="E260" t="str">
-        <v>30488741</v>
+        <v>30366656</v>
       </c>
       <c r="F260" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G260" t="str">
-        <v>Ilyas</v>
-      </c>
-      <c r="H260" t="str">
-        <v>24/05/2026</v>
-      </c>
-      <c r="I260" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="J260" t="str">
-        <v>20:29:18</v>
+        <v/>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>1778659312652_103</v>
+        <v>1778659312652_104</v>
       </c>
       <c r="B261" t="str">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C261" t="str">
-        <v>1303</v>
+        <v>76</v>
       </c>
       <c r="D261" t="str">
-        <v>Batul bai Qutbuddin bhai Rustam</v>
+        <v>Batul bai Saifuddin bhai Doodhbhai</v>
       </c>
       <c r="E261" t="str">
-        <v>30366656</v>
+        <v>30368616</v>
       </c>
       <c r="F261" t="str">
         <v>Pending</v>
@@ -7097,19 +7070,19 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>1778659312652_104</v>
+        <v>1778659312652_105</v>
       </c>
       <c r="B262" t="str">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C262" t="str">
-        <v>76</v>
+        <v>744</v>
       </c>
       <c r="D262" t="str">
-        <v>Batul bai Saifuddin bhai Doodhbhai</v>
+        <v>Batul bai Shaikh Akbarhusain bhai Rampurwala</v>
       </c>
       <c r="E262" t="str">
-        <v>30368616</v>
+        <v>30367359</v>
       </c>
       <c r="F262" t="str">
         <v>Pending</v>
@@ -7120,80 +7093,89 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>1778659312652_105</v>
+        <v>1778659312652_106</v>
       </c>
       <c r="B263" t="str">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C263" t="str">
-        <v>744</v>
+        <v>807</v>
       </c>
       <c r="D263" t="str">
-        <v>Batul bai Shaikh Akbarhusain bhai Rampurwala</v>
+        <v>Batul bai Taiyebali bhai Bankoda</v>
       </c>
       <c r="E263" t="str">
-        <v>30367359</v>
+        <v>30367508</v>
       </c>
       <c r="F263" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G263" t="str">
-        <v/>
+        <v>zainab ben antri</v>
+      </c>
+      <c r="H263" t="str">
+        <v>18/05/2026</v>
+      </c>
+      <c r="I263" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J263" t="str">
+        <v>11:50:34</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>1778659312652_106</v>
+        <v>1778659312652_6</v>
       </c>
       <c r="B264" t="str">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="C264" t="str">
-        <v>807</v>
+        <v>7</v>
       </c>
       <c r="D264" t="str">
-        <v>Batul bai Taiyebali bhai Bankoda</v>
+        <v>Abbas bhai Alihusain bhai Sihjee</v>
       </c>
       <c r="E264" t="str">
-        <v>30367508</v>
+        <v>20435003</v>
       </c>
       <c r="F264" t="str">
         <v>Given</v>
       </c>
       <c r="G264" t="str">
-        <v>zainab ben antri</v>
+        <v>Ajab ben Khand</v>
       </c>
       <c r="H264" t="str">
-        <v>18/05/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="I264" t="str">
-        <v>Monday</v>
+        <v>Thursday</v>
       </c>
       <c r="J264" t="str">
-        <v>11:50:34</v>
+        <v>10:25:43</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>1778659312652_6</v>
+        <v>1778659312652_335</v>
       </c>
       <c r="B265" t="str">
-        <v>7</v>
+        <v>336</v>
       </c>
       <c r="C265" t="str">
-        <v>7</v>
+        <v>1197</v>
       </c>
       <c r="D265" t="str">
-        <v>Abbas bhai Alihusain bhai Sihjee</v>
+        <v>Khanali bhai Mohammadhussain bhai Hedari</v>
       </c>
       <c r="E265" t="str">
-        <v>20435003</v>
+        <v>20414120</v>
       </c>
       <c r="F265" t="str">
         <v>Given</v>
       </c>
       <c r="G265" t="str">
-        <v>Ajab ben Khand</v>
+        <v/>
       </c>
       <c r="H265" t="str">
         <v>21/05/2026</v>
@@ -7202,56 +7184,47 @@
         <v>Thursday</v>
       </c>
       <c r="J265" t="str">
-        <v>10:25:43</v>
+        <v>11:08:30</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>1778659312652_335</v>
+        <v>1778659312652_107</v>
       </c>
       <c r="B266" t="str">
-        <v>336</v>
+        <v>108</v>
       </c>
       <c r="C266" t="str">
-        <v>1197</v>
+        <v>17</v>
       </c>
       <c r="D266" t="str">
-        <v>Khanali bhai Mohammadhussain bhai Hedari</v>
+        <v>Bilqis bai Abidhusain bhai Nareli</v>
       </c>
       <c r="E266" t="str">
-        <v>20414120</v>
+        <v>20318722</v>
       </c>
       <c r="F266" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G266" t="str">
         <v/>
-      </c>
-      <c r="H266" t="str">
-        <v>21/05/2026</v>
-      </c>
-      <c r="I266" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="J266" t="str">
-        <v>11:08:30</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>1778659312652_107</v>
+        <v>1778659312652_108</v>
       </c>
       <c r="B267" t="str">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C267" t="str">
-        <v>17</v>
+        <v>588</v>
       </c>
       <c r="D267" t="str">
-        <v>Bilqis bai Abidhusain bhai Nareli</v>
+        <v>Bilqis bai Husain bhai Gadi</v>
       </c>
       <c r="E267" t="str">
-        <v>20318722</v>
+        <v>20318760</v>
       </c>
       <c r="F267" t="str">
         <v>Pending</v>
@@ -7262,19 +7235,19 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>1778659312652_108</v>
+        <v>1778659312652_326</v>
       </c>
       <c r="B268" t="str">
-        <v>109</v>
+        <v>327</v>
       </c>
       <c r="C268" t="str">
-        <v>588</v>
+        <v>431</v>
       </c>
       <c r="D268" t="str">
-        <v>Bilqis bai Husain bhai Gadi</v>
+        <v>Khadija bai Fakhruddin bhai Peeth</v>
       </c>
       <c r="E268" t="str">
-        <v>20318760</v>
+        <v>30366840</v>
       </c>
       <c r="F268" t="str">
         <v>Pending</v>
@@ -7285,19 +7258,19 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>1778659312652_326</v>
+        <v>1778659312652_327</v>
       </c>
       <c r="B269" t="str">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C269" t="str">
-        <v>431</v>
+        <v>822</v>
       </c>
       <c r="D269" t="str">
-        <v>Khadija bai Fakhruddin bhai Peeth</v>
+        <v>Khadija bai Ghulamhusain bhai Dudhwala</v>
       </c>
       <c r="E269" t="str">
-        <v>30366840</v>
+        <v>30367535</v>
       </c>
       <c r="F269" t="str">
         <v>Pending</v>
@@ -7308,19 +7281,19 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>1778659312652_327</v>
+        <v>1778659312652_328</v>
       </c>
       <c r="B270" t="str">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C270" t="str">
-        <v>822</v>
+        <v>684</v>
       </c>
       <c r="D270" t="str">
-        <v>Khadija bai Ghulamhusain bhai Dudhwala</v>
+        <v>Khadija bai Haiderali bhai Maudi wala</v>
       </c>
       <c r="E270" t="str">
-        <v>30367535</v>
+        <v>30367251</v>
       </c>
       <c r="F270" t="str">
         <v>Pending</v>
@@ -7331,19 +7304,19 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>1778659312652_328</v>
+        <v>1778659312652_329</v>
       </c>
       <c r="B271" t="str">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C271" t="str">
-        <v>684</v>
+        <v>62</v>
       </c>
       <c r="D271" t="str">
-        <v>Khadija bai Haiderali bhai Maudi wala</v>
+        <v>Khadija bai Mulla Fakhruddin bhai Baroda</v>
       </c>
       <c r="E271" t="str">
-        <v>30367251</v>
+        <v>20318054</v>
       </c>
       <c r="F271" t="str">
         <v>Pending</v>
@@ -7354,97 +7327,97 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>1778659312652_329</v>
+        <v>1778659312652_102</v>
       </c>
       <c r="B272" t="str">
-        <v>330</v>
+        <v>103</v>
       </c>
       <c r="C272" t="str">
-        <v>62</v>
+        <v>637</v>
       </c>
       <c r="D272" t="str">
-        <v>Khadija bai Mulla Fakhruddin bhai Baroda</v>
+        <v>Batul bai Mufaddal bhai Jaan</v>
       </c>
       <c r="E272" t="str">
-        <v>20318054</v>
+        <v>30367654</v>
       </c>
       <c r="F272" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G272" t="str">
-        <v/>
+        <v>mulla jivaji</v>
+      </c>
+      <c r="H272" t="str">
+        <v>22/05/2026</v>
+      </c>
+      <c r="I272" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="J272" t="str">
+        <v>11:47:31</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>1778659312652_102</v>
+        <v>1778659312652_330</v>
       </c>
       <c r="B273" t="str">
-        <v>103</v>
+        <v>331</v>
       </c>
       <c r="C273" t="str">
-        <v>637</v>
+        <v>1356</v>
       </c>
       <c r="D273" t="str">
-        <v>Batul bai Mufaddal bhai Jaan</v>
+        <v>Khadija bai Murtaza bhai Ratawala</v>
       </c>
       <c r="E273" t="str">
-        <v>30367654</v>
+        <v>30367899</v>
       </c>
       <c r="F273" t="str">
         <v>Given</v>
       </c>
       <c r="G273" t="str">
-        <v>mulla jivaji</v>
-      </c>
-      <c r="H273" t="str">
-        <v>22/05/2026</v>
-      </c>
-      <c r="I273" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J273" t="str">
-        <v>11:47:31</v>
+        <v>Fakhruddin kawja</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>1778659312652_330</v>
+        <v>1778659312652_331</v>
       </c>
       <c r="B274" t="str">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C274" t="str">
-        <v>1356</v>
+        <v>388</v>
       </c>
       <c r="D274" t="str">
-        <v>Khadija bai Murtaza bhai Ratawala</v>
+        <v>Khadija bai Qutbuddin bhai Tara</v>
       </c>
       <c r="E274" t="str">
-        <v>30367899</v>
+        <v>30366583</v>
       </c>
       <c r="F274" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G274" t="str">
-        <v>Fakhruddin kawja</v>
+        <v/>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>1778659312652_331</v>
+        <v>1778659312652_332</v>
       </c>
       <c r="B275" t="str">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C275" t="str">
-        <v>388</v>
+        <v>310</v>
       </c>
       <c r="D275" t="str">
-        <v>Khadija bai Qutbuddin bhai Tara</v>
+        <v>Khadija bai Saifuddin bhai Ezzi</v>
       </c>
       <c r="E275" t="str">
-        <v>30366583</v>
+        <v>30366643</v>
       </c>
       <c r="F275" t="str">
         <v>Pending</v>
@@ -7455,114 +7428,114 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>1778659312652_332</v>
+        <v>1778659312652_333</v>
       </c>
       <c r="B276" t="str">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C276" t="str">
-        <v>310</v>
+        <v>1029</v>
       </c>
       <c r="D276" t="str">
-        <v>Khadija bai Saifuddin bhai Ezzi</v>
+        <v>Khadija bai Shaikh Mohammed bhai Khumanpur</v>
       </c>
       <c r="E276" t="str">
-        <v>30366643</v>
+        <v>30367849</v>
       </c>
       <c r="F276" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G276" t="str">
-        <v/>
+        <v>yakut bhai gaba</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>1778659312652_333</v>
+        <v>1778659312652_334</v>
       </c>
       <c r="B277" t="str">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C277" t="str">
-        <v>1029</v>
+        <v>138</v>
       </c>
       <c r="D277" t="str">
-        <v>Khadija bai Shaikh Mohammed bhai Khumanpur</v>
+        <v>Khadija bai Tayyeb bhai Gadi</v>
       </c>
       <c r="E277" t="str">
-        <v>30367849</v>
+        <v>30366336</v>
       </c>
       <c r="F277" t="str">
         <v>Given</v>
       </c>
       <c r="G277" t="str">
-        <v>yakut bhai gaba</v>
+        <v>shkh fakhruddin badi</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>1778659312652_334</v>
+        <v>1778659312652_336</v>
       </c>
       <c r="B278" t="str">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C278" t="str">
-        <v>138</v>
+        <v>980</v>
       </c>
       <c r="D278" t="str">
-        <v>Khadija bai Tayyeb bhai Gadi</v>
+        <v>Khuzaima bhai Shabbirhusain bhai Ramgarhwala</v>
       </c>
       <c r="E278" t="str">
-        <v>30366336</v>
+        <v>20402290</v>
       </c>
       <c r="F278" t="str">
         <v>Given</v>
       </c>
       <c r="G278" t="str">
-        <v>shkh fakhruddin badi</v>
+        <v>Nasa bhai</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>1778659312652_336</v>
+        <v>1778659312652_698</v>
       </c>
       <c r="B279" t="str">
-        <v>337</v>
+        <v>699</v>
       </c>
       <c r="C279" t="str">
-        <v>980</v>
+        <v>1475</v>
       </c>
       <c r="D279" t="str">
-        <v>Khuzaima bhai Shabbirhusain bhai Ramgarhwala</v>
+        <v>Tasneem bai Yusuf bhai Rail</v>
       </c>
       <c r="E279" t="str">
-        <v>20402290</v>
+        <v>30366367</v>
       </c>
       <c r="F279" t="str">
         <v>Given</v>
       </c>
       <c r="G279" t="str">
-        <v>Nasa bhai</v>
+        <v/>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>1778659312652_698</v>
+        <v>1778659312652_69</v>
       </c>
       <c r="B280" t="str">
-        <v>699</v>
+        <v>70</v>
       </c>
       <c r="C280" t="str">
-        <v>1475</v>
+        <v>931</v>
       </c>
       <c r="D280" t="str">
-        <v>Tasneem bai Yusuf bhai Rail</v>
+        <v>Arwa bai Sajjadhusain bhai Partapur</v>
       </c>
       <c r="E280" t="str">
-        <v>30366367</v>
+        <v>20318614</v>
       </c>
       <c r="F280" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G280" t="str">
         <v/>
@@ -7570,25 +7543,34 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>1778659312652_69</v>
+        <v>1778659312652_99</v>
       </c>
       <c r="B281" t="str">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C281" t="str">
-        <v>931</v>
+        <v>236</v>
       </c>
       <c r="D281" t="str">
-        <v>Arwa bai Sajjadhusain bhai Partapur</v>
+        <v>Batul bai Johar bhai Saroda</v>
       </c>
       <c r="E281" t="str">
-        <v>20318614</v>
+        <v>30488741</v>
       </c>
       <c r="F281" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G281" t="str">
-        <v/>
+        <v>Ilyas</v>
+      </c>
+      <c r="H281" t="str">
+        <v>24/05/2026</v>
+      </c>
+      <c r="I281" t="str">
+        <v>Sunday</v>
+      </c>
+      <c r="J281" t="str">
+        <v>22:35:04</v>
       </c>
     </row>
     <row r="282">
@@ -15147,19 +15129,19 @@
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>1778659312652_309</v>
+        <v>1778659312652_316</v>
       </c>
       <c r="B585" t="str">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C585" t="str">
-        <v>1146</v>
+        <v>235</v>
       </c>
       <c r="D585" t="str">
-        <v>Ismail bhai Alihusain bhai Damdi</v>
+        <v>Jumana bai Fakhruddin bhai Tarawala</v>
       </c>
       <c r="E585" t="str">
-        <v>30366733</v>
+        <v>30367675</v>
       </c>
       <c r="F585" t="str">
         <v>Pending</v>
@@ -15170,22 +15152,22 @@
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>1778659312652_310</v>
+        <v>1778659312652_309</v>
       </c>
       <c r="B586" t="str">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C586" t="str">
-        <v>1227</v>
+        <v>1146</v>
       </c>
       <c r="D586" t="str">
-        <v>Ismail bhai Qurbanhusain bhai Billa</v>
+        <v>Ismail bhai Alihusain bhai Damdi</v>
       </c>
       <c r="E586" t="str">
-        <v>20318051</v>
+        <v>30366733</v>
       </c>
       <c r="F586" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G586" t="str">
         <v/>
@@ -15193,22 +15175,22 @@
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>1778659312652_311</v>
+        <v>1778659312652_310</v>
       </c>
       <c r="B587" t="str">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C587" t="str">
-        <v>1438</v>
+        <v>1227</v>
       </c>
       <c r="D587" t="str">
-        <v>Ismail bhai Saifuddin bhai Patrawala</v>
+        <v>Ismail bhai Qurbanhusain bhai Billa</v>
       </c>
       <c r="E587" t="str">
-        <v>30904442</v>
+        <v>20318051</v>
       </c>
       <c r="F587" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G587" t="str">
         <v/>
@@ -15216,19 +15198,19 @@
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>1778659312652_313</v>
+        <v>1778659312652_311</v>
       </c>
       <c r="B588" t="str">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C588" t="str">
-        <v>316</v>
+        <v>1438</v>
       </c>
       <c r="D588" t="str">
-        <v>Jamila bai Ahmedali bhai Tara</v>
+        <v>Ismail bhai Saifuddin bhai Patrawala</v>
       </c>
       <c r="E588" t="str">
-        <v>20318246</v>
+        <v>30904442</v>
       </c>
       <c r="F588" t="str">
         <v>Pending</v>
@@ -15239,19 +15221,19 @@
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>1778659312652_314</v>
+        <v>1778659312652_313</v>
       </c>
       <c r="B589" t="str">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C589" t="str">
-        <v>494</v>
+        <v>316</v>
       </c>
       <c r="D589" t="str">
-        <v>Jamila bai Najmuddin bhai Gadhiwala</v>
+        <v>Jamila bai Ahmedali bhai Tara</v>
       </c>
       <c r="E589" t="str">
-        <v>30368526</v>
+        <v>20318246</v>
       </c>
       <c r="F589" t="str">
         <v>Pending</v>
@@ -15262,22 +15244,22 @@
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>1778659312652_315</v>
+        <v>1778659312652_314</v>
       </c>
       <c r="B590" t="str">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C590" t="str">
-        <v>304</v>
+        <v>494</v>
       </c>
       <c r="D590" t="str">
-        <v>Jumana bai Burhanuddin bhai Gabruwala</v>
+        <v>Jamila bai Najmuddin bhai Gadhiwala</v>
       </c>
       <c r="E590" t="str">
-        <v>30366585</v>
+        <v>30368526</v>
       </c>
       <c r="F590" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G590" t="str">
         <v/>
@@ -15285,22 +15267,22 @@
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>1778659312652_317</v>
+        <v>1778659312652_315</v>
       </c>
       <c r="B591" t="str">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C591" t="str">
-        <v>1181</v>
+        <v>304</v>
       </c>
       <c r="D591" t="str">
-        <v>Jumana bai Hakimuddin bhai Dhambola</v>
+        <v>Jumana bai Burhanuddin bhai Gabruwala</v>
       </c>
       <c r="E591" t="str">
-        <v>30367995</v>
+        <v>30366585</v>
       </c>
       <c r="F591" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G591" t="str">
         <v/>
@@ -15308,19 +15290,19 @@
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>1778659312652_318</v>
+        <v>1778659312652_317</v>
       </c>
       <c r="B592" t="str">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C592" t="str">
-        <v>196</v>
+        <v>1181</v>
       </c>
       <c r="D592" t="str">
-        <v>Jumana bai Husain bhai Badshah</v>
+        <v>Jumana bai Hakimuddin bhai Dhambola</v>
       </c>
       <c r="E592" t="str">
-        <v>30368195</v>
+        <v>30367995</v>
       </c>
       <c r="F592" t="str">
         <v>Pending</v>
@@ -15331,19 +15313,19 @@
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>1778659312652_31</v>
+        <v>1778659312652_318</v>
       </c>
       <c r="B593" t="str">
-        <v>32</v>
+        <v>319</v>
       </c>
       <c r="C593" t="str">
-        <v/>
+        <v>196</v>
       </c>
       <c r="D593" t="str">
-        <v>Ajab bai Mulla Burhanuddin bhai Mohib</v>
+        <v>Jumana bai Husain bhai Badshah</v>
       </c>
       <c r="E593" t="str">
-        <v>30391898</v>
+        <v>30368195</v>
       </c>
       <c r="F593" t="str">
         <v>Pending</v>
@@ -15354,98 +15336,89 @@
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>1778659312652_312</v>
+        <v>1778659312652_31</v>
       </c>
       <c r="B594" t="str">
-        <v>313</v>
+        <v>32</v>
       </c>
       <c r="C594" t="str">
-        <v>160</v>
+        <v/>
       </c>
       <c r="D594" t="str">
-        <v>Jamila bai Abdullah bhai Patwari</v>
+        <v>Ajab bai Mulla Burhanuddin bhai Mohib</v>
       </c>
       <c r="E594" t="str">
-        <v>30366400</v>
+        <v>30391898</v>
       </c>
       <c r="F594" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G594" t="str">
         <v/>
-      </c>
-      <c r="H594" t="str">
-        <v>21/05/2026</v>
-      </c>
-      <c r="I594" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="J594" t="str">
-        <v>11:02:18</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>1778659312652_30</v>
+        <v>1778659312652_312</v>
       </c>
       <c r="B595" t="str">
-        <v>31</v>
+        <v>313</v>
       </c>
       <c r="C595" t="str">
-        <v>101</v>
+        <v>160</v>
       </c>
       <c r="D595" t="str">
-        <v>Ajab bai Mufaddal bhai Bangali</v>
+        <v>Jamila bai Abdullah bhai Patwari</v>
       </c>
       <c r="E595" t="str">
-        <v>30368206</v>
+        <v>30366400</v>
       </c>
       <c r="F595" t="str">
         <v>Given</v>
       </c>
       <c r="G595" t="str">
-        <v>Insiya ben pachlasa</v>
+        <v/>
       </c>
       <c r="H595" t="str">
-        <v>23/05/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="I595" t="str">
-        <v>Saturday</v>
+        <v>Thursday</v>
       </c>
       <c r="J595" t="str">
-        <v>12:14:22</v>
+        <v>11:02:18</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>1778659312652_316</v>
+        <v>1778659312652_30</v>
       </c>
       <c r="B596" t="str">
-        <v>317</v>
+        <v>31</v>
       </c>
       <c r="C596" t="str">
-        <v>235</v>
+        <v>101</v>
       </c>
       <c r="D596" t="str">
-        <v>Jumana bai Fakhruddin bhai Tarawala</v>
+        <v>Ajab bai Mufaddal bhai Bangali</v>
       </c>
       <c r="E596" t="str">
-        <v>30367675</v>
+        <v>30368206</v>
       </c>
       <c r="F596" t="str">
         <v>Given</v>
       </c>
       <c r="G596" t="str">
-        <v>Ilyas</v>
+        <v>Insiya ben pachlasa</v>
       </c>
       <c r="H596" t="str">
-        <v>24/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="I596" t="str">
-        <v>Sunday</v>
+        <v>Saturday</v>
       </c>
       <c r="J596" t="str">
-        <v>20:53:42</v>
+        <v>12:14:22</v>
       </c>
     </row>
     <row r="597">

--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -6969,74 +6969,74 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>1778659312652_100</v>
+        <v>1778659312652_99</v>
       </c>
       <c r="B258" t="str">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C258" t="str">
-        <v>117</v>
+        <v>236</v>
       </c>
       <c r="D258" t="str">
-        <v>Batul bai Mohammadhussain bhai Bankoda</v>
+        <v>Batul bai Johar bhai Saroda</v>
       </c>
       <c r="E258" t="str">
-        <v>30360295</v>
+        <v>30488741</v>
       </c>
       <c r="F258" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G258" t="str">
         <v/>
-      </c>
-      <c r="H258" t="str">
-        <v>22/05/2026</v>
-      </c>
-      <c r="I258" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J258" t="str">
-        <v>12:19:42</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>1778659312652_101</v>
+        <v>1778659312652_100</v>
       </c>
       <c r="B259" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C259" t="str">
-        <v>254</v>
+        <v>117</v>
       </c>
       <c r="D259" t="str">
-        <v>Batul bai Mohammadhussain bhai Patra</v>
+        <v>Batul bai Mohammadhussain bhai Bankoda</v>
       </c>
       <c r="E259" t="str">
-        <v>20318132</v>
+        <v>30360295</v>
       </c>
       <c r="F259" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G259" t="str">
         <v/>
+      </c>
+      <c r="H259" t="str">
+        <v>22/05/2026</v>
+      </c>
+      <c r="I259" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="J259" t="str">
+        <v>12:19:42</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>1778659312652_103</v>
+        <v>1778659312652_101</v>
       </c>
       <c r="B260" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C260" t="str">
-        <v>1303</v>
+        <v>254</v>
       </c>
       <c r="D260" t="str">
-        <v>Batul bai Qutbuddin bhai Rustam</v>
+        <v>Batul bai Mohammadhussain bhai Patra</v>
       </c>
       <c r="E260" t="str">
-        <v>30366656</v>
+        <v>20318132</v>
       </c>
       <c r="F260" t="str">
         <v>Pending</v>
@@ -7047,19 +7047,19 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>1778659312652_104</v>
+        <v>1778659312652_103</v>
       </c>
       <c r="B261" t="str">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C261" t="str">
-        <v>76</v>
+        <v>1303</v>
       </c>
       <c r="D261" t="str">
-        <v>Batul bai Saifuddin bhai Doodhbhai</v>
+        <v>Batul bai Qutbuddin bhai Rustam</v>
       </c>
       <c r="E261" t="str">
-        <v>30368616</v>
+        <v>30366656</v>
       </c>
       <c r="F261" t="str">
         <v>Pending</v>
@@ -7070,19 +7070,19 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>1778659312652_105</v>
+        <v>1778659312652_104</v>
       </c>
       <c r="B262" t="str">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C262" t="str">
-        <v>744</v>
+        <v>76</v>
       </c>
       <c r="D262" t="str">
-        <v>Batul bai Shaikh Akbarhusain bhai Rampurwala</v>
+        <v>Batul bai Saifuddin bhai Doodhbhai</v>
       </c>
       <c r="E262" t="str">
-        <v>30367359</v>
+        <v>30368616</v>
       </c>
       <c r="F262" t="str">
         <v>Pending</v>
@@ -7093,89 +7093,80 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>1778659312652_106</v>
+        <v>1778659312652_105</v>
       </c>
       <c r="B263" t="str">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C263" t="str">
-        <v>807</v>
+        <v>744</v>
       </c>
       <c r="D263" t="str">
-        <v>Batul bai Taiyebali bhai Bankoda</v>
+        <v>Batul bai Shaikh Akbarhusain bhai Rampurwala</v>
       </c>
       <c r="E263" t="str">
-        <v>30367508</v>
+        <v>30367359</v>
       </c>
       <c r="F263" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G263" t="str">
-        <v>zainab ben antri</v>
-      </c>
-      <c r="H263" t="str">
-        <v>18/05/2026</v>
-      </c>
-      <c r="I263" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="J263" t="str">
-        <v>11:50:34</v>
+        <v/>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>1778659312652_6</v>
+        <v>1778659312652_106</v>
       </c>
       <c r="B264" t="str">
-        <v>7</v>
+        <v>107</v>
       </c>
       <c r="C264" t="str">
-        <v>7</v>
+        <v>807</v>
       </c>
       <c r="D264" t="str">
-        <v>Abbas bhai Alihusain bhai Sihjee</v>
+        <v>Batul bai Taiyebali bhai Bankoda</v>
       </c>
       <c r="E264" t="str">
-        <v>20435003</v>
+        <v>30367508</v>
       </c>
       <c r="F264" t="str">
         <v>Given</v>
       </c>
       <c r="G264" t="str">
-        <v>Ajab ben Khand</v>
+        <v>zainab ben antri</v>
       </c>
       <c r="H264" t="str">
-        <v>21/05/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="I264" t="str">
-        <v>Thursday</v>
+        <v>Monday</v>
       </c>
       <c r="J264" t="str">
-        <v>10:25:43</v>
+        <v>11:50:34</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>1778659312652_335</v>
+        <v>1778659312652_6</v>
       </c>
       <c r="B265" t="str">
-        <v>336</v>
+        <v>7</v>
       </c>
       <c r="C265" t="str">
-        <v>1197</v>
+        <v>7</v>
       </c>
       <c r="D265" t="str">
-        <v>Khanali bhai Mohammadhussain bhai Hedari</v>
+        <v>Abbas bhai Alihusain bhai Sihjee</v>
       </c>
       <c r="E265" t="str">
-        <v>20414120</v>
+        <v>20435003</v>
       </c>
       <c r="F265" t="str">
         <v>Given</v>
       </c>
       <c r="G265" t="str">
-        <v/>
+        <v>Ajab ben Khand</v>
       </c>
       <c r="H265" t="str">
         <v>21/05/2026</v>
@@ -7184,47 +7175,56 @@
         <v>Thursday</v>
       </c>
       <c r="J265" t="str">
-        <v>11:08:30</v>
+        <v>10:25:43</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>1778659312652_107</v>
+        <v>1778659312652_335</v>
       </c>
       <c r="B266" t="str">
-        <v>108</v>
+        <v>336</v>
       </c>
       <c r="C266" t="str">
-        <v>17</v>
+        <v>1197</v>
       </c>
       <c r="D266" t="str">
-        <v>Bilqis bai Abidhusain bhai Nareli</v>
+        <v>Khanali bhai Mohammadhussain bhai Hedari</v>
       </c>
       <c r="E266" t="str">
-        <v>20318722</v>
+        <v>20414120</v>
       </c>
       <c r="F266" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G266" t="str">
         <v/>
+      </c>
+      <c r="H266" t="str">
+        <v>21/05/2026</v>
+      </c>
+      <c r="I266" t="str">
+        <v>Thursday</v>
+      </c>
+      <c r="J266" t="str">
+        <v>11:08:30</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>1778659312652_108</v>
+        <v>1778659312652_107</v>
       </c>
       <c r="B267" t="str">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C267" t="str">
-        <v>588</v>
+        <v>17</v>
       </c>
       <c r="D267" t="str">
-        <v>Bilqis bai Husain bhai Gadi</v>
+        <v>Bilqis bai Abidhusain bhai Nareli</v>
       </c>
       <c r="E267" t="str">
-        <v>20318760</v>
+        <v>20318722</v>
       </c>
       <c r="F267" t="str">
         <v>Pending</v>
@@ -7235,19 +7235,19 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>1778659312652_326</v>
+        <v>1778659312652_108</v>
       </c>
       <c r="B268" t="str">
-        <v>327</v>
+        <v>109</v>
       </c>
       <c r="C268" t="str">
-        <v>431</v>
+        <v>588</v>
       </c>
       <c r="D268" t="str">
-        <v>Khadija bai Fakhruddin bhai Peeth</v>
+        <v>Bilqis bai Husain bhai Gadi</v>
       </c>
       <c r="E268" t="str">
-        <v>30366840</v>
+        <v>20318760</v>
       </c>
       <c r="F268" t="str">
         <v>Pending</v>
@@ -7258,19 +7258,19 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>1778659312652_327</v>
+        <v>1778659312652_326</v>
       </c>
       <c r="B269" t="str">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C269" t="str">
-        <v>822</v>
+        <v>431</v>
       </c>
       <c r="D269" t="str">
-        <v>Khadija bai Ghulamhusain bhai Dudhwala</v>
+        <v>Khadija bai Fakhruddin bhai Peeth</v>
       </c>
       <c r="E269" t="str">
-        <v>30367535</v>
+        <v>30366840</v>
       </c>
       <c r="F269" t="str">
         <v>Pending</v>
@@ -7281,19 +7281,19 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>1778659312652_328</v>
+        <v>1778659312652_327</v>
       </c>
       <c r="B270" t="str">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C270" t="str">
-        <v>684</v>
+        <v>822</v>
       </c>
       <c r="D270" t="str">
-        <v>Khadija bai Haiderali bhai Maudi wala</v>
+        <v>Khadija bai Ghulamhusain bhai Dudhwala</v>
       </c>
       <c r="E270" t="str">
-        <v>30367251</v>
+        <v>30367535</v>
       </c>
       <c r="F270" t="str">
         <v>Pending</v>
@@ -7304,19 +7304,19 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>1778659312652_329</v>
+        <v>1778659312652_328</v>
       </c>
       <c r="B271" t="str">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C271" t="str">
-        <v>62</v>
+        <v>684</v>
       </c>
       <c r="D271" t="str">
-        <v>Khadija bai Mulla Fakhruddin bhai Baroda</v>
+        <v>Khadija bai Haiderali bhai Maudi wala</v>
       </c>
       <c r="E271" t="str">
-        <v>20318054</v>
+        <v>30367251</v>
       </c>
       <c r="F271" t="str">
         <v>Pending</v>
@@ -7327,97 +7327,97 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>1778659312652_102</v>
+        <v>1778659312652_329</v>
       </c>
       <c r="B272" t="str">
-        <v>103</v>
+        <v>330</v>
       </c>
       <c r="C272" t="str">
-        <v>637</v>
+        <v>62</v>
       </c>
       <c r="D272" t="str">
-        <v>Batul bai Mufaddal bhai Jaan</v>
+        <v>Khadija bai Mulla Fakhruddin bhai Baroda</v>
       </c>
       <c r="E272" t="str">
-        <v>30367654</v>
+        <v>20318054</v>
       </c>
       <c r="F272" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G272" t="str">
-        <v>mulla jivaji</v>
-      </c>
-      <c r="H272" t="str">
-        <v>22/05/2026</v>
-      </c>
-      <c r="I272" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J272" t="str">
-        <v>11:47:31</v>
+        <v/>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>1778659312652_330</v>
+        <v>1778659312652_102</v>
       </c>
       <c r="B273" t="str">
-        <v>331</v>
+        <v>103</v>
       </c>
       <c r="C273" t="str">
-        <v>1356</v>
+        <v>637</v>
       </c>
       <c r="D273" t="str">
-        <v>Khadija bai Murtaza bhai Ratawala</v>
+        <v>Batul bai Mufaddal bhai Jaan</v>
       </c>
       <c r="E273" t="str">
-        <v>30367899</v>
+        <v>30367654</v>
       </c>
       <c r="F273" t="str">
         <v>Given</v>
       </c>
       <c r="G273" t="str">
-        <v>Fakhruddin kawja</v>
+        <v>mulla jivaji</v>
+      </c>
+      <c r="H273" t="str">
+        <v>22/05/2026</v>
+      </c>
+      <c r="I273" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="J273" t="str">
+        <v>11:47:31</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>1778659312652_331</v>
+        <v>1778659312652_330</v>
       </c>
       <c r="B274" t="str">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C274" t="str">
-        <v>388</v>
+        <v>1356</v>
       </c>
       <c r="D274" t="str">
-        <v>Khadija bai Qutbuddin bhai Tara</v>
+        <v>Khadija bai Murtaza bhai Ratawala</v>
       </c>
       <c r="E274" t="str">
-        <v>30366583</v>
+        <v>30367899</v>
       </c>
       <c r="F274" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G274" t="str">
-        <v/>
+        <v>Fakhruddin kawja</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>1778659312652_332</v>
+        <v>1778659312652_331</v>
       </c>
       <c r="B275" t="str">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C275" t="str">
-        <v>310</v>
+        <v>388</v>
       </c>
       <c r="D275" t="str">
-        <v>Khadija bai Saifuddin bhai Ezzi</v>
+        <v>Khadija bai Qutbuddin bhai Tara</v>
       </c>
       <c r="E275" t="str">
-        <v>30366643</v>
+        <v>30366583</v>
       </c>
       <c r="F275" t="str">
         <v>Pending</v>
@@ -7428,114 +7428,114 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>1778659312652_333</v>
+        <v>1778659312652_332</v>
       </c>
       <c r="B276" t="str">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C276" t="str">
-        <v>1029</v>
+        <v>310</v>
       </c>
       <c r="D276" t="str">
-        <v>Khadija bai Shaikh Mohammed bhai Khumanpur</v>
+        <v>Khadija bai Saifuddin bhai Ezzi</v>
       </c>
       <c r="E276" t="str">
-        <v>30367849</v>
+        <v>30366643</v>
       </c>
       <c r="F276" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G276" t="str">
-        <v>yakut bhai gaba</v>
+        <v/>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>1778659312652_334</v>
+        <v>1778659312652_333</v>
       </c>
       <c r="B277" t="str">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C277" t="str">
-        <v>138</v>
+        <v>1029</v>
       </c>
       <c r="D277" t="str">
-        <v>Khadija bai Tayyeb bhai Gadi</v>
+        <v>Khadija bai Shaikh Mohammed bhai Khumanpur</v>
       </c>
       <c r="E277" t="str">
-        <v>30366336</v>
+        <v>30367849</v>
       </c>
       <c r="F277" t="str">
         <v>Given</v>
       </c>
       <c r="G277" t="str">
-        <v>shkh fakhruddin badi</v>
+        <v>yakut bhai gaba</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>1778659312652_336</v>
+        <v>1778659312652_334</v>
       </c>
       <c r="B278" t="str">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C278" t="str">
-        <v>980</v>
+        <v>138</v>
       </c>
       <c r="D278" t="str">
-        <v>Khuzaima bhai Shabbirhusain bhai Ramgarhwala</v>
+        <v>Khadija bai Tayyeb bhai Gadi</v>
       </c>
       <c r="E278" t="str">
-        <v>20402290</v>
+        <v>30366336</v>
       </c>
       <c r="F278" t="str">
         <v>Given</v>
       </c>
       <c r="G278" t="str">
-        <v>Nasa bhai</v>
+        <v>shkh fakhruddin badi</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>1778659312652_698</v>
+        <v>1778659312652_336</v>
       </c>
       <c r="B279" t="str">
-        <v>699</v>
+        <v>337</v>
       </c>
       <c r="C279" t="str">
-        <v>1475</v>
+        <v>980</v>
       </c>
       <c r="D279" t="str">
-        <v>Tasneem bai Yusuf bhai Rail</v>
+        <v>Khuzaima bhai Shabbirhusain bhai Ramgarhwala</v>
       </c>
       <c r="E279" t="str">
-        <v>30366367</v>
+        <v>20402290</v>
       </c>
       <c r="F279" t="str">
         <v>Given</v>
       </c>
       <c r="G279" t="str">
-        <v/>
+        <v>Nasa bhai</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>1778659312652_69</v>
+        <v>1778659312652_698</v>
       </c>
       <c r="B280" t="str">
-        <v>70</v>
+        <v>699</v>
       </c>
       <c r="C280" t="str">
-        <v>931</v>
+        <v>1475</v>
       </c>
       <c r="D280" t="str">
-        <v>Arwa bai Sajjadhusain bhai Partapur</v>
+        <v>Tasneem bai Yusuf bhai Rail</v>
       </c>
       <c r="E280" t="str">
-        <v>20318614</v>
+        <v>30366367</v>
       </c>
       <c r="F280" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G280" t="str">
         <v/>
@@ -7543,34 +7543,25 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>1778659312652_99</v>
+        <v>1778659312652_69</v>
       </c>
       <c r="B281" t="str">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="C281" t="str">
-        <v>236</v>
+        <v>931</v>
       </c>
       <c r="D281" t="str">
-        <v>Batul bai Johar bhai Saroda</v>
+        <v>Arwa bai Sajjadhusain bhai Partapur</v>
       </c>
       <c r="E281" t="str">
-        <v>30488741</v>
+        <v>20318614</v>
       </c>
       <c r="F281" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G281" t="str">
-        <v>Ilyas</v>
-      </c>
-      <c r="H281" t="str">
-        <v>24/05/2026</v>
-      </c>
-      <c r="I281" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="J281" t="str">
-        <v>22:35:04</v>
+        <v/>
       </c>
     </row>
     <row r="282">
@@ -15129,19 +15120,19 @@
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>1778659312652_316</v>
+        <v>1778659312652_309</v>
       </c>
       <c r="B585" t="str">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C585" t="str">
-        <v>235</v>
+        <v>1146</v>
       </c>
       <c r="D585" t="str">
-        <v>Jumana bai Fakhruddin bhai Tarawala</v>
+        <v>Ismail bhai Alihusain bhai Damdi</v>
       </c>
       <c r="E585" t="str">
-        <v>30367675</v>
+        <v>30366733</v>
       </c>
       <c r="F585" t="str">
         <v>Pending</v>
@@ -15152,22 +15143,22 @@
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>1778659312652_309</v>
+        <v>1778659312652_310</v>
       </c>
       <c r="B586" t="str">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C586" t="str">
-        <v>1146</v>
+        <v>1227</v>
       </c>
       <c r="D586" t="str">
-        <v>Ismail bhai Alihusain bhai Damdi</v>
+        <v>Ismail bhai Qurbanhusain bhai Billa</v>
       </c>
       <c r="E586" t="str">
-        <v>30366733</v>
+        <v>20318051</v>
       </c>
       <c r="F586" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G586" t="str">
         <v/>
@@ -15175,22 +15166,22 @@
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>1778659312652_310</v>
+        <v>1778659312652_311</v>
       </c>
       <c r="B587" t="str">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C587" t="str">
-        <v>1227</v>
+        <v>1438</v>
       </c>
       <c r="D587" t="str">
-        <v>Ismail bhai Qurbanhusain bhai Billa</v>
+        <v>Ismail bhai Saifuddin bhai Patrawala</v>
       </c>
       <c r="E587" t="str">
-        <v>20318051</v>
+        <v>30904442</v>
       </c>
       <c r="F587" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G587" t="str">
         <v/>
@@ -15198,19 +15189,19 @@
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>1778659312652_311</v>
+        <v>1778659312652_316</v>
       </c>
       <c r="B588" t="str">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C588" t="str">
-        <v>1438</v>
+        <v>235</v>
       </c>
       <c r="D588" t="str">
-        <v>Ismail bhai Saifuddin bhai Patrawala</v>
+        <v>Jumana bai Fakhruddin bhai Tarawala</v>
       </c>
       <c r="E588" t="str">
-        <v>30904442</v>
+        <v>30367675</v>
       </c>
       <c r="F588" t="str">
         <v>Pending</v>

--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -6969,77 +6969,77 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>1778659312652_99</v>
+        <v>1778659312652_100</v>
       </c>
       <c r="B258" t="str">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C258" t="str">
-        <v>236</v>
+        <v>117</v>
       </c>
       <c r="D258" t="str">
-        <v>Batul bai Johar bhai Saroda</v>
+        <v>Batul bai Mohammadhussain bhai Bankoda</v>
       </c>
       <c r="E258" t="str">
-        <v>30488741</v>
+        <v>30360295</v>
       </c>
       <c r="F258" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G258" t="str">
         <v/>
+      </c>
+      <c r="H258" t="str">
+        <v>22/05/2026</v>
+      </c>
+      <c r="I258" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="J258" t="str">
+        <v>12:19:42</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>1778659312652_100</v>
+        <v>1778659312652_101</v>
       </c>
       <c r="B259" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C259" t="str">
-        <v>117</v>
+        <v>254</v>
       </c>
       <c r="D259" t="str">
-        <v>Batul bai Mohammadhussain bhai Bankoda</v>
+        <v>Batul bai Mohammadhussain bhai Patra</v>
       </c>
       <c r="E259" t="str">
-        <v>30360295</v>
+        <v>20318132</v>
       </c>
       <c r="F259" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G259" t="str">
         <v/>
-      </c>
-      <c r="H259" t="str">
-        <v>22/05/2026</v>
-      </c>
-      <c r="I259" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J259" t="str">
-        <v>12:19:42</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>1778659312652_101</v>
+        <v>1778659312652_99</v>
       </c>
       <c r="B260" t="str">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C260" t="str">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="D260" t="str">
-        <v>Batul bai Mohammadhussain bhai Patra</v>
+        <v>Batul bai Johar bhai Saroda</v>
       </c>
       <c r="E260" t="str">
-        <v>20318132</v>
+        <v>30488741</v>
       </c>
       <c r="F260" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G260" t="str">
         <v/>
@@ -15189,19 +15189,19 @@
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>1778659312652_316</v>
+        <v>1778659312652_313</v>
       </c>
       <c r="B588" t="str">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C588" t="str">
-        <v>235</v>
+        <v>316</v>
       </c>
       <c r="D588" t="str">
-        <v>Jumana bai Fakhruddin bhai Tarawala</v>
+        <v>Jamila bai Ahmedali bhai Tara</v>
       </c>
       <c r="E588" t="str">
-        <v>30367675</v>
+        <v>20318246</v>
       </c>
       <c r="F588" t="str">
         <v>Pending</v>
@@ -15212,19 +15212,19 @@
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>1778659312652_313</v>
+        <v>1778659312652_314</v>
       </c>
       <c r="B589" t="str">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C589" t="str">
-        <v>316</v>
+        <v>494</v>
       </c>
       <c r="D589" t="str">
-        <v>Jamila bai Ahmedali bhai Tara</v>
+        <v>Jamila bai Najmuddin bhai Gadhiwala</v>
       </c>
       <c r="E589" t="str">
-        <v>20318246</v>
+        <v>30368526</v>
       </c>
       <c r="F589" t="str">
         <v>Pending</v>
@@ -15235,22 +15235,22 @@
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>1778659312652_314</v>
+        <v>1778659312652_315</v>
       </c>
       <c r="B590" t="str">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C590" t="str">
-        <v>494</v>
+        <v>304</v>
       </c>
       <c r="D590" t="str">
-        <v>Jamila bai Najmuddin bhai Gadhiwala</v>
+        <v>Jumana bai Burhanuddin bhai Gabruwala</v>
       </c>
       <c r="E590" t="str">
-        <v>30368526</v>
+        <v>30366585</v>
       </c>
       <c r="F590" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G590" t="str">
         <v/>
@@ -15258,22 +15258,22 @@
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>1778659312652_315</v>
+        <v>1778659312652_317</v>
       </c>
       <c r="B591" t="str">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C591" t="str">
-        <v>304</v>
+        <v>1181</v>
       </c>
       <c r="D591" t="str">
-        <v>Jumana bai Burhanuddin bhai Gabruwala</v>
+        <v>Jumana bai Hakimuddin bhai Dhambola</v>
       </c>
       <c r="E591" t="str">
-        <v>30366585</v>
+        <v>30367995</v>
       </c>
       <c r="F591" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G591" t="str">
         <v/>
@@ -15281,19 +15281,19 @@
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>1778659312652_317</v>
+        <v>1778659312652_318</v>
       </c>
       <c r="B592" t="str">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C592" t="str">
-        <v>1181</v>
+        <v>196</v>
       </c>
       <c r="D592" t="str">
-        <v>Jumana bai Hakimuddin bhai Dhambola</v>
+        <v>Jumana bai Husain bhai Badshah</v>
       </c>
       <c r="E592" t="str">
-        <v>30367995</v>
+        <v>30368195</v>
       </c>
       <c r="F592" t="str">
         <v>Pending</v>
@@ -15304,19 +15304,19 @@
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>1778659312652_318</v>
+        <v>1778659312652_31</v>
       </c>
       <c r="B593" t="str">
-        <v>319</v>
+        <v>32</v>
       </c>
       <c r="C593" t="str">
-        <v>196</v>
+        <v/>
       </c>
       <c r="D593" t="str">
-        <v>Jumana bai Husain bhai Badshah</v>
+        <v>Ajab bai Mulla Burhanuddin bhai Mohib</v>
       </c>
       <c r="E593" t="str">
-        <v>30368195</v>
+        <v>30391898</v>
       </c>
       <c r="F593" t="str">
         <v>Pending</v>
@@ -15327,57 +15327,57 @@
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>1778659312652_31</v>
+        <v>1778659312652_312</v>
       </c>
       <c r="B594" t="str">
-        <v>32</v>
+        <v>313</v>
       </c>
       <c r="C594" t="str">
-        <v/>
+        <v>160</v>
       </c>
       <c r="D594" t="str">
-        <v>Ajab bai Mulla Burhanuddin bhai Mohib</v>
+        <v>Jamila bai Abdullah bhai Patwari</v>
       </c>
       <c r="E594" t="str">
-        <v>30391898</v>
+        <v>30366400</v>
       </c>
       <c r="F594" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G594" t="str">
         <v/>
+      </c>
+      <c r="H594" t="str">
+        <v>21/05/2026</v>
+      </c>
+      <c r="I594" t="str">
+        <v>Thursday</v>
+      </c>
+      <c r="J594" t="str">
+        <v>11:02:18</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>1778659312652_312</v>
+        <v>1778659312652_316</v>
       </c>
       <c r="B595" t="str">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C595" t="str">
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="D595" t="str">
-        <v>Jamila bai Abdullah bhai Patwari</v>
+        <v>Jumana bai Fakhruddin bhai Tarawala</v>
       </c>
       <c r="E595" t="str">
-        <v>30366400</v>
+        <v>30367675</v>
       </c>
       <c r="F595" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G595" t="str">
         <v/>
-      </c>
-      <c r="H595" t="str">
-        <v>21/05/2026</v>
-      </c>
-      <c r="I595" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="J595" t="str">
-        <v>11:02:18</v>
       </c>
     </row>
     <row r="596">

--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -1250,97 +1250,88 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>1778659312652_154</v>
+        <v>1778659312652_145</v>
       </c>
       <c r="B34" t="str">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C34" t="str">
-        <v>1339</v>
+        <v>1234</v>
       </c>
       <c r="D34" t="str">
-        <v>Farida bai Mohammedhusain bhai Kothari</v>
+        <v>Fakhruddin bhai Talib bhai Najafi</v>
       </c>
       <c r="E34" t="str">
-        <v>30367383</v>
+        <v>30368536</v>
       </c>
       <c r="F34" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G34" t="str">
-        <v>Ilyas</v>
-      </c>
-      <c r="H34" t="str">
-        <v>24/05/2026</v>
-      </c>
-      <c r="I34" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="J34" t="str">
-        <v>22:35:04</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>1778659312652_145</v>
+        <v>1778659312652_146</v>
       </c>
       <c r="B35" t="str">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C35" t="str">
-        <v>1234</v>
+        <v>855</v>
       </c>
       <c r="D35" t="str">
-        <v>Fakhruddin bhai Talib bhai Najafi</v>
+        <v>Fakhruddin bhai Yusuf bhai Kabja</v>
       </c>
       <c r="E35" t="str">
-        <v>30368536</v>
+        <v>30367601</v>
       </c>
       <c r="F35" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G35" t="str">
-        <v/>
+        <v>Fakhruddin kawja</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>1778659312652_146</v>
+        <v>1778659312652_14</v>
       </c>
       <c r="B36" t="str">
-        <v>147</v>
+        <v>15</v>
       </c>
       <c r="C36" t="str">
-        <v>855</v>
+        <v>1452</v>
       </c>
       <c r="D36" t="str">
-        <v>Fakhruddin bhai Yusuf bhai Kabja</v>
+        <v>Abdeali bhai Husain bhai Kika</v>
       </c>
       <c r="E36" t="str">
-        <v>30367601</v>
+        <v>30367463</v>
       </c>
       <c r="F36" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G36" t="str">
-        <v>Fakhruddin kawja</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>1778659312652_14</v>
+        <v>1778659312652_149</v>
       </c>
       <c r="B37" t="str">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="C37" t="str">
-        <v>1452</v>
+        <v>315</v>
       </c>
       <c r="D37" t="str">
-        <v>Abdeali bhai Husain bhai Kika</v>
+        <v>Farida bai Fakhruddin bhai Rustam</v>
       </c>
       <c r="E37" t="str">
-        <v>30367463</v>
+        <v>20318201</v>
       </c>
       <c r="F37" t="str">
         <v>Pending</v>
@@ -1351,74 +1342,74 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>1778659312652_149</v>
+        <v>1778659312652_150</v>
       </c>
       <c r="B38" t="str">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C38" t="str">
-        <v>315</v>
+        <v>491</v>
       </c>
       <c r="D38" t="str">
-        <v>Farida bai Fakhruddin bhai Rustam</v>
+        <v>Farida bai Husain bhai Galalji</v>
       </c>
       <c r="E38" t="str">
-        <v>20318201</v>
+        <v>30366897</v>
       </c>
       <c r="F38" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G38" t="str">
-        <v/>
+        <v>Zainab ben shabbir bhai Dhambola</v>
+      </c>
+      <c r="H38" t="str">
+        <v>22/05/2026</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="J38" t="str">
+        <v>11:31:37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>1778659312652_150</v>
+        <v>1778659312652_151</v>
       </c>
       <c r="B39" t="str">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C39" t="str">
-        <v>491</v>
+        <v>1122</v>
       </c>
       <c r="D39" t="str">
-        <v>Farida bai Husain bhai Galalji</v>
+        <v>Farida bai Juzer bhai Gyori</v>
       </c>
       <c r="E39" t="str">
-        <v>30366897</v>
+        <v>30367320</v>
       </c>
       <c r="F39" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G39" t="str">
-        <v>Zainab ben shabbir bhai Dhambola</v>
-      </c>
-      <c r="H39" t="str">
-        <v>22/05/2026</v>
-      </c>
-      <c r="I39" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J39" t="str">
-        <v>11:31:37</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>1778659312652_151</v>
+        <v>1778659312652_152</v>
       </c>
       <c r="B40" t="str">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C40" t="str">
-        <v>1122</v>
+        <v>970</v>
       </c>
       <c r="D40" t="str">
-        <v>Farida bai Juzer bhai Gyori</v>
+        <v>Farida bai Khuzaima bhai Obri</v>
       </c>
       <c r="E40" t="str">
-        <v>30367320</v>
+        <v>30367525</v>
       </c>
       <c r="F40" t="str">
         <v>Pending</v>
@@ -1429,19 +1420,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>1778659312652_152</v>
+        <v>1778659312652_153</v>
       </c>
       <c r="B41" t="str">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C41" t="str">
-        <v>970</v>
+        <v>1336</v>
       </c>
       <c r="D41" t="str">
-        <v>Farida bai Khuzaima bhai Obri</v>
+        <v>Farida bai Mohammed bhai Maudiwala</v>
       </c>
       <c r="E41" t="str">
-        <v>30367525</v>
+        <v>30367788</v>
       </c>
       <c r="F41" t="str">
         <v>Pending</v>
@@ -1452,132 +1443,132 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>1778659312652_153</v>
+        <v>1778659312652_391</v>
       </c>
       <c r="B42" t="str">
-        <v>154</v>
+        <v>392</v>
       </c>
       <c r="C42" t="str">
-        <v>1336</v>
+        <v>1055</v>
       </c>
       <c r="D42" t="str">
-        <v>Farida bai Mohammed bhai Maudiwala</v>
+        <v>Mulla Husain bhai Jivaji bhai Pachlasa</v>
       </c>
       <c r="E42" t="str">
-        <v>30367788</v>
+        <v>20318738</v>
       </c>
       <c r="F42" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G42" t="str">
         <v/>
+      </c>
+      <c r="H42" t="str">
+        <v>22/05/2026</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="J42" t="str">
+        <v>11:46:17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>1778659312652_391</v>
+        <v>1778659312652_155</v>
       </c>
       <c r="B43" t="str">
-        <v>392</v>
+        <v>156</v>
       </c>
       <c r="C43" t="str">
-        <v>1055</v>
+        <v>1317</v>
       </c>
       <c r="D43" t="str">
-        <v>Mulla Husain bhai Jivaji bhai Pachlasa</v>
+        <v>Farida bai Mufaddal bhai Peeth</v>
       </c>
       <c r="E43" t="str">
-        <v>20318738</v>
+        <v>30360229</v>
       </c>
       <c r="F43" t="str">
         <v>Given</v>
       </c>
       <c r="G43" t="str">
-        <v/>
-      </c>
-      <c r="H43" t="str">
-        <v>22/05/2026</v>
-      </c>
-      <c r="I43" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J43" t="str">
-        <v>11:46:17</v>
+        <v>shkh fakhruddin badi</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>1778659312652_155</v>
+        <v>1778659312652_156</v>
       </c>
       <c r="B44" t="str">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C44" t="str">
-        <v>1317</v>
+        <v>1021</v>
       </c>
       <c r="D44" t="str">
-        <v>Farida bai Mufaddal bhai Peeth</v>
+        <v>Farida bai Munavar bhai Baroda</v>
       </c>
       <c r="E44" t="str">
-        <v>30360229</v>
+        <v>30368232</v>
       </c>
       <c r="F44" t="str">
         <v>Given</v>
       </c>
       <c r="G44" t="str">
-        <v>shkh fakhruddin badi</v>
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>19/05/2026</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="J44" t="str">
+        <v>12:01:13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>1778659312652_156</v>
+        <v>1778659312652_157</v>
       </c>
       <c r="B45" t="str">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C45" t="str">
-        <v>1021</v>
+        <v>1391</v>
       </c>
       <c r="D45" t="str">
-        <v>Farida bai Munavar bhai Baroda</v>
+        <v>Farzana bai Aliasgar bhai Mulla</v>
       </c>
       <c r="E45" t="str">
-        <v>30368232</v>
+        <v>30368283</v>
       </c>
       <c r="F45" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G45" t="str">
         <v/>
-      </c>
-      <c r="H45" t="str">
-        <v>19/05/2026</v>
-      </c>
-      <c r="I45" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="J45" t="str">
-        <v>12:01:13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>1778659312652_157</v>
+        <v>1778659312652_158</v>
       </c>
       <c r="B46" t="str">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C46" t="str">
-        <v>1391</v>
+        <v>411</v>
       </c>
       <c r="D46" t="str">
-        <v>Farzana bai Aliasgar bhai Mulla</v>
+        <v>Fatema bai Abbas bhai Badshah</v>
       </c>
       <c r="E46" t="str">
-        <v>30368283</v>
+        <v>30366810</v>
       </c>
       <c r="F46" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -1585,22 +1576,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>1778659312652_158</v>
+        <v>1778659312652_15</v>
       </c>
       <c r="B47" t="str">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="C47" t="str">
-        <v>411</v>
+        <v>129</v>
       </c>
       <c r="D47" t="str">
-        <v>Fatema bai Abbas bhai Badshah</v>
+        <v>Abdulhusain bhai Ahmedali bhai Pachalasa</v>
       </c>
       <c r="E47" t="str">
-        <v>30366810</v>
+        <v>20318101</v>
       </c>
       <c r="F47" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -1608,19 +1599,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>1778659312652_15</v>
+        <v>1778659312652_360</v>
       </c>
       <c r="B48" t="str">
-        <v>16</v>
+        <v>361</v>
       </c>
       <c r="C48" t="str">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="D48" t="str">
-        <v>Abdulhusain bhai Ahmedali bhai Pachalasa</v>
+        <v>Mohammadhussain bhai Abdeali bhai Hamed (godichand)</v>
       </c>
       <c r="E48" t="str">
-        <v>20318101</v>
+        <v>20318014</v>
       </c>
       <c r="F48" t="str">
         <v>Pending</v>
@@ -1631,65 +1622,65 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>1778659312652_360</v>
+        <v>1778659312652_362</v>
       </c>
       <c r="B49" t="str">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C49" t="str">
-        <v>239</v>
+        <v>37</v>
       </c>
       <c r="D49" t="str">
-        <v>Mohammadhussain bhai Abdeali bhai Hamed (godichand)</v>
+        <v>Mohammed bhai Abbas bhai Daru</v>
       </c>
       <c r="E49" t="str">
-        <v>20318014</v>
+        <v>20318034</v>
       </c>
       <c r="F49" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G49" t="str">
-        <v/>
+        <v>Zainab ben Khandi</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>1778659312652_362</v>
+        <v>1778659312652_363</v>
       </c>
       <c r="B50" t="str">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C50" t="str">
-        <v>37</v>
+        <v>417</v>
       </c>
       <c r="D50" t="str">
-        <v>Mohammed bhai Abbas bhai Daru</v>
+        <v>Mohammed bhai Abbas bhai Sukhsar</v>
       </c>
       <c r="E50" t="str">
-        <v>20318034</v>
+        <v>20387135</v>
       </c>
       <c r="F50" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G50" t="str">
-        <v>Zainab ben Khandi</v>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>1778659312652_363</v>
+        <v>1778659312652_393</v>
       </c>
       <c r="B51" t="str">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="C51" t="str">
-        <v>417</v>
+        <v>251</v>
       </c>
       <c r="D51" t="str">
-        <v>Mohammed bhai Abbas bhai Sukhsar</v>
+        <v>Mulla Husain bhai Mustansir bhai Ramakda</v>
       </c>
       <c r="E51" t="str">
-        <v>20387135</v>
+        <v>30360243</v>
       </c>
       <c r="F51" t="str">
         <v>Pending</v>
@@ -1700,22 +1691,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>1778659312652_393</v>
+        <v>1778659312652_475</v>
       </c>
       <c r="B52" t="str">
-        <v>394</v>
+        <v>476</v>
       </c>
       <c r="C52" t="str">
-        <v>251</v>
+        <v>662</v>
       </c>
       <c r="D52" t="str">
-        <v>Mulla Husain bhai Mustansir bhai Ramakda</v>
+        <v>Rashida bai Taher bhai Goonjwala</v>
       </c>
       <c r="E52" t="str">
-        <v>30360243</v>
+        <v>30367211</v>
       </c>
       <c r="F52" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -1723,22 +1714,22 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>1778659312652_475</v>
+        <v>1778659312652_476</v>
       </c>
       <c r="B53" t="str">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C53" t="str">
-        <v>662</v>
+        <v>44</v>
       </c>
       <c r="D53" t="str">
-        <v>Rashida bai Taher bhai Goonjwala</v>
+        <v>Razia bai Mansoor bhai Kabriwala</v>
       </c>
       <c r="E53" t="str">
-        <v>30367211</v>
+        <v>30360297</v>
       </c>
       <c r="F53" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -1746,25 +1737,34 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>1778659312652_476</v>
+        <v>1778659312652_154</v>
       </c>
       <c r="B54" t="str">
-        <v>477</v>
+        <v>155</v>
       </c>
       <c r="C54" t="str">
-        <v>44</v>
+        <v>1339</v>
       </c>
       <c r="D54" t="str">
-        <v>Razia bai Mansoor bhai Kabriwala</v>
+        <v>Farida bai Mohammedhusain bhai Kothari</v>
       </c>
       <c r="E54" t="str">
-        <v>30360297</v>
+        <v>30367383</v>
       </c>
       <c r="F54" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G54" t="str">
-        <v/>
+        <v>Ilyas</v>
+      </c>
+      <c r="H54" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J54" t="str">
+        <v>03:09:19</v>
       </c>
     </row>
     <row r="55">
@@ -7042,7 +7042,16 @@
         <v>Given</v>
       </c>
       <c r="G260" t="str">
-        <v/>
+        <v>Ilyas</v>
+      </c>
+      <c r="H260" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I260" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J260" t="str">
+        <v>03:31:23</v>
       </c>
     </row>
     <row r="261">

--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -667,19 +667,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1778659312652_121</v>
+        <v>1778659312652_122</v>
       </c>
       <c r="B11" t="str">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C11" t="str">
-        <v>750</v>
+        <v>1238</v>
       </c>
       <c r="D11" t="str">
-        <v>Fakhruddin bhai Abbas bhai Shujai</v>
+        <v>Fakhruddin bhai Abbasali bhai Hathi</v>
       </c>
       <c r="E11" t="str">
-        <v>20387715</v>
+        <v>20414145</v>
       </c>
       <c r="F11" t="str">
         <v>Pending</v>
@@ -690,19 +690,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1778659312652_122</v>
+        <v>1778659312652_123</v>
       </c>
       <c r="B12" t="str">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C12" t="str">
-        <v>1238</v>
+        <v>34</v>
       </c>
       <c r="D12" t="str">
-        <v>Fakhruddin bhai Abbasali bhai Hathi</v>
+        <v>Fakhruddin bhai Ahmedali bhai Obri</v>
       </c>
       <c r="E12" t="str">
-        <v>20414145</v>
+        <v>20318032</v>
       </c>
       <c r="F12" t="str">
         <v>Pending</v>
@@ -713,25 +713,34 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1778659312652_123</v>
+        <v>1778659312652_121</v>
       </c>
       <c r="B13" t="str">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C13" t="str">
-        <v>34</v>
+        <v>750</v>
       </c>
       <c r="D13" t="str">
-        <v>Fakhruddin bhai Ahmedali bhai Obri</v>
+        <v>Fakhruddin bhai Abbas bhai Shujai</v>
       </c>
       <c r="E13" t="str">
-        <v>20318032</v>
+        <v>20387715</v>
       </c>
       <c r="F13" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>Abdeali shujai</v>
+      </c>
+      <c r="H13" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J13" t="str">
+        <v>12:15:38</v>
       </c>
     </row>
     <row r="14">
@@ -1645,19 +1654,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>1778659312652_363</v>
+        <v>1778659312652_393</v>
       </c>
       <c r="B50" t="str">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="C50" t="str">
-        <v>417</v>
+        <v>251</v>
       </c>
       <c r="D50" t="str">
-        <v>Mohammed bhai Abbas bhai Sukhsar</v>
+        <v>Mulla Husain bhai Mustansir bhai Ramakda</v>
       </c>
       <c r="E50" t="str">
-        <v>20387135</v>
+        <v>30360243</v>
       </c>
       <c r="F50" t="str">
         <v>Pending</v>
@@ -1668,22 +1677,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>1778659312652_393</v>
+        <v>1778659312652_475</v>
       </c>
       <c r="B51" t="str">
-        <v>394</v>
+        <v>476</v>
       </c>
       <c r="C51" t="str">
-        <v>251</v>
+        <v>662</v>
       </c>
       <c r="D51" t="str">
-        <v>Mulla Husain bhai Mustansir bhai Ramakda</v>
+        <v>Rashida bai Taher bhai Goonjwala</v>
       </c>
       <c r="E51" t="str">
-        <v>30360243</v>
+        <v>30367211</v>
       </c>
       <c r="F51" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -1691,22 +1700,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>1778659312652_475</v>
+        <v>1778659312652_476</v>
       </c>
       <c r="B52" t="str">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C52" t="str">
-        <v>662</v>
+        <v>44</v>
       </c>
       <c r="D52" t="str">
-        <v>Rashida bai Taher bhai Goonjwala</v>
+        <v>Razia bai Mansoor bhai Kabriwala</v>
       </c>
       <c r="E52" t="str">
-        <v>30367211</v>
+        <v>30360297</v>
       </c>
       <c r="F52" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -1714,48 +1723,57 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>1778659312652_476</v>
+        <v>1778659312652_154</v>
       </c>
       <c r="B53" t="str">
-        <v>477</v>
+        <v>155</v>
       </c>
       <c r="C53" t="str">
-        <v>44</v>
+        <v>1339</v>
       </c>
       <c r="D53" t="str">
-        <v>Razia bai Mansoor bhai Kabriwala</v>
+        <v>Farida bai Mohammedhusain bhai Kothari</v>
       </c>
       <c r="E53" t="str">
-        <v>30360297</v>
+        <v>30367383</v>
       </c>
       <c r="F53" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G53" t="str">
-        <v/>
+        <v>Ilyas</v>
+      </c>
+      <c r="H53" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J53" t="str">
+        <v>03:09:19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>1778659312652_154</v>
+        <v>1778659312652_363</v>
       </c>
       <c r="B54" t="str">
-        <v>155</v>
+        <v>364</v>
       </c>
       <c r="C54" t="str">
-        <v>1339</v>
+        <v>417</v>
       </c>
       <c r="D54" t="str">
-        <v>Farida bai Mohammedhusain bhai Kothari</v>
+        <v>Mohammed bhai Abbas bhai Sukhsar</v>
       </c>
       <c r="E54" t="str">
-        <v>30367383</v>
+        <v>20387135</v>
       </c>
       <c r="F54" t="str">
         <v>Given</v>
       </c>
       <c r="G54" t="str">
-        <v>Ilyas</v>
+        <v/>
       </c>
       <c r="H54" t="str">
         <v>25/05/2026</v>
@@ -1764,7 +1782,7 @@
         <v>Monday</v>
       </c>
       <c r="J54" t="str">
-        <v>03:09:19</v>
+        <v>11:09:13</v>
       </c>
     </row>
     <row r="55">
@@ -1870,83 +1888,83 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>1778659312652_257</v>
+        <v>1778659312652_262</v>
       </c>
       <c r="B59" t="str">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C59" t="str">
-        <v>1049</v>
+        <v>1418</v>
       </c>
       <c r="D59" t="str">
-        <v>Hameda bai Abbas bhai Mukaddam</v>
+        <v>Hatim bhai Mansoorali bhai Gadi</v>
       </c>
       <c r="E59" t="str">
-        <v>20318616</v>
+        <v>20376598</v>
       </c>
       <c r="F59" t="str">
         <v>Given</v>
       </c>
       <c r="G59" t="str">
-        <v>Aliasgar bhai Mulla</v>
+        <v/>
       </c>
       <c r="H59" t="str">
-        <v>19/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="I59" t="str">
-        <v>Tuesday</v>
+        <v>Monday</v>
       </c>
       <c r="J59" t="str">
-        <v>11:35:06</v>
+        <v>11:13:34</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>1778659312652_272</v>
+        <v>1778659312652_257</v>
       </c>
       <c r="B60" t="str">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="C60" t="str">
-        <v>1268</v>
+        <v>1049</v>
       </c>
       <c r="D60" t="str">
-        <v>Husain bhai Fakhruddin bhai Fata</v>
+        <v>Hameda bai Abbas bhai Mukaddam</v>
       </c>
       <c r="E60" t="str">
-        <v>30366541</v>
+        <v>20318616</v>
       </c>
       <c r="F60" t="str">
         <v>Given</v>
       </c>
       <c r="G60" t="str">
-        <v/>
+        <v>Aliasgar bhai Mulla</v>
       </c>
       <c r="H60" t="str">
-        <v>22/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="I60" t="str">
-        <v>Friday</v>
+        <v>Tuesday</v>
       </c>
       <c r="J60" t="str">
-        <v>12:05:47</v>
+        <v>11:35:06</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>1778659312652_279</v>
+        <v>1778659312652_272</v>
       </c>
       <c r="B61" t="str">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C61" t="str">
-        <v>1006</v>
+        <v>1268</v>
       </c>
       <c r="D61" t="str">
-        <v>Husain bhai Saifuddin bhai Husami</v>
+        <v>Husain bhai Fakhruddin bhai Fata</v>
       </c>
       <c r="E61" t="str">
-        <v>20318656</v>
+        <v>30366541</v>
       </c>
       <c r="F61" t="str">
         <v>Given</v>
@@ -1955,36 +1973,36 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>23/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="I61" t="str">
-        <v>Saturday</v>
+        <v>Friday</v>
       </c>
       <c r="J61" t="str">
-        <v>10:44:57</v>
+        <v>12:05:47</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>1778659312652_18</v>
+        <v>1778659312652_279</v>
       </c>
       <c r="B62" t="str">
-        <v>19</v>
+        <v>280</v>
       </c>
       <c r="C62" t="str">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="D62" t="str">
-        <v>Ahmedali bhai Mulla Yaqubali bhai Peethwala</v>
+        <v>Husain bhai Saifuddin bhai Husami</v>
       </c>
       <c r="E62" t="str">
-        <v>20348013</v>
+        <v>20318656</v>
       </c>
       <c r="F62" t="str">
         <v>Given</v>
       </c>
       <c r="G62" t="str">
-        <v>shkh fakhruddin badi</v>
+        <v/>
       </c>
       <c r="H62" t="str">
         <v>23/05/2026</v>
@@ -1993,47 +2011,56 @@
         <v>Saturday</v>
       </c>
       <c r="J62" t="str">
-        <v>10:59:13</v>
+        <v>10:44:57</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>1778659312652_258</v>
+        <v>1778659312652_273</v>
       </c>
       <c r="B63" t="str">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="C63" t="str">
-        <v>791</v>
+        <v>883</v>
       </c>
       <c r="D63" t="str">
-        <v>Hameda bai Husain bhai Kikawala</v>
+        <v>Husain bhai Fakhruddin bhai Jogpurwala</v>
       </c>
       <c r="E63" t="str">
-        <v>30367462</v>
+        <v>20406066</v>
       </c>
       <c r="F63" t="str">
         <v>Given</v>
       </c>
       <c r="G63" t="str">
         <v/>
+      </c>
+      <c r="H63" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J63" t="str">
+        <v>11:17:29</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>1778659312652_25</v>
+        <v>1778659312652_18</v>
       </c>
       <c r="B64" t="str">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C64" t="str">
-        <v>905</v>
+        <v>23</v>
       </c>
       <c r="D64" t="str">
-        <v>Ajab bai Husain bhai Obriwala</v>
+        <v>Ahmedali bhai Mulla Yaqubali bhai Peethwala</v>
       </c>
       <c r="E64" t="str">
-        <v>30367685</v>
+        <v>20348013</v>
       </c>
       <c r="F64" t="str">
         <v>Given</v>
@@ -2041,100 +2068,109 @@
       <c r="G64" t="str">
         <v>shkh fakhruddin badi</v>
       </c>
+      <c r="H64" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J64" t="str">
+        <v>10:59:13</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>1778659312652_259</v>
+        <v>1778659312652_258</v>
       </c>
       <c r="B65" t="str">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C65" t="str">
-        <v>723</v>
+        <v>791</v>
       </c>
       <c r="D65" t="str">
-        <v>Haseena bai Abbas bhai Daliwala</v>
+        <v>Hameda bai Husain bhai Kikawala</v>
       </c>
       <c r="E65" t="str">
-        <v>30367315</v>
+        <v>30367462</v>
       </c>
       <c r="F65" t="str">
         <v>Given</v>
       </c>
       <c r="G65" t="str">
-        <v>Lamiya ben ratawala</v>
-      </c>
-      <c r="H65" t="str">
-        <v>16/05/2026</v>
-      </c>
-      <c r="I65" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="J65" t="str">
-        <v>10:33:16</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>1778659312652_260</v>
+        <v>1778659312652_25</v>
       </c>
       <c r="B66" t="str">
-        <v>261</v>
+        <v>26</v>
       </c>
       <c r="C66" t="str">
-        <v>1305</v>
+        <v>905</v>
       </c>
       <c r="D66" t="str">
-        <v>Haseena bai Ahmedali bhai Baroda</v>
+        <v>Ajab bai Husain bhai Obriwala</v>
       </c>
       <c r="E66" t="str">
-        <v>30367593</v>
+        <v>30367685</v>
       </c>
       <c r="F66" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G66" t="str">
-        <v/>
+        <v>shkh fakhruddin badi</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>1778659312652_262</v>
+        <v>1778659312652_259</v>
       </c>
       <c r="B67" t="str">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C67" t="str">
-        <v>1418</v>
+        <v>723</v>
       </c>
       <c r="D67" t="str">
-        <v>Hatim bhai Mansoorali bhai Gadi</v>
+        <v>Haseena bai Abbas bhai Daliwala</v>
       </c>
       <c r="E67" t="str">
-        <v>20376598</v>
+        <v>30367315</v>
       </c>
       <c r="F67" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G67" t="str">
-        <v/>
+        <v>Lamiya ben ratawala</v>
+      </c>
+      <c r="H67" t="str">
+        <v>16/05/2026</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J67" t="str">
+        <v>10:33:16</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>1778659312652_263</v>
+        <v>1778659312652_260</v>
       </c>
       <c r="B68" t="str">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C68" t="str">
-        <v>951</v>
+        <v>1305</v>
       </c>
       <c r="D68" t="str">
-        <v>Hatim bhai Taiyebali bhai Warda</v>
+        <v>Haseena bai Ahmedali bhai Baroda</v>
       </c>
       <c r="E68" t="str">
-        <v>20402148</v>
+        <v>30367593</v>
       </c>
       <c r="F68" t="str">
         <v>Pending</v>
@@ -2145,19 +2181,19 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>1778659312652_264</v>
+        <v>1778659312652_263</v>
       </c>
       <c r="B69" t="str">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C69" t="str">
-        <v>854</v>
+        <v>951</v>
       </c>
       <c r="D69" t="str">
-        <v>Husain bhai Abdeali bhai Baroda</v>
+        <v>Hatim bhai Taiyebali bhai Warda</v>
       </c>
       <c r="E69" t="str">
-        <v>20318542</v>
+        <v>20402148</v>
       </c>
       <c r="F69" t="str">
         <v>Pending</v>
@@ -2168,19 +2204,19 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>1778659312652_271</v>
+        <v>1778659312652_264</v>
       </c>
       <c r="B70" t="str">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C70" t="str">
-        <v>1159</v>
+        <v>854</v>
       </c>
       <c r="D70" t="str">
-        <v>Husain bhai Asgarali bhai Rampur</v>
+        <v>Husain bhai Abdeali bhai Baroda</v>
       </c>
       <c r="E70" t="str">
-        <v>20434568</v>
+        <v>20318542</v>
       </c>
       <c r="F70" t="str">
         <v>Pending</v>
@@ -2191,19 +2227,19 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>1778659312652_273</v>
+        <v>1778659312652_271</v>
       </c>
       <c r="B71" t="str">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C71" t="str">
-        <v>883</v>
+        <v>1159</v>
       </c>
       <c r="D71" t="str">
-        <v>Husain bhai Fakhruddin bhai Jogpurwala</v>
+        <v>Husain bhai Asgarali bhai Rampur</v>
       </c>
       <c r="E71" t="str">
-        <v>20406066</v>
+        <v>20434568</v>
       </c>
       <c r="F71" t="str">
         <v>Pending</v>
@@ -2535,57 +2571,57 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>1778659312652_294</v>
+        <v>1778659312652_291</v>
       </c>
       <c r="B84" t="str">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C84" t="str">
-        <v>1425</v>
+        <v>1211</v>
       </c>
       <c r="D84" t="str">
-        <v>Husaina bai Mohammed bhai Ammarrgi</v>
+        <v>Husaina bai Husain bhai Ajmerwala</v>
       </c>
       <c r="E84" t="str">
-        <v>30366501</v>
+        <v>30368037</v>
       </c>
       <c r="F84" t="str">
         <v>Given</v>
       </c>
       <c r="G84" t="str">
-        <v>Mariya ben peeth</v>
+        <v>Sakina ben kotwal</v>
       </c>
       <c r="H84" t="str">
-        <v>22/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="I84" t="str">
-        <v>Friday</v>
+        <v>Monday</v>
       </c>
       <c r="J84" t="str">
-        <v>11:14:43</v>
+        <v>11:25:43</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>1778659312652_352</v>
+        <v>1778659312652_294</v>
       </c>
       <c r="B85" t="str">
-        <v>353</v>
+        <v>295</v>
       </c>
       <c r="C85" t="str">
-        <v>217</v>
+        <v>1425</v>
       </c>
       <c r="D85" t="str">
-        <v>Maryam bai Fakhruddin bhai Peethwala</v>
+        <v>Husaina bai Mohammed bhai Ammarrgi</v>
       </c>
       <c r="E85" t="str">
-        <v>30368184</v>
+        <v>30366501</v>
       </c>
       <c r="F85" t="str">
         <v>Given</v>
       </c>
       <c r="G85" t="str">
-        <v/>
+        <v>Mariya ben peeth</v>
       </c>
       <c r="H85" t="str">
         <v>22/05/2026</v>
@@ -2594,102 +2630,111 @@
         <v>Friday</v>
       </c>
       <c r="J85" t="str">
-        <v>11:36:25</v>
+        <v>11:14:43</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>1778659312652_285</v>
+        <v>1778659312652_352</v>
       </c>
       <c r="B86" t="str">
-        <v>286</v>
+        <v>353</v>
       </c>
       <c r="C86" t="str">
-        <v>57</v>
+        <v>217</v>
       </c>
       <c r="D86" t="str">
-        <v>Husaina bai Baqir bhai Lukmani</v>
+        <v>Maryam bai Fakhruddin bhai Peethwala</v>
       </c>
       <c r="E86" t="str">
-        <v>30360194</v>
+        <v>30368184</v>
       </c>
       <c r="F86" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G86" t="str">
         <v/>
+      </c>
+      <c r="H86" t="str">
+        <v>22/05/2026</v>
+      </c>
+      <c r="I86" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="J86" t="str">
+        <v>11:36:25</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>1778659312652_293</v>
+        <v>1778659312652_285</v>
       </c>
       <c r="B87" t="str">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C87" t="str">
-        <v>1363</v>
+        <v>57</v>
       </c>
       <c r="D87" t="str">
-        <v>Husaina bai Husain bhai Khanji</v>
+        <v>Husaina bai Baqir bhai Lukmani</v>
       </c>
       <c r="E87" t="str">
-        <v>20318341</v>
+        <v>30360194</v>
       </c>
       <c r="F87" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G87" t="str">
-        <v>Aliasgar bhai Mulla</v>
-      </c>
-      <c r="H87" t="str">
-        <v>23/05/2026</v>
-      </c>
-      <c r="I87" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="J87" t="str">
-        <v>11:38:05</v>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>1778659312652_286</v>
+        <v>1778659312652_293</v>
       </c>
       <c r="B88" t="str">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C88" t="str">
-        <v>405</v>
+        <v>1363</v>
       </c>
       <c r="D88" t="str">
-        <v>Husaina bai Baqirali bhai Peethwala</v>
+        <v>Husaina bai Husain bhai Khanji</v>
       </c>
       <c r="E88" t="str">
-        <v>60446480</v>
+        <v>20318341</v>
       </c>
       <c r="F88" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G88" t="str">
-        <v/>
+        <v>Aliasgar bhai Mulla</v>
+      </c>
+      <c r="H88" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I88" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J88" t="str">
+        <v>11:38:05</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>1778659312652_287</v>
+        <v>1778659312652_286</v>
       </c>
       <c r="B89" t="str">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C89" t="str">
-        <v>1089</v>
+        <v>405</v>
       </c>
       <c r="D89" t="str">
-        <v>Husaina bai Enayat bhai Gunj</v>
+        <v>Husaina bai Baqirali bhai Peethwala</v>
       </c>
       <c r="E89" t="str">
-        <v>20318649</v>
+        <v>60446480</v>
       </c>
       <c r="F89" t="str">
         <v>Pending</v>
@@ -2700,19 +2745,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>1778659312652_288</v>
+        <v>1778659312652_287</v>
       </c>
       <c r="B90" t="str">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C90" t="str">
-        <v>1342</v>
+        <v>1089</v>
       </c>
       <c r="D90" t="str">
-        <v>Husaina bai Fakhruddin bhai Damriwala</v>
+        <v>Husaina bai Enayat bhai Gunj</v>
       </c>
       <c r="E90" t="str">
-        <v>60446035</v>
+        <v>20318649</v>
       </c>
       <c r="F90" t="str">
         <v>Pending</v>
@@ -2723,19 +2768,19 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>1778659312652_28</v>
+        <v>1778659312652_288</v>
       </c>
       <c r="B91" t="str">
-        <v>29</v>
+        <v>289</v>
       </c>
       <c r="C91" t="str">
-        <v>149</v>
+        <v>1342</v>
       </c>
       <c r="D91" t="str">
-        <v>Ajab bai Khuzaima bhai Shaikhadam</v>
+        <v>Husaina bai Fakhruddin bhai Damriwala</v>
       </c>
       <c r="E91" t="str">
-        <v>20374118</v>
+        <v>60446035</v>
       </c>
       <c r="F91" t="str">
         <v>Pending</v>
@@ -2746,19 +2791,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>1778659312652_289</v>
+        <v>1778659312652_28</v>
       </c>
       <c r="B92" t="str">
-        <v>290</v>
+        <v>29</v>
       </c>
       <c r="C92" t="str">
-        <v>486</v>
+        <v>149</v>
       </c>
       <c r="D92" t="str">
-        <v>Husaina bai Fakhruddin bhai Peethwala</v>
+        <v>Ajab bai Khuzaima bhai Shaikhadam</v>
       </c>
       <c r="E92" t="str">
-        <v>30366894</v>
+        <v>20374118</v>
       </c>
       <c r="F92" t="str">
         <v>Pending</v>
@@ -2769,48 +2814,48 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>1778659312652_290</v>
+        <v>1778659312652_289</v>
       </c>
       <c r="B93" t="str">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C93" t="str">
-        <v>45</v>
+        <v>486</v>
       </c>
       <c r="D93" t="str">
-        <v>Husaina bai Hashim bhai Sagir</v>
+        <v>Husaina bai Fakhruddin bhai Peethwala</v>
       </c>
       <c r="E93" t="str">
-        <v>20318759</v>
+        <v>30366894</v>
       </c>
       <c r="F93" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G93" t="str">
-        <v>Aliasgar bhai varda</v>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>1778659312652_291</v>
+        <v>1778659312652_290</v>
       </c>
       <c r="B94" t="str">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C94" t="str">
-        <v>1211</v>
+        <v>45</v>
       </c>
       <c r="D94" t="str">
-        <v>Husaina bai Husain bhai Ajmerwala</v>
+        <v>Husaina bai Hashim bhai Sagir</v>
       </c>
       <c r="E94" t="str">
-        <v>30368037</v>
+        <v>20318759</v>
       </c>
       <c r="F94" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G94" t="str">
-        <v/>
+        <v>Aliasgar bhai varda</v>
       </c>
     </row>
     <row r="95">
@@ -3214,42 +3259,51 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>1778659312652_394</v>
+        <v>1778659312652_398</v>
       </c>
       <c r="B110" t="str">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C110" t="str">
-        <v/>
+        <v>186</v>
       </c>
       <c r="D110" t="str">
-        <v>Mulla Murtaza bhai Shaikh Fakhruddin bhai Bhanpurawala</v>
+        <v>Mulla Shabbirhusain bhai Alihusain bhai Mushala</v>
       </c>
       <c r="E110" t="str">
-        <v>40475784</v>
+        <v>20352226</v>
       </c>
       <c r="F110" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>Fatema ben Mulla Hakimuddin bhai sageer</v>
+      </c>
+      <c r="H110" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I110" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J110" t="str">
+        <v>10:53:51</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>1778659312652_395</v>
+        <v>1778659312652_394</v>
       </c>
       <c r="B111" t="str">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C111" t="str">
-        <v>1109</v>
+        <v/>
       </c>
       <c r="D111" t="str">
-        <v>Mulla Qutbuddin bhai Ismail bhai Argenwala</v>
+        <v>Mulla Murtaza bhai Shaikh Fakhruddin bhai Bhanpurawala</v>
       </c>
       <c r="E111" t="str">
-        <v>20387948</v>
+        <v>40475784</v>
       </c>
       <c r="F111" t="str">
         <v>Pending</v>
@@ -3260,22 +3314,22 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>1778659312652_396</v>
+        <v>1778659312652_395</v>
       </c>
       <c r="B112" t="str">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C112" t="str">
-        <v>181</v>
+        <v>1109</v>
       </c>
       <c r="D112" t="str">
-        <v>Mulla Qutbuddin bhai Mulla Abdullah bhai Gaba</v>
+        <v>Mulla Qutbuddin bhai Ismail bhai Argenwala</v>
       </c>
       <c r="E112" t="str">
-        <v>20348483</v>
+        <v>20387948</v>
       </c>
       <c r="F112" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -3283,22 +3337,22 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>1778659312652_397</v>
+        <v>1778659312652_396</v>
       </c>
       <c r="B113" t="str">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C113" t="str">
-        <v>464</v>
+        <v>181</v>
       </c>
       <c r="D113" t="str">
-        <v>Mulla Saifuddin bhai Shaikh Ibrahim bhai Electric</v>
+        <v>Mulla Qutbuddin bhai Mulla Abdullah bhai Gaba</v>
       </c>
       <c r="E113" t="str">
-        <v>30366865</v>
+        <v>20348483</v>
       </c>
       <c r="F113" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -3306,19 +3360,19 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>1778659312652_398</v>
+        <v>1778659312652_397</v>
       </c>
       <c r="B114" t="str">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C114" t="str">
-        <v>186</v>
+        <v>464</v>
       </c>
       <c r="D114" t="str">
-        <v>Mulla Shabbirhusain bhai Alihusain bhai Mushala</v>
+        <v>Mulla Saifuddin bhai Shaikh Ibrahim bhai Electric</v>
       </c>
       <c r="E114" t="str">
-        <v>20352226</v>
+        <v>30366865</v>
       </c>
       <c r="F114" t="str">
         <v>Pending</v>
@@ -3485,19 +3539,19 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>1778659312652_611</v>
+        <v>1778659312652_612</v>
       </c>
       <c r="B121" t="str">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C121" t="str">
-        <v>1069</v>
+        <v>20408101</v>
       </c>
       <c r="D121" t="str">
-        <v>Shaikh Fakhruddin bhai Ishaq bhai Doodh</v>
+        <v>Shaikh Fakhruddin bhai Mulla Adamali bhai Bhanpurwala</v>
       </c>
       <c r="E121" t="str">
-        <v>20318610</v>
+        <v>20408101</v>
       </c>
       <c r="F121" t="str">
         <v>Pending</v>
@@ -3508,88 +3562,88 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>1778659312652_612</v>
+        <v>1778659312652_613</v>
       </c>
       <c r="B122" t="str">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C122" t="str">
-        <v>20408101</v>
+        <v>574</v>
       </c>
       <c r="D122" t="str">
-        <v>Shaikh Fakhruddin bhai Mulla Adamali bhai Bhanpurwala</v>
+        <v>Shaikh Fakhruddin bhai Qurbanhusain bhai Khedapa</v>
       </c>
       <c r="E122" t="str">
-        <v>20408101</v>
+        <v>20348014</v>
       </c>
       <c r="F122" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G122" t="str">
-        <v/>
+        <v>Given in Masjid</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>1778659312652_613</v>
+        <v>1778659312652_615</v>
       </c>
       <c r="B123" t="str">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C123" t="str">
-        <v>574</v>
+        <v>802</v>
       </c>
       <c r="D123" t="str">
-        <v>Shaikh Fakhruddin bhai Qurbanhusain bhai Khedapa</v>
+        <v>Shaikh Fakhruddin bhai Taherali bhai Giyori</v>
       </c>
       <c r="E123" t="str">
-        <v>20348014</v>
+        <v>20318506</v>
       </c>
       <c r="F123" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G123" t="str">
-        <v>Given in Masjid</v>
+        <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>1778659312652_615</v>
+        <v>1778659312652_630</v>
       </c>
       <c r="B124" t="str">
-        <v>616</v>
+        <v>631</v>
       </c>
       <c r="C124" t="str">
-        <v>802</v>
+        <v>596</v>
       </c>
       <c r="D124" t="str">
-        <v>Shaikh Fakhruddin bhai Taherali bhai Giyori</v>
+        <v>Shaikh Qasim bhai Ahmedali bhai Saroda</v>
       </c>
       <c r="E124" t="str">
-        <v>20318506</v>
+        <v>20437983</v>
       </c>
       <c r="F124" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G124" t="str">
-        <v/>
+        <v>Given in Masjid</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>1778659312652_630</v>
+        <v>1778659312652_631</v>
       </c>
       <c r="B125" t="str">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C125" t="str">
-        <v>596</v>
+        <v>1176</v>
       </c>
       <c r="D125" t="str">
-        <v>Shaikh Qasim bhai Ahmedali bhai Saroda</v>
+        <v>Shaikh Quaidjohar bhai Shaikh Taiyeb bhai Husami</v>
       </c>
       <c r="E125" t="str">
-        <v>20437983</v>
+        <v>20358979</v>
       </c>
       <c r="F125" t="str">
         <v>Given</v>
@@ -3600,48 +3654,57 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>1778659312652_631</v>
+        <v>1778659312652_632</v>
       </c>
       <c r="B126" t="str">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C126" t="str">
-        <v>1176</v>
+        <v>367</v>
       </c>
       <c r="D126" t="str">
-        <v>Shaikh Quaidjohar bhai Shaikh Taiyeb bhai Husami</v>
+        <v>Shaikh Qutbuddin bhai Alihusain bhai Peeth</v>
       </c>
       <c r="E126" t="str">
-        <v>20358979</v>
+        <v>20318217</v>
       </c>
       <c r="F126" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G126" t="str">
-        <v>Given in Masjid</v>
+        <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>1778659312652_632</v>
+        <v>1778659312652_611</v>
       </c>
       <c r="B127" t="str">
-        <v>633</v>
+        <v>612</v>
       </c>
       <c r="C127" t="str">
-        <v>367</v>
+        <v>1069</v>
       </c>
       <c r="D127" t="str">
-        <v>Shaikh Qutbuddin bhai Alihusain bhai Peeth</v>
+        <v>Shaikh Fakhruddin bhai Ishaq bhai Doodh</v>
       </c>
       <c r="E127" t="str">
-        <v>20318217</v>
+        <v>20318610</v>
       </c>
       <c r="F127" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G127" t="str">
-        <v/>
+        <v>Aziz bhai Jaan</v>
+      </c>
+      <c r="H127" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I127" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J127" t="str">
+        <v>10:56:01</v>
       </c>
     </row>
     <row r="128">
@@ -3738,176 +3801,176 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>1778659312652_695</v>
+        <v>1778659312652_382</v>
       </c>
       <c r="B132" t="str">
-        <v>696</v>
+        <v>383</v>
       </c>
       <c r="C132" t="str">
-        <v>314</v>
+        <v>749</v>
       </c>
       <c r="D132" t="str">
-        <v>Tasneem bai Taherali bhai Bharde</v>
+        <v>Mubarakah bai Qutbuddin bhai Lodalwala</v>
       </c>
       <c r="E132" t="str">
-        <v>30366504</v>
+        <v>30367371</v>
       </c>
       <c r="F132" t="str">
         <v>Given</v>
       </c>
       <c r="G132" t="str">
-        <v>Hussain bhai omiya</v>
+        <v>Abdeali shujai</v>
       </c>
       <c r="H132" t="str">
-        <v>22/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="I132" t="str">
-        <v>Friday</v>
+        <v>Monday</v>
       </c>
       <c r="J132" t="str">
-        <v>12:19:00</v>
+        <v>12:15:38</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>1778659312652_740</v>
+        <v>1778659312652_695</v>
       </c>
       <c r="B133" t="str">
-        <v>741</v>
+        <v>696</v>
       </c>
       <c r="C133" t="str">
-        <v>1499</v>
+        <v>314</v>
       </c>
       <c r="D133" t="str">
-        <v>Zainab bai Huzaifa bhai Saroda</v>
+        <v>Tasneem bai Taherali bhai Bharde</v>
       </c>
       <c r="E133" t="str">
-        <v>30367469</v>
+        <v>30366504</v>
       </c>
       <c r="F133" t="str">
         <v>Given</v>
       </c>
       <c r="G133" t="str">
-        <v>shkh fakhruddin badi</v>
+        <v>Hussain bhai omiya</v>
       </c>
       <c r="H133" t="str">
-        <v>20/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="I133" t="str">
-        <v>Wednesday</v>
+        <v>Friday</v>
       </c>
       <c r="J133" t="str">
-        <v>12:25:05</v>
+        <v>12:19:00</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>1778659312652_378</v>
+        <v>1778659312652_740</v>
       </c>
       <c r="B134" t="str">
-        <v>379</v>
+        <v>741</v>
       </c>
       <c r="C134" t="str">
-        <v>1344</v>
+        <v>1499</v>
       </c>
       <c r="D134" t="str">
-        <v>Mubarakah bai Aliakbar bhai Kabri</v>
+        <v>Zainab bai Huzaifa bhai Saroda</v>
       </c>
       <c r="E134" t="str">
-        <v>20318146</v>
+        <v>30367469</v>
       </c>
       <c r="F134" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G134" t="str">
-        <v/>
+        <v>shkh fakhruddin badi</v>
+      </c>
+      <c r="H134" t="str">
+        <v>20/05/2026</v>
+      </c>
+      <c r="I134" t="str">
+        <v>Wednesday</v>
+      </c>
+      <c r="J134" t="str">
+        <v>12:25:05</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>1778659312652_696</v>
+        <v>1778659312652_378</v>
       </c>
       <c r="B135" t="str">
-        <v>697</v>
+        <v>379</v>
       </c>
       <c r="C135" t="str">
-        <v>65</v>
+        <v>1344</v>
       </c>
       <c r="D135" t="str">
-        <v>Tasneem bai Talib bhai Thakarda</v>
+        <v>Mubarakah bai Aliakbar bhai Kabri</v>
       </c>
       <c r="E135" t="str">
-        <v>30360265</v>
+        <v>20318146</v>
       </c>
       <c r="F135" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G135" t="str">
-        <v>Farida ben Electric</v>
-      </c>
-      <c r="H135" t="str">
-        <v>20/05/2026</v>
-      </c>
-      <c r="I135" t="str">
-        <v>Wednesday</v>
-      </c>
-      <c r="J135" t="str">
-        <v>12:23:49</v>
+        <v/>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>1778659312652_388</v>
+        <v>1778659312652_696</v>
       </c>
       <c r="B136" t="str">
-        <v>389</v>
+        <v>697</v>
       </c>
       <c r="C136" t="str">
-        <v>594</v>
+        <v>65</v>
       </c>
       <c r="D136" t="str">
-        <v>Mulla Fakhruddin bhai Taher bhai Kabir</v>
+        <v>Tasneem bai Talib bhai Thakarda</v>
       </c>
       <c r="E136" t="str">
-        <v>20318360</v>
+        <v>30360265</v>
       </c>
       <c r="F136" t="str">
         <v>Given</v>
       </c>
       <c r="G136" t="str">
-        <v>Akbar Bhai Abbas bhai gatau</v>
+        <v>Farida ben Electric</v>
       </c>
       <c r="H136" t="str">
-        <v>21/05/2026</v>
+        <v>20/05/2026</v>
       </c>
       <c r="I136" t="str">
-        <v>Thursday</v>
+        <v>Wednesday</v>
       </c>
       <c r="J136" t="str">
-        <v>11:44:07</v>
+        <v>12:23:49</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>1778659312652_387</v>
+        <v>1778659312652_388</v>
       </c>
       <c r="B137" t="str">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C137" t="str">
-        <v>19</v>
+        <v>594</v>
       </c>
       <c r="D137" t="str">
-        <v>Mulla Fakhruddin bhai Qayumali bhai Nareli (nkd)</v>
+        <v>Mulla Fakhruddin bhai Taher bhai Kabir</v>
       </c>
       <c r="E137" t="str">
-        <v>20318018</v>
+        <v>20318360</v>
       </c>
       <c r="F137" t="str">
         <v>Given</v>
       </c>
       <c r="G137" t="str">
-        <v/>
+        <v>Akbar Bhai Abbas bhai gatau</v>
       </c>
       <c r="H137" t="str">
         <v>21/05/2026</v>
@@ -3916,47 +3979,56 @@
         <v>Thursday</v>
       </c>
       <c r="J137" t="str">
-        <v>12:48:38</v>
+        <v>11:44:07</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>1778659312652_379</v>
+        <v>1778659312652_387</v>
       </c>
       <c r="B138" t="str">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="C138" t="str">
-        <v/>
+        <v>19</v>
       </c>
       <c r="D138" t="str">
-        <v>Mubarakah bai Ismail bhai Munshi</v>
+        <v>Mulla Fakhruddin bhai Qayumali bhai Nareli (nkd)</v>
       </c>
       <c r="E138" t="str">
-        <v>30367342</v>
+        <v>20318018</v>
       </c>
       <c r="F138" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G138" t="str">
         <v/>
+      </c>
+      <c r="H138" t="str">
+        <v>21/05/2026</v>
+      </c>
+      <c r="I138" t="str">
+        <v>Thursday</v>
+      </c>
+      <c r="J138" t="str">
+        <v>12:48:38</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>1778659312652_380</v>
+        <v>1778659312652_379</v>
       </c>
       <c r="B139" t="str">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C139" t="str">
-        <v>1351</v>
+        <v/>
       </c>
       <c r="D139" t="str">
-        <v>Mubarakah bai Khuzaima bhai Agency</v>
+        <v>Mubarakah bai Ismail bhai Munshi</v>
       </c>
       <c r="E139" t="str">
-        <v>30443732</v>
+        <v>30367342</v>
       </c>
       <c r="F139" t="str">
         <v>Pending</v>
@@ -3967,19 +4039,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>1778659312652_381</v>
+        <v>1778659312652_380</v>
       </c>
       <c r="B140" t="str">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C140" t="str">
-        <v>1338</v>
+        <v>1351</v>
       </c>
       <c r="D140" t="str">
-        <v>Mubarakah bai Qurbanhusain bhai Thakerdawala</v>
+        <v>Mubarakah bai Khuzaima bhai Agency</v>
       </c>
       <c r="E140" t="str">
-        <v>30366822</v>
+        <v>30443732</v>
       </c>
       <c r="F140" t="str">
         <v>Pending</v>
@@ -3990,19 +4062,19 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>1778659312652_382</v>
+        <v>1778659312652_381</v>
       </c>
       <c r="B141" t="str">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C141" t="str">
-        <v>749</v>
+        <v>1338</v>
       </c>
       <c r="D141" t="str">
-        <v>Mubarakah bai Qutbuddin bhai Lodalwala</v>
+        <v>Mubarakah bai Qurbanhusain bhai Thakerdawala</v>
       </c>
       <c r="E141" t="str">
-        <v>30367371</v>
+        <v>30366822</v>
       </c>
       <c r="F141" t="str">
         <v>Pending</v>
@@ -4385,100 +4457,100 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>1778659312652_198</v>
+        <v>1778659312652_213</v>
       </c>
       <c r="B157" t="str">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="C157" t="str">
-        <v>1043</v>
+        <v>1397</v>
       </c>
       <c r="D157" t="str">
-        <v>Fatema bai Husain bhai Sarodawala</v>
+        <v>Fatema bai Qutbuddin bhai Bhabhranawala</v>
       </c>
       <c r="E157" t="str">
-        <v>20318641</v>
+        <v>30366326</v>
       </c>
       <c r="F157" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G157" t="str">
-        <v/>
+        <v>Nasa bhai</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>1778659312652_213</v>
+        <v>1778659312652_437</v>
       </c>
       <c r="B158" t="str">
-        <v>214</v>
+        <v>438</v>
       </c>
       <c r="C158" t="str">
-        <v>1397</v>
+        <v>1086</v>
       </c>
       <c r="D158" t="str">
-        <v>Fatema bai Qutbuddin bhai Bhabhranawala</v>
+        <v>Nafisa bai Zainuddin bhai Rata</v>
       </c>
       <c r="E158" t="str">
-        <v>30366326</v>
+        <v>30367872</v>
       </c>
       <c r="F158" t="str">
         <v>Given</v>
       </c>
       <c r="G158" t="str">
-        <v>Nasa bhai</v>
+        <v>Farida bai Abbas bhai Khumanpur</v>
+      </c>
+      <c r="H158" t="str">
+        <v>20/05/2026</v>
+      </c>
+      <c r="I158" t="str">
+        <v>Wednesday</v>
+      </c>
+      <c r="J158" t="str">
+        <v>11:49:29</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>1778659312652_437</v>
+        <v>1778659312652_214</v>
       </c>
       <c r="B159" t="str">
-        <v>438</v>
+        <v>215</v>
       </c>
       <c r="C159" t="str">
-        <v>1086</v>
+        <v>1213</v>
       </c>
       <c r="D159" t="str">
-        <v>Nafisa bai Zainuddin bhai Rata</v>
+        <v>Fatema bai Qutbuddin bhai Bhura</v>
       </c>
       <c r="E159" t="str">
-        <v>30367872</v>
+        <v>20318751</v>
       </c>
       <c r="F159" t="str">
         <v>Given</v>
       </c>
       <c r="G159" t="str">
-        <v>Farida bai Abbas bhai Khumanpur</v>
-      </c>
-      <c r="H159" t="str">
-        <v>20/05/2026</v>
-      </c>
-      <c r="I159" t="str">
-        <v>Wednesday</v>
-      </c>
-      <c r="J159" t="str">
-        <v>11:49:29</v>
+        <v/>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>1778659312652_214</v>
+        <v>1778659312652_215</v>
       </c>
       <c r="B160" t="str">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C160" t="str">
-        <v>1213</v>
+        <v>1169</v>
       </c>
       <c r="D160" t="str">
-        <v>Fatema bai Qutbuddin bhai Bhura</v>
+        <v>Fatema bai Qutbuddin bhai Maimoon</v>
       </c>
       <c r="E160" t="str">
-        <v>20318751</v>
+        <v>20318801</v>
       </c>
       <c r="F160" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -4486,184 +4558,184 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>1778659312652_215</v>
+        <v>1778659312652_216</v>
       </c>
       <c r="B161" t="str">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C161" t="str">
-        <v>1169</v>
+        <v>426</v>
       </c>
       <c r="D161" t="str">
-        <v>Fatema bai Qutbuddin bhai Maimoon</v>
+        <v>Fatema bai Qutbuddin bhai Peeth</v>
       </c>
       <c r="E161" t="str">
-        <v>20318801</v>
+        <v>30366524</v>
       </c>
       <c r="F161" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G161" t="str">
-        <v/>
+        <v>shkh fakhruddin badi</v>
+      </c>
+      <c r="H161" t="str">
+        <v>18/05/2026</v>
+      </c>
+      <c r="I161" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J161" t="str">
+        <v>12:20:39</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>1778659312652_216</v>
+        <v>1778659312652_217</v>
       </c>
       <c r="B162" t="str">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C162" t="str">
-        <v>426</v>
+        <v>123</v>
       </c>
       <c r="D162" t="str">
-        <v>Fatema bai Qutbuddin bhai Peeth</v>
+        <v>Fatema bai Sadiqali bhai Obri</v>
       </c>
       <c r="E162" t="str">
-        <v>30366524</v>
+        <v>20318096</v>
       </c>
       <c r="F162" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G162" t="str">
-        <v>shkh fakhruddin badi</v>
-      </c>
-      <c r="H162" t="str">
-        <v>18/05/2026</v>
-      </c>
-      <c r="I162" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="J162" t="str">
-        <v>12:20:39</v>
+        <v/>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>1778659312652_217</v>
+        <v>1778659312652_443</v>
       </c>
       <c r="B163" t="str">
-        <v>218</v>
+        <v>444</v>
       </c>
       <c r="C163" t="str">
-        <v>123</v>
+        <v>820</v>
       </c>
       <c r="D163" t="str">
-        <v>Fatema bai Sadiqali bhai Obri</v>
+        <v>Nisreen bai Mohammed bhai Peethwala</v>
       </c>
       <c r="E163" t="str">
-        <v>20318096</v>
+        <v>30366448</v>
       </c>
       <c r="F163" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G163" t="str">
         <v/>
+      </c>
+      <c r="H163" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I163" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J163" t="str">
+        <v>11:05:00</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>1778659312652_443</v>
+        <v>1778659312652_218</v>
       </c>
       <c r="B164" t="str">
-        <v>444</v>
+        <v>219</v>
       </c>
       <c r="C164" t="str">
-        <v>820</v>
+        <v>972</v>
       </c>
       <c r="D164" t="str">
-        <v>Nisreen bai Mohammed bhai Peethwala</v>
+        <v>Fatema bai Saifuddin bhai Giyori</v>
       </c>
       <c r="E164" t="str">
-        <v>30366448</v>
+        <v>30367317</v>
       </c>
       <c r="F164" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G164" t="str">
         <v/>
-      </c>
-      <c r="H164" t="str">
-        <v>23/05/2026</v>
-      </c>
-      <c r="I164" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="J164" t="str">
-        <v>11:05:00</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>1778659312652_218</v>
+        <v>1778659312652_432</v>
       </c>
       <c r="B165" t="str">
-        <v>219</v>
+        <v>433</v>
       </c>
       <c r="C165" t="str">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="D165" t="str">
-        <v>Fatema bai Saifuddin bhai Giyori</v>
+        <v>Nafisa bai Shabbir bhai Antriwala</v>
       </c>
       <c r="E165" t="str">
-        <v>30367317</v>
+        <v>20318620</v>
       </c>
       <c r="F165" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G165" t="str">
         <v/>
+      </c>
+      <c r="H165" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I165" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J165" t="str">
+        <v>11:07:44</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>1778659312652_432</v>
+        <v>1778659312652_427</v>
       </c>
       <c r="B166" t="str">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C166" t="str">
-        <v>975</v>
+        <v>986</v>
       </c>
       <c r="D166" t="str">
-        <v>Nafisa bai Shabbir bhai Antriwala</v>
+        <v>Nafisa bai Ismail bhai Jaan</v>
       </c>
       <c r="E166" t="str">
-        <v>20318620</v>
+        <v>20318626</v>
       </c>
       <c r="F166" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G166" t="str">
         <v/>
-      </c>
-      <c r="H166" t="str">
-        <v>23/05/2026</v>
-      </c>
-      <c r="I166" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="J166" t="str">
-        <v>11:07:44</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>1778659312652_427</v>
+        <v>1778659312652_428</v>
       </c>
       <c r="B167" t="str">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C167" t="str">
-        <v>986</v>
+        <v>696</v>
       </c>
       <c r="D167" t="str">
-        <v>Nafisa bai Ismail bhai Jaan</v>
+        <v>Nafisa bai Mohammed bhai Tuta</v>
       </c>
       <c r="E167" t="str">
-        <v>20318626</v>
+        <v>30367268</v>
       </c>
       <c r="F167" t="str">
         <v>Pending</v>
@@ -4674,19 +4746,19 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>1778659312652_428</v>
+        <v>1778659312652_42</v>
       </c>
       <c r="B168" t="str">
-        <v>429</v>
+        <v>43</v>
       </c>
       <c r="C168" t="str">
-        <v>696</v>
+        <v>425</v>
       </c>
       <c r="D168" t="str">
-        <v>Nafisa bai Mohammed bhai Tuta</v>
+        <v>Akbarhusain bhai Ghulamabbas bhai Peethwala</v>
       </c>
       <c r="E168" t="str">
-        <v>30367268</v>
+        <v>20437460</v>
       </c>
       <c r="F168" t="str">
         <v>Pending</v>
@@ -4697,80 +4769,89 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>1778659312652_42</v>
+        <v>1778659312652_429</v>
       </c>
       <c r="B169" t="str">
-        <v>43</v>
+        <v>430</v>
       </c>
       <c r="C169" t="str">
-        <v>425</v>
+        <v>607</v>
       </c>
       <c r="D169" t="str">
-        <v>Akbarhusain bhai Ghulamabbas bhai Peethwala</v>
+        <v>Nafisa bai Mohammedhusain bhai Lodal</v>
       </c>
       <c r="E169" t="str">
-        <v>20437460</v>
+        <v>30367102</v>
       </c>
       <c r="F169" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G169" t="str">
         <v/>
+      </c>
+      <c r="H169" t="str">
+        <v>18/05/2026</v>
+      </c>
+      <c r="I169" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J169" t="str">
+        <v>12:48:43</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>1778659312652_429</v>
+        <v>1778659312652_430</v>
       </c>
       <c r="B170" t="str">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C170" t="str">
-        <v>607</v>
+        <v>636</v>
       </c>
       <c r="D170" t="str">
-        <v>Nafisa bai Mohammedhusain bhai Lodal</v>
+        <v>Nafisa bai Saifuddin bhai Saroda</v>
       </c>
       <c r="E170" t="str">
-        <v>30367102</v>
+        <v>20318383</v>
       </c>
       <c r="F170" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G170" t="str">
         <v/>
-      </c>
-      <c r="H170" t="str">
-        <v>18/05/2026</v>
-      </c>
-      <c r="I170" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="J170" t="str">
-        <v>12:48:43</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>1778659312652_430</v>
+        <v>1778659312652_198</v>
       </c>
       <c r="B171" t="str">
-        <v>431</v>
+        <v>199</v>
       </c>
       <c r="C171" t="str">
-        <v>636</v>
+        <v>1043</v>
       </c>
       <c r="D171" t="str">
-        <v>Nafisa bai Saifuddin bhai Saroda</v>
+        <v>Fatema bai Husain bhai Sarodawala</v>
       </c>
       <c r="E171" t="str">
-        <v>20318383</v>
+        <v>20318641</v>
       </c>
       <c r="F171" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G171" t="str">
         <v/>
+      </c>
+      <c r="H171" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I171" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J171" t="str">
+        <v>10:50:25</v>
       </c>
     </row>
     <row r="172">
@@ -6368,57 +6449,57 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>1778659312652_266</v>
+        <v>1778659312652_647</v>
       </c>
       <c r="B235" t="str">
-        <v>267</v>
+        <v>648</v>
       </c>
       <c r="C235" t="str">
-        <v>1423</v>
+        <v>110</v>
       </c>
       <c r="D235" t="str">
-        <v>Husain bhai Abidhusain bhai Rashid</v>
+        <v>Shireen bai Fakhruddin bhai Obri</v>
       </c>
       <c r="E235" t="str">
-        <v>30366502</v>
+        <v>20318062</v>
       </c>
       <c r="F235" t="str">
         <v>Given</v>
       </c>
       <c r="G235" t="str">
-        <v>Huzaifa bhai maudi</v>
+        <v/>
       </c>
       <c r="H235" t="str">
-        <v>19/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="I235" t="str">
-        <v>Tuesday</v>
+        <v>Monday</v>
       </c>
       <c r="J235" t="str">
-        <v>10:33:50</v>
+        <v>12:05:28</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>1778659312652_598</v>
+        <v>1778659312652_266</v>
       </c>
       <c r="B236" t="str">
-        <v>599</v>
+        <v>267</v>
       </c>
       <c r="C236" t="str">
-        <v>610</v>
+        <v>1423</v>
       </c>
       <c r="D236" t="str">
-        <v>Shaikh Abdulhusain bhai Haiderali bhai Thepadiya</v>
+        <v>Husain bhai Abidhusain bhai Rashid</v>
       </c>
       <c r="E236" t="str">
-        <v>20318369</v>
+        <v>30366502</v>
       </c>
       <c r="F236" t="str">
         <v>Given</v>
       </c>
       <c r="G236" t="str">
-        <v/>
+        <v>Huzaifa bhai maudi</v>
       </c>
       <c r="H236" t="str">
         <v>19/05/2026</v>
@@ -6427,47 +6508,56 @@
         <v>Tuesday</v>
       </c>
       <c r="J236" t="str">
-        <v>10:41:25</v>
+        <v>10:33:50</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>1778659312652_646</v>
+        <v>1778659312652_598</v>
       </c>
       <c r="B237" t="str">
-        <v>647</v>
+        <v>599</v>
       </c>
       <c r="C237" t="str">
-        <v>1205</v>
+        <v>610</v>
       </c>
       <c r="D237" t="str">
-        <v>Shireen bai Fakhruddin bhai Galiakotwala</v>
+        <v>Shaikh Abdulhusain bhai Haiderali bhai Thepadiya</v>
       </c>
       <c r="E237" t="str">
-        <v>20318240</v>
+        <v>20318369</v>
       </c>
       <c r="F237" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G237" t="str">
         <v/>
+      </c>
+      <c r="H237" t="str">
+        <v>19/05/2026</v>
+      </c>
+      <c r="I237" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="J237" t="str">
+        <v>10:41:25</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>1778659312652_647</v>
+        <v>1778659312652_646</v>
       </c>
       <c r="B238" t="str">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C238" t="str">
-        <v>110</v>
+        <v>1205</v>
       </c>
       <c r="D238" t="str">
-        <v>Shireen bai Fakhruddin bhai Obri</v>
+        <v>Shireen bai Fakhruddin bhai Galiakotwala</v>
       </c>
       <c r="E238" t="str">
-        <v>20318062</v>
+        <v>20318240</v>
       </c>
       <c r="F238" t="str">
         <v>Pending</v>
@@ -7024,51 +7114,42 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>1778659312652_99</v>
+        <v>1778659312652_103</v>
       </c>
       <c r="B260" t="str">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C260" t="str">
-        <v>236</v>
+        <v>1303</v>
       </c>
       <c r="D260" t="str">
-        <v>Batul bai Johar bhai Saroda</v>
+        <v>Batul bai Qutbuddin bhai Rustam</v>
       </c>
       <c r="E260" t="str">
-        <v>30488741</v>
+        <v>30366656</v>
       </c>
       <c r="F260" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G260" t="str">
-        <v>Ilyas</v>
-      </c>
-      <c r="H260" t="str">
-        <v>25/05/2026</v>
-      </c>
-      <c r="I260" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="J260" t="str">
-        <v>03:31:23</v>
+        <v/>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>1778659312652_103</v>
+        <v>1778659312652_104</v>
       </c>
       <c r="B261" t="str">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C261" t="str">
-        <v>1303</v>
+        <v>76</v>
       </c>
       <c r="D261" t="str">
-        <v>Batul bai Qutbuddin bhai Rustam</v>
+        <v>Batul bai Saifuddin bhai Doodhbhai</v>
       </c>
       <c r="E261" t="str">
-        <v>30366656</v>
+        <v>30368616</v>
       </c>
       <c r="F261" t="str">
         <v>Pending</v>
@@ -7079,19 +7160,19 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>1778659312652_104</v>
+        <v>1778659312652_105</v>
       </c>
       <c r="B262" t="str">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C262" t="str">
-        <v>76</v>
+        <v>744</v>
       </c>
       <c r="D262" t="str">
-        <v>Batul bai Saifuddin bhai Doodhbhai</v>
+        <v>Batul bai Shaikh Akbarhusain bhai Rampurwala</v>
       </c>
       <c r="E262" t="str">
-        <v>30368616</v>
+        <v>30367359</v>
       </c>
       <c r="F262" t="str">
         <v>Pending</v>
@@ -7102,80 +7183,89 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>1778659312652_105</v>
+        <v>1778659312652_106</v>
       </c>
       <c r="B263" t="str">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C263" t="str">
-        <v>744</v>
+        <v>807</v>
       </c>
       <c r="D263" t="str">
-        <v>Batul bai Shaikh Akbarhusain bhai Rampurwala</v>
+        <v>Batul bai Taiyebali bhai Bankoda</v>
       </c>
       <c r="E263" t="str">
-        <v>30367359</v>
+        <v>30367508</v>
       </c>
       <c r="F263" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G263" t="str">
-        <v/>
+        <v>zainab ben antri</v>
+      </c>
+      <c r="H263" t="str">
+        <v>18/05/2026</v>
+      </c>
+      <c r="I263" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J263" t="str">
+        <v>11:50:34</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>1778659312652_106</v>
+        <v>1778659312652_6</v>
       </c>
       <c r="B264" t="str">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="C264" t="str">
-        <v>807</v>
+        <v>7</v>
       </c>
       <c r="D264" t="str">
-        <v>Batul bai Taiyebali bhai Bankoda</v>
+        <v>Abbas bhai Alihusain bhai Sihjee</v>
       </c>
       <c r="E264" t="str">
-        <v>30367508</v>
+        <v>20435003</v>
       </c>
       <c r="F264" t="str">
         <v>Given</v>
       </c>
       <c r="G264" t="str">
-        <v>zainab ben antri</v>
+        <v>Ajab ben Khand</v>
       </c>
       <c r="H264" t="str">
-        <v>18/05/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="I264" t="str">
-        <v>Monday</v>
+        <v>Thursday</v>
       </c>
       <c r="J264" t="str">
-        <v>11:50:34</v>
+        <v>10:25:43</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>1778659312652_6</v>
+        <v>1778659312652_335</v>
       </c>
       <c r="B265" t="str">
-        <v>7</v>
+        <v>336</v>
       </c>
       <c r="C265" t="str">
-        <v>7</v>
+        <v>1197</v>
       </c>
       <c r="D265" t="str">
-        <v>Abbas bhai Alihusain bhai Sihjee</v>
+        <v>Khanali bhai Mohammadhussain bhai Hedari</v>
       </c>
       <c r="E265" t="str">
-        <v>20435003</v>
+        <v>20414120</v>
       </c>
       <c r="F265" t="str">
         <v>Given</v>
       </c>
       <c r="G265" t="str">
-        <v>Ajab ben Khand</v>
+        <v/>
       </c>
       <c r="H265" t="str">
         <v>21/05/2026</v>
@@ -7184,56 +7274,47 @@
         <v>Thursday</v>
       </c>
       <c r="J265" t="str">
-        <v>10:25:43</v>
+        <v>11:08:30</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>1778659312652_335</v>
+        <v>1778659312652_108</v>
       </c>
       <c r="B266" t="str">
-        <v>336</v>
+        <v>109</v>
       </c>
       <c r="C266" t="str">
-        <v>1197</v>
+        <v>588</v>
       </c>
       <c r="D266" t="str">
-        <v>Khanali bhai Mohammadhussain bhai Hedari</v>
+        <v>Bilqis bai Husain bhai Gadi</v>
       </c>
       <c r="E266" t="str">
-        <v>20414120</v>
+        <v>20318760</v>
       </c>
       <c r="F266" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G266" t="str">
         <v/>
-      </c>
-      <c r="H266" t="str">
-        <v>21/05/2026</v>
-      </c>
-      <c r="I266" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="J266" t="str">
-        <v>11:08:30</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>1778659312652_107</v>
+        <v>1778659312652_326</v>
       </c>
       <c r="B267" t="str">
-        <v>108</v>
+        <v>327</v>
       </c>
       <c r="C267" t="str">
-        <v>17</v>
+        <v>431</v>
       </c>
       <c r="D267" t="str">
-        <v>Bilqis bai Abidhusain bhai Nareli</v>
+        <v>Khadija bai Fakhruddin bhai Peeth</v>
       </c>
       <c r="E267" t="str">
-        <v>20318722</v>
+        <v>30366840</v>
       </c>
       <c r="F267" t="str">
         <v>Pending</v>
@@ -7244,19 +7325,19 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>1778659312652_108</v>
+        <v>1778659312652_327</v>
       </c>
       <c r="B268" t="str">
-        <v>109</v>
+        <v>328</v>
       </c>
       <c r="C268" t="str">
-        <v>588</v>
+        <v>822</v>
       </c>
       <c r="D268" t="str">
-        <v>Bilqis bai Husain bhai Gadi</v>
+        <v>Khadija bai Ghulamhusain bhai Dudhwala</v>
       </c>
       <c r="E268" t="str">
-        <v>20318760</v>
+        <v>30367535</v>
       </c>
       <c r="F268" t="str">
         <v>Pending</v>
@@ -7267,19 +7348,19 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>1778659312652_326</v>
+        <v>1778659312652_328</v>
       </c>
       <c r="B269" t="str">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C269" t="str">
-        <v>431</v>
+        <v>684</v>
       </c>
       <c r="D269" t="str">
-        <v>Khadija bai Fakhruddin bhai Peeth</v>
+        <v>Khadija bai Haiderali bhai Maudi wala</v>
       </c>
       <c r="E269" t="str">
-        <v>30366840</v>
+        <v>30367251</v>
       </c>
       <c r="F269" t="str">
         <v>Pending</v>
@@ -7290,65 +7371,74 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>1778659312652_327</v>
+        <v>1778659312652_102</v>
       </c>
       <c r="B270" t="str">
-        <v>328</v>
+        <v>103</v>
       </c>
       <c r="C270" t="str">
-        <v>822</v>
+        <v>637</v>
       </c>
       <c r="D270" t="str">
-        <v>Khadija bai Ghulamhusain bhai Dudhwala</v>
+        <v>Batul bai Mufaddal bhai Jaan</v>
       </c>
       <c r="E270" t="str">
-        <v>30367535</v>
+        <v>30367654</v>
       </c>
       <c r="F270" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G270" t="str">
-        <v/>
+        <v>mulla jivaji</v>
+      </c>
+      <c r="H270" t="str">
+        <v>22/05/2026</v>
+      </c>
+      <c r="I270" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="J270" t="str">
+        <v>11:47:31</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>1778659312652_328</v>
+        <v>1778659312652_330</v>
       </c>
       <c r="B271" t="str">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C271" t="str">
-        <v>684</v>
+        <v>1356</v>
       </c>
       <c r="D271" t="str">
-        <v>Khadija bai Haiderali bhai Maudi wala</v>
+        <v>Khadija bai Murtaza bhai Ratawala</v>
       </c>
       <c r="E271" t="str">
-        <v>30367251</v>
+        <v>30367899</v>
       </c>
       <c r="F271" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G271" t="str">
-        <v/>
+        <v>Fakhruddin kawja</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>1778659312652_329</v>
+        <v>1778659312652_331</v>
       </c>
       <c r="B272" t="str">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C272" t="str">
-        <v>62</v>
+        <v>388</v>
       </c>
       <c r="D272" t="str">
-        <v>Khadija bai Mulla Fakhruddin bhai Baroda</v>
+        <v>Khadija bai Qutbuddin bhai Tara</v>
       </c>
       <c r="E272" t="str">
-        <v>20318054</v>
+        <v>30366583</v>
       </c>
       <c r="F272" t="str">
         <v>Pending</v>
@@ -7359,192 +7449,201 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>1778659312652_102</v>
+        <v>1778659312652_332</v>
       </c>
       <c r="B273" t="str">
-        <v>103</v>
+        <v>333</v>
       </c>
       <c r="C273" t="str">
-        <v>637</v>
+        <v>310</v>
       </c>
       <c r="D273" t="str">
-        <v>Batul bai Mufaddal bhai Jaan</v>
+        <v>Khadija bai Saifuddin bhai Ezzi</v>
       </c>
       <c r="E273" t="str">
-        <v>30367654</v>
+        <v>30366643</v>
       </c>
       <c r="F273" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G273" t="str">
-        <v>mulla jivaji</v>
-      </c>
-      <c r="H273" t="str">
-        <v>22/05/2026</v>
-      </c>
-      <c r="I273" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J273" t="str">
-        <v>11:47:31</v>
+        <v/>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>1778659312652_330</v>
+        <v>1778659312652_333</v>
       </c>
       <c r="B274" t="str">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C274" t="str">
-        <v>1356</v>
+        <v>1029</v>
       </c>
       <c r="D274" t="str">
-        <v>Khadija bai Murtaza bhai Ratawala</v>
+        <v>Khadija bai Shaikh Mohammed bhai Khumanpur</v>
       </c>
       <c r="E274" t="str">
-        <v>30367899</v>
+        <v>30367849</v>
       </c>
       <c r="F274" t="str">
         <v>Given</v>
       </c>
       <c r="G274" t="str">
-        <v>Fakhruddin kawja</v>
+        <v>yakut bhai gaba</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>1778659312652_331</v>
+        <v>1778659312652_334</v>
       </c>
       <c r="B275" t="str">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C275" t="str">
-        <v>388</v>
+        <v>138</v>
       </c>
       <c r="D275" t="str">
-        <v>Khadija bai Qutbuddin bhai Tara</v>
+        <v>Khadija bai Tayyeb bhai Gadi</v>
       </c>
       <c r="E275" t="str">
-        <v>30366583</v>
+        <v>30366336</v>
       </c>
       <c r="F275" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G275" t="str">
-        <v/>
+        <v>shkh fakhruddin badi</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>1778659312652_332</v>
+        <v>1778659312652_99</v>
       </c>
       <c r="B276" t="str">
-        <v>333</v>
+        <v>100</v>
       </c>
       <c r="C276" t="str">
-        <v>310</v>
+        <v>236</v>
       </c>
       <c r="D276" t="str">
-        <v>Khadija bai Saifuddin bhai Ezzi</v>
+        <v>Batul bai Johar bhai Saroda</v>
       </c>
       <c r="E276" t="str">
-        <v>30366643</v>
+        <v>30488741</v>
       </c>
       <c r="F276" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G276" t="str">
-        <v/>
+        <v>Ilyas</v>
+      </c>
+      <c r="H276" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I276" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J276" t="str">
+        <v>03:34:44</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>1778659312652_333</v>
+        <v>1778659312652_336</v>
       </c>
       <c r="B277" t="str">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C277" t="str">
-        <v>1029</v>
+        <v>980</v>
       </c>
       <c r="D277" t="str">
-        <v>Khadija bai Shaikh Mohammed bhai Khumanpur</v>
+        <v>Khuzaima bhai Shabbirhusain bhai Ramgarhwala</v>
       </c>
       <c r="E277" t="str">
-        <v>30367849</v>
+        <v>20402290</v>
       </c>
       <c r="F277" t="str">
         <v>Given</v>
       </c>
       <c r="G277" t="str">
-        <v>yakut bhai gaba</v>
+        <v>Nasa bhai</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>1778659312652_334</v>
+        <v>1778659312652_698</v>
       </c>
       <c r="B278" t="str">
-        <v>335</v>
+        <v>699</v>
       </c>
       <c r="C278" t="str">
-        <v>138</v>
+        <v>1475</v>
       </c>
       <c r="D278" t="str">
-        <v>Khadija bai Tayyeb bhai Gadi</v>
+        <v>Tasneem bai Yusuf bhai Rail</v>
       </c>
       <c r="E278" t="str">
-        <v>30366336</v>
+        <v>30366367</v>
       </c>
       <c r="F278" t="str">
         <v>Given</v>
       </c>
       <c r="G278" t="str">
-        <v>shkh fakhruddin badi</v>
+        <v/>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>1778659312652_336</v>
+        <v>1778659312652_107</v>
       </c>
       <c r="B279" t="str">
-        <v>337</v>
+        <v>108</v>
       </c>
       <c r="C279" t="str">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="D279" t="str">
-        <v>Khuzaima bhai Shabbirhusain bhai Ramgarhwala</v>
+        <v>Bilqis bai Abidhusain bhai Nareli</v>
       </c>
       <c r="E279" t="str">
-        <v>20402290</v>
+        <v>20318722</v>
       </c>
       <c r="F279" t="str">
         <v>Given</v>
       </c>
       <c r="G279" t="str">
-        <v>Nasa bhai</v>
+        <v/>
+      </c>
+      <c r="H279" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I279" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J279" t="str">
+        <v>10:40:28</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>1778659312652_698</v>
+        <v>1778659312652_69</v>
       </c>
       <c r="B280" t="str">
-        <v>699</v>
+        <v>70</v>
       </c>
       <c r="C280" t="str">
-        <v>1475</v>
+        <v>931</v>
       </c>
       <c r="D280" t="str">
-        <v>Tasneem bai Yusuf bhai Rail</v>
+        <v>Arwa bai Sajjadhusain bhai Partapur</v>
       </c>
       <c r="E280" t="str">
-        <v>30366367</v>
+        <v>20318614</v>
       </c>
       <c r="F280" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G280" t="str">
         <v/>
@@ -7552,25 +7651,34 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>1778659312652_69</v>
+        <v>1778659312652_329</v>
       </c>
       <c r="B281" t="str">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="C281" t="str">
-        <v>931</v>
+        <v>62</v>
       </c>
       <c r="D281" t="str">
-        <v>Arwa bai Sajjadhusain bhai Partapur</v>
+        <v>Khadija bai Mulla Fakhruddin bhai Baroda</v>
       </c>
       <c r="E281" t="str">
-        <v>20318614</v>
+        <v>20318054</v>
       </c>
       <c r="F281" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G281" t="str">
-        <v/>
+        <v>Murtaza bhai Baroda</v>
+      </c>
+      <c r="H281" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I281" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J281" t="str">
+        <v>10:59:46</v>
       </c>
     </row>
     <row r="282">
@@ -7653,42 +7761,51 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>1778659312652_10</v>
+        <v>1778659312652_246</v>
       </c>
       <c r="B285" t="str">
-        <v>11</v>
+        <v>247</v>
       </c>
       <c r="C285" t="str">
-        <v>15</v>
+        <v>394</v>
       </c>
       <c r="D285" t="str">
-        <v>Abbas bhai Sadiqali bhai Badshah</v>
+        <v>Habib bhai Shaikh Mohammed bhai Peethwala</v>
       </c>
       <c r="E285" t="str">
-        <v>20342313</v>
+        <v>30366781</v>
       </c>
       <c r="F285" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G285" t="str">
         <v/>
+      </c>
+      <c r="H285" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I285" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J285" t="str">
+        <v>10:38:36</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>1778659312652_109</v>
+        <v>1778659312652_10</v>
       </c>
       <c r="B286" t="str">
-        <v>110</v>
+        <v>11</v>
       </c>
       <c r="C286" t="str">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="D286" t="str">
-        <v>Bilqis bai Mohammadhussain bhai Kamruddinwala</v>
+        <v>Abbas bhai Sadiqali bhai Badshah</v>
       </c>
       <c r="E286" t="str">
-        <v>20318061</v>
+        <v>20342313</v>
       </c>
       <c r="F286" t="str">
         <v>Pending</v>
@@ -7699,19 +7816,19 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>1778659312652_110</v>
+        <v>1778659312652_109</v>
       </c>
       <c r="B287" t="str">
+        <v>110</v>
+      </c>
+      <c r="C287" t="str">
         <v>111</v>
       </c>
-      <c r="C287" t="str">
-        <v>826</v>
-      </c>
       <c r="D287" t="str">
-        <v>Bilqis bai Qutbuddin bhai Kikabhai</v>
+        <v>Bilqis bai Mohammadhussain bhai Kamruddinwala</v>
       </c>
       <c r="E287" t="str">
-        <v>30367538</v>
+        <v>20318061</v>
       </c>
       <c r="F287" t="str">
         <v>Pending</v>
@@ -7722,19 +7839,19 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>1778659312652_111</v>
+        <v>1778659312652_110</v>
       </c>
       <c r="B288" t="str">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C288" t="str">
-        <v/>
+        <v>826</v>
       </c>
       <c r="D288" t="str">
-        <v>Burhanuddin bhai Kutbuddin bhai Peeth</v>
+        <v>Bilqis bai Qutbuddin bhai Kikabhai</v>
       </c>
       <c r="E288" t="str">
-        <v>30366845</v>
+        <v>30367538</v>
       </c>
       <c r="F288" t="str">
         <v>Pending</v>
@@ -7745,19 +7862,19 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>1778659312652_112</v>
+        <v>1778659312652_111</v>
       </c>
       <c r="B289" t="str">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C289" t="str">
         <v/>
       </c>
       <c r="D289" t="str">
-        <v>Burhanuddin bhai Saifuddin bhai Tuta</v>
+        <v>Burhanuddin bhai Kutbuddin bhai Peeth</v>
       </c>
       <c r="E289" t="str">
-        <v>30367203</v>
+        <v>30366845</v>
       </c>
       <c r="F289" t="str">
         <v>Pending</v>
@@ -7768,65 +7885,65 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>1778659312652_113</v>
+        <v>1778659312652_112</v>
       </c>
       <c r="B290" t="str">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C290" t="str">
-        <v>1050</v>
+        <v/>
       </c>
       <c r="D290" t="str">
-        <v>Dawood bhai Ahmedali bhai Najra</v>
+        <v>Burhanuddin bhai Saifuddin bhai Tuta</v>
       </c>
       <c r="E290" t="str">
-        <v>20387950</v>
+        <v>30367203</v>
       </c>
       <c r="F290" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G290" t="str">
-        <v>Taher bhai Abbas bhai Tuta</v>
+        <v/>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>1778659312652_242</v>
+        <v>1778659312652_113</v>
       </c>
       <c r="B291" t="str">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="C291" t="str">
-        <v>282</v>
+        <v>1050</v>
       </c>
       <c r="D291" t="str">
-        <v>Habib bhai Fakhruddin bhai Fata</v>
+        <v>Dawood bhai Ahmedali bhai Najra</v>
       </c>
       <c r="E291" t="str">
-        <v>20438486</v>
+        <v>20387950</v>
       </c>
       <c r="F291" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G291" t="str">
-        <v/>
+        <v>Taher bhai Abbas bhai Tuta</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>1778659312652_243</v>
+        <v>1778659312652_242</v>
       </c>
       <c r="B292" t="str">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C292" t="str">
-        <v>3</v>
+        <v>282</v>
       </c>
       <c r="D292" t="str">
-        <v>Habib bhai Fakhruddin bhai Sagir</v>
+        <v>Habib bhai Fakhruddin bhai Fata</v>
       </c>
       <c r="E292" t="str">
-        <v>20352546</v>
+        <v>20438486</v>
       </c>
       <c r="F292" t="str">
         <v>Pending</v>
@@ -7837,19 +7954,19 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>1778659312652_244</v>
+        <v>1778659312652_243</v>
       </c>
       <c r="B293" t="str">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C293" t="str">
-        <v>962</v>
+        <v>3</v>
       </c>
       <c r="D293" t="str">
-        <v>Habib bhai Jivaji bhai Pachlasa</v>
+        <v>Habib bhai Fakhruddin bhai Sagir</v>
       </c>
       <c r="E293" t="str">
-        <v>20318592</v>
+        <v>20352546</v>
       </c>
       <c r="F293" t="str">
         <v>Pending</v>
@@ -7860,42 +7977,51 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>1778659312652_245</v>
+        <v>1778659312652_0</v>
       </c>
       <c r="B294" t="str">
-        <v>246</v>
+        <v>1</v>
       </c>
       <c r="C294" t="str">
-        <v>421</v>
+        <v>16</v>
       </c>
       <c r="D294" t="str">
-        <v>Habib bhai Shaikh Fakhruddin bhai Daya</v>
+        <v>Aashiqhusain bhai Fakhruddin bhai Sultiwala</v>
       </c>
       <c r="E294" t="str">
-        <v>20435822</v>
+        <v>30704209</v>
       </c>
       <c r="F294" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G294" t="str">
-        <v/>
+        <v>Abbas bhai</v>
+      </c>
+      <c r="H294" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I294" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J294" t="str">
+        <v>11:09:46</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>1778659312652_246</v>
+        <v>1778659312652_244</v>
       </c>
       <c r="B295" t="str">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C295" t="str">
-        <v>394</v>
+        <v>962</v>
       </c>
       <c r="D295" t="str">
-        <v>Habib bhai Shaikh Mohammed bhai Peethwala</v>
+        <v>Habib bhai Jivaji bhai Pachlasa</v>
       </c>
       <c r="E295" t="str">
-        <v>30366781</v>
+        <v>20318592</v>
       </c>
       <c r="F295" t="str">
         <v>Pending</v>
@@ -7906,19 +8032,19 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>1778659312652_247</v>
+        <v>1778659312652_245</v>
       </c>
       <c r="B296" t="str">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C296" t="str">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D296" t="str">
-        <v>Haider bhai Akberali bhai Tutawala</v>
+        <v>Habib bhai Shaikh Fakhruddin bhai Daya</v>
       </c>
       <c r="E296" t="str">
-        <v>20318260</v>
+        <v>20435822</v>
       </c>
       <c r="F296" t="str">
         <v>Pending</v>
@@ -7929,19 +8055,19 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>1778659312652_248</v>
+        <v>1778659312652_247</v>
       </c>
       <c r="B297" t="str">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C297" t="str">
-        <v>634</v>
+        <v>416</v>
       </c>
       <c r="D297" t="str">
-        <v>Hajera bai Fakhruddin bhai Vakil</v>
+        <v>Haider bhai Akberali bhai Tutawala</v>
       </c>
       <c r="E297" t="str">
-        <v>20318382</v>
+        <v>20318260</v>
       </c>
       <c r="F297" t="str">
         <v>Pending</v>
@@ -7952,19 +8078,19 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>1778659312652_249</v>
+        <v>1778659312652_248</v>
       </c>
       <c r="B298" t="str">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C298" t="str">
-        <v>611</v>
+        <v>634</v>
       </c>
       <c r="D298" t="str">
-        <v>Hakimuddin bhai Abbas bhai Barkat</v>
+        <v>Hajera bai Fakhruddin bhai Vakil</v>
       </c>
       <c r="E298" t="str">
-        <v>30805002</v>
+        <v>20318382</v>
       </c>
       <c r="F298" t="str">
         <v>Pending</v>
@@ -7975,19 +8101,19 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>1778659312652_250</v>
+        <v>1778659312652_249</v>
       </c>
       <c r="B299" t="str">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C299" t="str">
-        <v>1179</v>
+        <v>611</v>
       </c>
       <c r="D299" t="str">
-        <v>Hakimuddin bhai Abdullah bhai Lodal</v>
+        <v>Hakimuddin bhai Abbas bhai Barkat</v>
       </c>
       <c r="E299" t="str">
-        <v>20352764</v>
+        <v>30805002</v>
       </c>
       <c r="F299" t="str">
         <v>Pending</v>
@@ -7998,19 +8124,19 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>1778659312652_251</v>
+        <v>1778659312652_250</v>
       </c>
       <c r="B300" t="str">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C300" t="str">
-        <v>845</v>
+        <v>1179</v>
       </c>
       <c r="D300" t="str">
-        <v>Hakimuddin bhai Fakhruddin bhai Bakri</v>
+        <v>Hakimuddin bhai Abdullah bhai Lodal</v>
       </c>
       <c r="E300" t="str">
-        <v>20318532</v>
+        <v>20352764</v>
       </c>
       <c r="F300" t="str">
         <v>Pending</v>
@@ -8021,19 +8147,19 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>1778659312652_252</v>
+        <v>1778659312652_251</v>
       </c>
       <c r="B301" t="str">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C301" t="str">
-        <v>467</v>
+        <v>845</v>
       </c>
       <c r="D301" t="str">
-        <v>Hakimuddin bhai Ibrahim bhai Electricwala</v>
+        <v>Hakimuddin bhai Fakhruddin bhai Bakri</v>
       </c>
       <c r="E301" t="str">
-        <v>20318280</v>
+        <v>20318532</v>
       </c>
       <c r="F301" t="str">
         <v>Pending</v>
@@ -8044,19 +8170,19 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>1778659312652_253</v>
+        <v>1778659312652_252</v>
       </c>
       <c r="B302" t="str">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C302" t="str">
-        <v>1473</v>
+        <v>467</v>
       </c>
       <c r="D302" t="str">
-        <v>Hakimuddin bhai Mohammadhussain bhai Hamed (godichand)</v>
+        <v>Hakimuddin bhai Ibrahim bhai Electricwala</v>
       </c>
       <c r="E302" t="str">
-        <v>30360130</v>
+        <v>20318280</v>
       </c>
       <c r="F302" t="str">
         <v>Pending</v>
@@ -8067,19 +8193,19 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>1778659312652_254</v>
+        <v>1778659312652_253</v>
       </c>
       <c r="B303" t="str">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C303" t="str">
-        <v>43</v>
+        <v>1473</v>
       </c>
       <c r="D303" t="str">
-        <v>Hakimuddin bhai Mohammedali bhai Kabri</v>
+        <v>Hakimuddin bhai Mohammadhussain bhai Hamed (godichand)</v>
       </c>
       <c r="E303" t="str">
-        <v>20318046</v>
+        <v>30360130</v>
       </c>
       <c r="F303" t="str">
         <v>Pending</v>
@@ -8090,19 +8216,19 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>1778659312652_255</v>
+        <v>1778659312652_254</v>
       </c>
       <c r="B304" t="str">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C304" t="str">
-        <v>567</v>
+        <v>43</v>
       </c>
       <c r="D304" t="str">
-        <v>Hakimuddin bhai Nazarhussain bhai Firangi</v>
+        <v>Hakimuddin bhai Mohammedali bhai Kabri</v>
       </c>
       <c r="E304" t="str">
-        <v>20434697</v>
+        <v>20318046</v>
       </c>
       <c r="F304" t="str">
         <v>Pending</v>
@@ -8113,19 +8239,19 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>1778659312652_256</v>
+        <v>1778659312652_255</v>
       </c>
       <c r="B305" t="str">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C305" t="str">
-        <v>306</v>
+        <v>567</v>
       </c>
       <c r="D305" t="str">
-        <v>Hakimuddin bhai Rajabali bhai Buraksha</v>
+        <v>Hakimuddin bhai Nazarhussain bhai Firangi</v>
       </c>
       <c r="E305" t="str">
-        <v>30366634</v>
+        <v>20434697</v>
       </c>
       <c r="F305" t="str">
         <v>Pending</v>
@@ -8136,19 +8262,19 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>1778659312652_0</v>
+        <v>1778659312652_256</v>
       </c>
       <c r="B306" t="str">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="C306" t="str">
-        <v>16</v>
+        <v>306</v>
       </c>
       <c r="D306" t="str">
-        <v>Aashiqhusain bhai Fakhruddin bhai Sultiwala</v>
+        <v>Hakimuddin bhai Rajabali bhai Buraksha</v>
       </c>
       <c r="E306" t="str">
-        <v>30704209</v>
+        <v>30366634</v>
       </c>
       <c r="F306" t="str">
         <v>Pending</v>
@@ -8283,77 +8409,77 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>1778659312652_284</v>
+        <v>1778659312652_722</v>
       </c>
       <c r="B312" t="str">
-        <v>285</v>
+        <v>723</v>
       </c>
       <c r="C312" t="str">
-        <v>1168</v>
+        <v>756</v>
       </c>
       <c r="D312" t="str">
-        <v>Husaina bai Alihusain bhai Bawan</v>
+        <v>Zahra bai Mukarram bhai Ammarji</v>
       </c>
       <c r="E312" t="str">
-        <v>20318800</v>
+        <v>20318470</v>
       </c>
       <c r="F312" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G312" t="str">
-        <v/>
+        <v>Mariya ben peeth</v>
+      </c>
+      <c r="H312" t="str">
+        <v>20/05/2026</v>
+      </c>
+      <c r="I312" t="str">
+        <v>Wednesday</v>
+      </c>
+      <c r="J312" t="str">
+        <v>11:40:35</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>1778659312652_722</v>
+        <v>1778659312652_451</v>
       </c>
       <c r="B313" t="str">
-        <v>723</v>
+        <v>452</v>
       </c>
       <c r="C313" t="str">
-        <v>756</v>
+        <v>135</v>
       </c>
       <c r="D313" t="str">
-        <v>Zahra bai Mukarram bhai Ammarji</v>
+        <v>Qutbuddin bhai Alihusain bhai Jamali(bawsi)</v>
       </c>
       <c r="E313" t="str">
-        <v>20318470</v>
+        <v>20352556</v>
       </c>
       <c r="F313" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G313" t="str">
-        <v>Mariya ben peeth</v>
-      </c>
-      <c r="H313" t="str">
-        <v>20/05/2026</v>
-      </c>
-      <c r="I313" t="str">
-        <v>Wednesday</v>
-      </c>
-      <c r="J313" t="str">
-        <v>11:40:35</v>
+        <v/>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>1778659312652_451</v>
+        <v>1778659312652_452</v>
       </c>
       <c r="B314" t="str">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C314" t="str">
-        <v>135</v>
+        <v>1035</v>
       </c>
       <c r="D314" t="str">
-        <v>Qutbuddin bhai Alihusain bhai Jamali(bawsi)</v>
+        <v>Qutbuddin bhai Alimohammed bhai Jigar</v>
       </c>
       <c r="E314" t="str">
-        <v>20352556</v>
+        <v>30928486</v>
       </c>
       <c r="F314" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G314" t="str">
         <v/>
@@ -8361,19 +8487,19 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>1778659312652_452</v>
+        <v>1778659312652_454</v>
       </c>
       <c r="B315" t="str">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C315" t="str">
-        <v>1035</v>
+        <v>1245</v>
       </c>
       <c r="D315" t="str">
-        <v>Qutbuddin bhai Alimohammed bhai Jigar</v>
+        <v>Qutbuddin bhai Fakhruddin bhai Ghiya</v>
       </c>
       <c r="E315" t="str">
-        <v>30928486</v>
+        <v>30801764</v>
       </c>
       <c r="F315" t="str">
         <v>Given</v>
@@ -8384,22 +8510,22 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>1778659312652_454</v>
+        <v>1778659312652_455</v>
       </c>
       <c r="B316" t="str">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C316" t="str">
-        <v>1245</v>
+        <v>29</v>
       </c>
       <c r="D316" t="str">
-        <v>Qutbuddin bhai Fakhruddin bhai Ghiya</v>
+        <v>Qutbuddin bhai Fakhruddin bhai Varda</v>
       </c>
       <c r="E316" t="str">
-        <v>30801764</v>
+        <v>20318781</v>
       </c>
       <c r="F316" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G316" t="str">
         <v/>
@@ -8407,19 +8533,19 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>1778659312652_455</v>
+        <v>1778659312652_458</v>
       </c>
       <c r="B317" t="str">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C317" t="str">
-        <v>29</v>
+        <v>289</v>
       </c>
       <c r="D317" t="str">
-        <v>Qutbuddin bhai Fakhruddin bhai Varda</v>
+        <v>Qutbuddin bhai Taherali bhai Varda</v>
       </c>
       <c r="E317" t="str">
-        <v>20318781</v>
+        <v>20318164</v>
       </c>
       <c r="F317" t="str">
         <v>Pending</v>
@@ -8430,74 +8556,74 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>1778659312652_458</v>
+        <v>1778659312652_700</v>
       </c>
       <c r="B318" t="str">
-        <v>459</v>
+        <v>701</v>
       </c>
       <c r="C318" t="str">
-        <v>289</v>
+        <v>1437</v>
       </c>
       <c r="D318" t="str">
-        <v>Qutbuddin bhai Taherali bhai Varda</v>
+        <v>Ummekulsum bai Haider bhai Gunj</v>
       </c>
       <c r="E318" t="str">
-        <v>20318164</v>
+        <v>30360238</v>
       </c>
       <c r="F318" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G318" t="str">
         <v/>
+      </c>
+      <c r="H318" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I318" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J318" t="str">
+        <v>11:34:15</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>1778659312652_700</v>
+        <v>1778659312652_45</v>
       </c>
       <c r="B319" t="str">
-        <v>701</v>
+        <v>46</v>
       </c>
       <c r="C319" t="str">
-        <v>1437</v>
+        <v>946</v>
       </c>
       <c r="D319" t="str">
-        <v>Ummekulsum bai Haider bhai Gunj</v>
+        <v>Alefiyah bai Aliasgar bhai Luqmani</v>
       </c>
       <c r="E319" t="str">
-        <v>30360238</v>
+        <v>30399266</v>
       </c>
       <c r="F319" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G319" t="str">
         <v/>
-      </c>
-      <c r="H319" t="str">
-        <v>23/05/2026</v>
-      </c>
-      <c r="I319" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="J319" t="str">
-        <v>11:34:15</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>1778659312652_45</v>
+        <v>1778659312652_459</v>
       </c>
       <c r="B320" t="str">
-        <v>46</v>
+        <v>460</v>
       </c>
       <c r="C320" t="str">
-        <v>946</v>
+        <v>102</v>
       </c>
       <c r="D320" t="str">
-        <v>Alefiyah bai Aliasgar bhai Luqmani</v>
+        <v>Qutbuddin bhai Taiyebali bhai Patanwala</v>
       </c>
       <c r="E320" t="str">
-        <v>30399266</v>
+        <v>20435747</v>
       </c>
       <c r="F320" t="str">
         <v>Pending</v>
@@ -8508,19 +8634,19 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>1778659312652_459</v>
+        <v>1778659312652_460</v>
       </c>
       <c r="B321" t="str">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C321" t="str">
-        <v>102</v>
+        <v>468</v>
       </c>
       <c r="D321" t="str">
-        <v>Qutbuddin bhai Taiyebali bhai Patanwala</v>
+        <v>Qutbuddin bhai Yusufali bhai Jigar</v>
       </c>
       <c r="E321" t="str">
-        <v>20435747</v>
+        <v>20348155</v>
       </c>
       <c r="F321" t="str">
         <v>Pending</v>
@@ -8531,19 +8657,19 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>1778659312652_460</v>
+        <v>1778659312652_461</v>
       </c>
       <c r="B322" t="str">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C322" t="str">
-        <v>468</v>
+        <v>228</v>
       </c>
       <c r="D322" t="str">
-        <v>Qutbuddin bhai Yusufali bhai Jigar</v>
+        <v>Rabab bai Abbas bhai Pan</v>
       </c>
       <c r="E322" t="str">
-        <v>20348155</v>
+        <v>20318805</v>
       </c>
       <c r="F322" t="str">
         <v>Pending</v>
@@ -8554,48 +8680,57 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>1778659312652_461</v>
+        <v>1778659312652_463</v>
       </c>
       <c r="B323" t="str">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C323" t="str">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="D323" t="str">
-        <v>Rabab bai Abbas bhai Pan</v>
+        <v>Rashida bai Alihusain bhai Nareli</v>
       </c>
       <c r="E323" t="str">
-        <v>20318805</v>
+        <v>30360138</v>
       </c>
       <c r="F323" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G323" t="str">
         <v/>
+      </c>
+      <c r="H323" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I323" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J323" t="str">
+        <v>11:45:06</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>1778659312652_463</v>
+        <v>1778659312652_281</v>
       </c>
       <c r="B324" t="str">
-        <v>464</v>
+        <v>282</v>
       </c>
       <c r="C324" t="str">
-        <v>20</v>
+        <v>479</v>
       </c>
       <c r="D324" t="str">
-        <v>Rashida bai Alihusain bhai Nareli</v>
+        <v>Husain bhai Shaikh Najmuddin bhai Tawawala</v>
       </c>
       <c r="E324" t="str">
-        <v>30360138</v>
+        <v>20352655</v>
       </c>
       <c r="F324" t="str">
         <v>Given</v>
       </c>
       <c r="G324" t="str">
-        <v/>
+        <v>hussain bhai tawa</v>
       </c>
       <c r="H324" t="str">
         <v>23/05/2026</v>
@@ -8604,62 +8739,62 @@
         <v>Saturday</v>
       </c>
       <c r="J324" t="str">
-        <v>11:45:06</v>
+        <v>12:30:15</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>1778659312652_281</v>
+        <v>1778659312652_699</v>
       </c>
       <c r="B325" t="str">
-        <v>282</v>
+        <v>700</v>
       </c>
       <c r="C325" t="str">
-        <v>479</v>
+        <v>1252</v>
       </c>
       <c r="D325" t="str">
-        <v>Husain bhai Shaikh Najmuddin bhai Tawawala</v>
+        <v>Ummeayman bai Qutbuddin bhai Kanchwala</v>
       </c>
       <c r="E325" t="str">
-        <v>20352655</v>
+        <v>30393342</v>
       </c>
       <c r="F325" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G325" t="str">
-        <v>hussain bhai tawa</v>
-      </c>
-      <c r="H325" t="str">
-        <v>23/05/2026</v>
-      </c>
-      <c r="I325" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="J325" t="str">
-        <v>12:30:15</v>
+        <v/>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>1778659312652_699</v>
+        <v>1778659312652_284</v>
       </c>
       <c r="B326" t="str">
-        <v>700</v>
+        <v>285</v>
       </c>
       <c r="C326" t="str">
-        <v>1252</v>
+        <v>1168</v>
       </c>
       <c r="D326" t="str">
-        <v>Ummeayman bai Qutbuddin bhai Kanchwala</v>
+        <v>Husaina bai Alihusain bhai Bawan</v>
       </c>
       <c r="E326" t="str">
-        <v>30393342</v>
+        <v>20318800</v>
       </c>
       <c r="F326" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G326" t="str">
         <v/>
+      </c>
+      <c r="H326" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I326" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J326" t="str">
+        <v>12:36:20</v>
       </c>
     </row>
     <row r="327">
@@ -9012,157 +9147,193 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>1778659312652_189</v>
+        <v>1778659312652_411</v>
       </c>
       <c r="B339" t="str">
-        <v>190</v>
+        <v>412</v>
       </c>
       <c r="C339" t="str">
-        <v>496</v>
+        <v>1194</v>
       </c>
       <c r="D339" t="str">
-        <v>Fatema bai Fakhruddin bhai Thakarda</v>
+        <v>Murtaza bhai Shaikh Mohammadhussain bhai Badri</v>
       </c>
       <c r="E339" t="str">
-        <v>20318297</v>
+        <v>30341651</v>
       </c>
       <c r="F339" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G339" t="str">
         <v/>
+      </c>
+      <c r="H339" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I339" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J339" t="str">
+        <v>10:39:16</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>1778659312652_190</v>
+        <v>1778659312652_189</v>
       </c>
       <c r="B340" t="str">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C340" t="str">
-        <v>33</v>
+        <v>496</v>
       </c>
       <c r="D340" t="str">
-        <v>Fatema bai Habib bhai Chavi</v>
+        <v>Fatema bai Fakhruddin bhai Thakarda</v>
       </c>
       <c r="E340" t="str">
-        <v>60401521</v>
+        <v>20318297</v>
       </c>
       <c r="F340" t="str">
         <v>Given</v>
       </c>
       <c r="G340" t="str">
-        <v>Zainab ben Khandi</v>
+        <v/>
+      </c>
+      <c r="H340" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I340" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J340" t="str">
+        <v>10:48:11</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>1778659312652_191</v>
+        <v>1778659312652_400</v>
       </c>
       <c r="B341" t="str">
-        <v>192</v>
+        <v>401</v>
       </c>
       <c r="C341" t="str">
-        <v>1361</v>
+        <v>166</v>
       </c>
       <c r="D341" t="str">
-        <v>Fatema bai Hakimuddin bhai Obri</v>
+        <v>Munira bai Ali bhai Pachlasa wala</v>
       </c>
       <c r="E341" t="str">
-        <v>30366472</v>
+        <v>20318114</v>
       </c>
       <c r="F341" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G341" t="str">
-        <v/>
+        <v>Kutub bhai Gaba</v>
+      </c>
+      <c r="H341" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I341" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J341" t="str">
+        <v>12:04:47</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>1778659312652_193</v>
+        <v>1778659312652_197</v>
       </c>
       <c r="B342" t="str">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C342" t="str">
-        <v>1312</v>
+        <v>865</v>
       </c>
       <c r="D342" t="str">
-        <v>Fatema bai Husain bhai Bhardey</v>
+        <v>Fatema bai Husain bhai Pachlasa</v>
       </c>
       <c r="E342" t="str">
-        <v>30366646</v>
+        <v>30367611</v>
       </c>
       <c r="F342" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G342" t="str">
         <v/>
+      </c>
+      <c r="H342" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I342" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J342" t="str">
+        <v>12:05:20</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>1778659312652_194</v>
+        <v>1778659312652_190</v>
       </c>
       <c r="B343" t="str">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C343" t="str">
-        <v>385</v>
+        <v>33</v>
       </c>
       <c r="D343" t="str">
-        <v>Fatema bai Husain bhai Daya</v>
+        <v>Fatema bai Habib bhai Chavi</v>
       </c>
       <c r="E343" t="str">
-        <v>50419406</v>
+        <v>60401521</v>
       </c>
       <c r="F343" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G343" t="str">
-        <v/>
+        <v>Zainab ben Khandi</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>1778659312652_196</v>
+        <v>1778659312652_191</v>
       </c>
       <c r="B344" t="str">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C344" t="str">
-        <v>1322</v>
+        <v>1361</v>
       </c>
       <c r="D344" t="str">
-        <v>Fatema bai Husain bhai Natak</v>
+        <v>Fatema bai Hakimuddin bhai Obri</v>
       </c>
       <c r="E344" t="str">
-        <v>30366479</v>
+        <v>30366472</v>
       </c>
       <c r="F344" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G344" t="str">
-        <v>Mohammed bhai sageer</v>
+        <v/>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>1778659312652_197</v>
+        <v>1778659312652_193</v>
       </c>
       <c r="B345" t="str">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C345" t="str">
-        <v>865</v>
+        <v>1312</v>
       </c>
       <c r="D345" t="str">
-        <v>Fatema bai Husain bhai Pachlasa</v>
+        <v>Fatema bai Husain bhai Bhardey</v>
       </c>
       <c r="E345" t="str">
-        <v>30367611</v>
+        <v>30366646</v>
       </c>
       <c r="F345" t="str">
         <v>Pending</v>
@@ -9173,22 +9344,22 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>1778659312652_399</v>
+        <v>1778659312652_194</v>
       </c>
       <c r="B346" t="str">
-        <v>400</v>
+        <v>195</v>
       </c>
       <c r="C346" t="str">
-        <v>1421</v>
+        <v>385</v>
       </c>
       <c r="D346" t="str">
-        <v>Munavar bhai Abid bhai Bashi</v>
+        <v>Fatema bai Husain bhai Daya</v>
       </c>
       <c r="E346" t="str">
-        <v>20345106</v>
+        <v>50419406</v>
       </c>
       <c r="F346" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G346" t="str">
         <v/>
@@ -9196,88 +9367,88 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>1778659312652_400</v>
+        <v>1778659312652_196</v>
       </c>
       <c r="B347" t="str">
-        <v>401</v>
+        <v>197</v>
       </c>
       <c r="C347" t="str">
-        <v>166</v>
+        <v>1322</v>
       </c>
       <c r="D347" t="str">
-        <v>Munira bai Ali bhai Pachlasa wala</v>
+        <v>Fatema bai Husain bhai Natak</v>
       </c>
       <c r="E347" t="str">
-        <v>20318114</v>
+        <v>30366479</v>
       </c>
       <c r="F347" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G347" t="str">
-        <v/>
+        <v>Mohammed bhai sageer</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>1778659312652_401</v>
+        <v>1778659312652_399</v>
       </c>
       <c r="B348" t="str">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C348" t="str">
-        <v>873</v>
+        <v>1421</v>
       </c>
       <c r="D348" t="str">
-        <v>Munira bai Aliasgar bhai Baroda</v>
+        <v>Munavar bhai Abid bhai Bashi</v>
       </c>
       <c r="E348" t="str">
-        <v>30484804</v>
+        <v>20345106</v>
       </c>
       <c r="F348" t="str">
         <v>Given</v>
       </c>
       <c r="G348" t="str">
-        <v>yakuta bai gaba</v>
+        <v/>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>1778659312652_402</v>
+        <v>1778659312652_401</v>
       </c>
       <c r="B349" t="str">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C349" t="str">
-        <v>638</v>
+        <v>873</v>
       </c>
       <c r="D349" t="str">
-        <v>Munira bai Fakhruddin bhai Anwer</v>
+        <v>Munira bai Aliasgar bhai Baroda</v>
       </c>
       <c r="E349" t="str">
-        <v>20318384</v>
+        <v>30484804</v>
       </c>
       <c r="F349" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G349" t="str">
-        <v/>
+        <v>yakuta bai gaba</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>1778659312652_403</v>
+        <v>1778659312652_402</v>
       </c>
       <c r="B350" t="str">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C350" t="str">
-        <v>1051</v>
+        <v>638</v>
       </c>
       <c r="D350" t="str">
-        <v>Munira bai Firoz bhai Gadiwala</v>
+        <v>Munira bai Fakhruddin bhai Anwer</v>
       </c>
       <c r="E350" t="str">
-        <v>20318667</v>
+        <v>20318384</v>
       </c>
       <c r="F350" t="str">
         <v>Pending</v>
@@ -9288,19 +9459,19 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>1778659312652_404</v>
+        <v>1778659312652_403</v>
       </c>
       <c r="B351" t="str">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C351" t="str">
-        <v>1258</v>
+        <v>1051</v>
       </c>
       <c r="D351" t="str">
-        <v>Munira bai Firoz bhai Mullah</v>
+        <v>Munira bai Firoz bhai Gadiwala</v>
       </c>
       <c r="E351" t="str">
-        <v>30919261</v>
+        <v>20318667</v>
       </c>
       <c r="F351" t="str">
         <v>Pending</v>
@@ -9311,19 +9482,19 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>1778659312652_405</v>
+        <v>1778659312652_404</v>
       </c>
       <c r="B352" t="str">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C352" t="str">
-        <v>622</v>
+        <v>1258</v>
       </c>
       <c r="D352" t="str">
-        <v>Munira bai Huseini bhai Kutbi</v>
+        <v>Munira bai Firoz bhai Mullah</v>
       </c>
       <c r="E352" t="str">
-        <v>20318375</v>
+        <v>30919261</v>
       </c>
       <c r="F352" t="str">
         <v>Pending</v>
@@ -9334,19 +9505,19 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>1778659312652_406</v>
+        <v>1778659312652_405</v>
       </c>
       <c r="B353" t="str">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C353" t="str">
-        <v>849</v>
+        <v>622</v>
       </c>
       <c r="D353" t="str">
-        <v>Munira bai Mohammed bhai Tutawala</v>
+        <v>Munira bai Huseini bhai Kutbi</v>
       </c>
       <c r="E353" t="str">
-        <v>30366900</v>
+        <v>20318375</v>
       </c>
       <c r="F353" t="str">
         <v>Pending</v>
@@ -9357,111 +9528,111 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>1778659312652_407</v>
+        <v>1778659312652_406</v>
       </c>
       <c r="B354" t="str">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C354" t="str">
-        <v>984</v>
+        <v>849</v>
       </c>
       <c r="D354" t="str">
-        <v>Munira bai Mustafa bhai Bhura</v>
+        <v>Munira bai Mohammed bhai Tutawala</v>
       </c>
       <c r="E354" t="str">
-        <v>30367153</v>
+        <v>30366900</v>
       </c>
       <c r="F354" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G354" t="str">
-        <v>Burhanuddin bhai peeth</v>
+        <v/>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>1778659312652_408</v>
+        <v>1778659312652_407</v>
       </c>
       <c r="B355" t="str">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C355" t="str">
-        <v>204</v>
+        <v>984</v>
       </c>
       <c r="D355" t="str">
-        <v>Munira bai Qutbuddin bhai Thakarda</v>
+        <v>Munira bai Mustafa bhai Bhura</v>
       </c>
       <c r="E355" t="str">
-        <v>20318078</v>
+        <v>30367153</v>
       </c>
       <c r="F355" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G355" t="str">
-        <v/>
+        <v>Burhanuddin bhai peeth</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>1778659312652_40</v>
+        <v>1778659312652_408</v>
       </c>
       <c r="B356" t="str">
-        <v>41</v>
+        <v>409</v>
       </c>
       <c r="C356" t="str">
-        <v>851</v>
+        <v>204</v>
       </c>
       <c r="D356" t="str">
-        <v>Ajab bai Yusuf bhai Alikaka</v>
+        <v>Munira bai Qutbuddin bhai Thakarda</v>
       </c>
       <c r="E356" t="str">
-        <v>30367338</v>
+        <v>20318078</v>
       </c>
       <c r="F356" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G356" t="str">
-        <v>Given to Kutub bhai bhura</v>
+        <v/>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>1778659312652_409</v>
+        <v>1778659312652_40</v>
       </c>
       <c r="B357" t="str">
-        <v>410</v>
+        <v>41</v>
       </c>
       <c r="C357" t="str">
-        <v>1256</v>
+        <v>851</v>
       </c>
       <c r="D357" t="str">
-        <v>Murtaza bhai Nooruddin bhai Parmar</v>
+        <v>Ajab bai Yusuf bhai Alikaka</v>
       </c>
       <c r="E357" t="str">
-        <v>40467550</v>
+        <v>30367338</v>
       </c>
       <c r="F357" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G357" t="str">
-        <v/>
+        <v>Given to Kutub bhai bhura</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>1778659312652_410</v>
+        <v>1778659312652_409</v>
       </c>
       <c r="B358" t="str">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C358" t="str">
-        <v>346</v>
+        <v>1256</v>
       </c>
       <c r="D358" t="str">
-        <v>Murtaza bhai Shabbir bhai Karbalai</v>
+        <v>Murtaza bhai Nooruddin bhai Parmar</v>
       </c>
       <c r="E358" t="str">
-        <v>20406934</v>
+        <v>40467550</v>
       </c>
       <c r="F358" t="str">
         <v>Pending</v>
@@ -9472,19 +9643,19 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>1778659312652_411</v>
+        <v>1778659312652_410</v>
       </c>
       <c r="B359" t="str">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C359" t="str">
-        <v>1194</v>
+        <v>346</v>
       </c>
       <c r="D359" t="str">
-        <v>Murtaza bhai Shaikh Mohammadhussain bhai Badri</v>
+        <v>Murtaza bhai Shabbir bhai Karbalai</v>
       </c>
       <c r="E359" t="str">
-        <v>30341651</v>
+        <v>20406934</v>
       </c>
       <c r="F359" t="str">
         <v>Pending</v>
@@ -10151,66 +10322,57 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>1778659312652_660</v>
+        <v>1778659312652_638</v>
       </c>
       <c r="B385" t="str">
-        <v>661</v>
+        <v>639</v>
       </c>
       <c r="C385" t="str">
-        <v>64</v>
+        <v>168</v>
       </c>
       <c r="D385" t="str">
-        <v>Sugra bai Fakhruddin bhai Gabruwala</v>
+        <v>Shaikh Shabbir bhai Qadirali bhai Jawadjya</v>
       </c>
       <c r="E385" t="str">
-        <v>20318686</v>
+        <v>20318112</v>
       </c>
       <c r="F385" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G385" t="str">
-        <v>shkh fakhruddin badi</v>
-      </c>
-      <c r="H385" t="str">
-        <v>23/05/2026</v>
-      </c>
-      <c r="I385" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="J385" t="str">
-        <v>10:59:21</v>
+        <v/>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>1778659312652_654</v>
+        <v>1778659312652_660</v>
       </c>
       <c r="B386" t="str">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="C386" t="str">
-        <v>427</v>
+        <v>64</v>
       </c>
       <c r="D386" t="str">
-        <v>Shireen bai Taherali bhai Peeth</v>
+        <v>Sugra bai Fakhruddin bhai Gabruwala</v>
       </c>
       <c r="E386" t="str">
-        <v>20318682</v>
+        <v>20318686</v>
       </c>
       <c r="F386" t="str">
         <v>Given</v>
       </c>
       <c r="G386" t="str">
-        <v>Fatema bai Husain bhai Mukadamvv</v>
+        <v>shkh fakhruddin badi</v>
       </c>
       <c r="H386" t="str">
-        <v>20/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="I386" t="str">
-        <v>Wednesday</v>
+        <v>Saturday</v>
       </c>
       <c r="J386" t="str">
-        <v>12:31:57</v>
+        <v>10:59:21</v>
       </c>
     </row>
     <row r="387">
@@ -10230,50 +10392,68 @@
         <v>20361906</v>
       </c>
       <c r="F387" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G387" t="str">
         <v/>
+      </c>
+      <c r="H387" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I387" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J387" t="str">
+        <v>12:24:11</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>1778659312652_636</v>
+        <v>1778659312652_654</v>
       </c>
       <c r="B388" t="str">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="C388" t="str">
-        <v>539</v>
+        <v>427</v>
       </c>
       <c r="D388" t="str">
-        <v>Shaikh Saifuddin bhai Qurbanhusain bhai Soni</v>
+        <v>Shireen bai Taherali bhai Peeth</v>
       </c>
       <c r="E388" t="str">
-        <v>20318325</v>
+        <v>20318682</v>
       </c>
       <c r="F388" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G388" t="str">
-        <v/>
+        <v>Fatema bai Husain bhai Mukadamvv</v>
+      </c>
+      <c r="H388" t="str">
+        <v>20/05/2026</v>
+      </c>
+      <c r="I388" t="str">
+        <v>Wednesday</v>
+      </c>
+      <c r="J388" t="str">
+        <v>12:31:57</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>1778659312652_637</v>
+        <v>1778659312652_636</v>
       </c>
       <c r="B389" t="str">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C389" t="str">
-        <v>965</v>
+        <v>539</v>
       </c>
       <c r="D389" t="str">
-        <v>Shaikh Shabbar bhai Mulla Taherali bhai Asif</v>
+        <v>Shaikh Saifuddin bhai Qurbanhusain bhai Soni</v>
       </c>
       <c r="E389" t="str">
-        <v>20318591</v>
+        <v>20318325</v>
       </c>
       <c r="F389" t="str">
         <v>Pending</v>
@@ -10284,19 +10464,19 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>1778659312652_638</v>
+        <v>1778659312652_637</v>
       </c>
       <c r="B390" t="str">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C390" t="str">
-        <v>168</v>
+        <v>965</v>
       </c>
       <c r="D390" t="str">
-        <v>Shaikh Shabbir bhai Qadirali bhai Jawadjya</v>
+        <v>Shaikh Shabbar bhai Mulla Taherali bhai Asif</v>
       </c>
       <c r="E390" t="str">
-        <v>20318112</v>
+        <v>20318591</v>
       </c>
       <c r="F390" t="str">
         <v>Pending</v>
@@ -10808,230 +10988,239 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>1778659312652_268</v>
+        <v>1778659312652_693</v>
       </c>
       <c r="B412" t="str">
-        <v>269</v>
+        <v>694</v>
       </c>
       <c r="C412" t="str">
-        <v>862</v>
+        <v>875</v>
       </c>
       <c r="D412" t="str">
-        <v>Husain bhai Alihusain bhai Aluda</v>
+        <v>Tasneem bai Saifuddin bhai Geyoriwala</v>
       </c>
       <c r="E412" t="str">
-        <v>20352317</v>
+        <v>20318696</v>
       </c>
       <c r="F412" t="str">
         <v>Given</v>
       </c>
       <c r="G412" t="str">
-        <v>Tasneem bai Yusuf bhai Rail</v>
+        <v/>
+      </c>
+      <c r="H412" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I412" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J412" t="str">
+        <v>11:08:17</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>1778659312652_691</v>
+        <v>1778659312652_268</v>
       </c>
       <c r="B413" t="str">
-        <v>692</v>
+        <v>269</v>
       </c>
       <c r="C413" t="str">
-        <v>794</v>
+        <v>862</v>
       </c>
       <c r="D413" t="str">
-        <v>Tasneem bai Qutbuddin bhai Tutawala</v>
+        <v>Husain bhai Alihusain bhai Aluda</v>
       </c>
       <c r="E413" t="str">
-        <v>30367468</v>
+        <v>20352317</v>
       </c>
       <c r="F413" t="str">
         <v>Given</v>
       </c>
       <c r="G413" t="str">
-        <v>shkh fakhruddin badi</v>
-      </c>
-      <c r="H413" t="str">
-        <v>20/05/2026</v>
-      </c>
-      <c r="I413" t="str">
-        <v>Wednesday</v>
-      </c>
-      <c r="J413" t="str">
-        <v>12:39:46</v>
+        <v>Tasneem bai Yusuf bhai Rail</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>1778659312652_26</v>
+        <v>1778659312652_691</v>
       </c>
       <c r="B414" t="str">
-        <v>27</v>
+        <v>692</v>
       </c>
       <c r="C414" t="str">
-        <v>1235</v>
+        <v>794</v>
       </c>
       <c r="D414" t="str">
-        <v>Ajab bai Jafar bhai Jariwala</v>
+        <v>Tasneem bai Qutbuddin bhai Tutawala</v>
       </c>
       <c r="E414" t="str">
-        <v>20318806</v>
+        <v>30367468</v>
       </c>
       <c r="F414" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G414" t="str">
-        <v/>
+        <v>shkh fakhruddin badi</v>
+      </c>
+      <c r="H414" t="str">
+        <v>20/05/2026</v>
+      </c>
+      <c r="I414" t="str">
+        <v>Wednesday</v>
+      </c>
+      <c r="J414" t="str">
+        <v>12:39:46</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>1778659312652_269</v>
+        <v>1778659312652_26</v>
       </c>
       <c r="B415" t="str">
-        <v>270</v>
+        <v>27</v>
       </c>
       <c r="C415" t="str">
-        <v>1395</v>
+        <v>1235</v>
       </c>
       <c r="D415" t="str">
-        <v>Husain bhai Alihusain bhai Kawja</v>
+        <v>Ajab bai Jafar bhai Jariwala</v>
       </c>
       <c r="E415" t="str">
-        <v>30367333</v>
+        <v>20318806</v>
       </c>
       <c r="F415" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G415" t="str">
-        <v>Rehena ben Kawja</v>
-      </c>
-      <c r="H415" t="str">
-        <v>18/05/2026</v>
-      </c>
-      <c r="I415" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="J415" t="str">
-        <v>11:37:50</v>
+        <v/>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>1778659312652_680</v>
+        <v>1778659312652_269</v>
       </c>
       <c r="B416" t="str">
-        <v>681</v>
+        <v>270</v>
       </c>
       <c r="C416" t="str">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="D416" t="str">
-        <v>Tasneem bai Aliasgar bhai Obriwala</v>
+        <v>Husain bhai Alihusain bhai Kawja</v>
       </c>
       <c r="E416" t="str">
-        <v>30366898</v>
+        <v>30367333</v>
       </c>
       <c r="F416" t="str">
         <v>Given</v>
       </c>
       <c r="G416" t="str">
-        <v/>
+        <v>Rehena ben Kawja</v>
       </c>
       <c r="H416" t="str">
-        <v>21/05/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="I416" t="str">
-        <v>Thursday</v>
+        <v>Monday</v>
       </c>
       <c r="J416" t="str">
-        <v>10:23:44</v>
+        <v>11:37:50</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>1778659312652_270</v>
+        <v>1778659312652_680</v>
       </c>
       <c r="B417" t="str">
-        <v>271</v>
+        <v>681</v>
       </c>
       <c r="C417" t="str">
-        <v>773</v>
+        <v>1382</v>
       </c>
       <c r="D417" t="str">
-        <v>Husain bhai Alihusain bhai Nanuji</v>
+        <v>Tasneem bai Aliasgar bhai Obriwala</v>
       </c>
       <c r="E417" t="str">
-        <v>20318485</v>
+        <v>30366898</v>
       </c>
       <c r="F417" t="str">
         <v>Given</v>
       </c>
       <c r="G417" t="str">
-        <v>Zainab ben Khandi</v>
+        <v/>
+      </c>
+      <c r="H417" t="str">
+        <v>21/05/2026</v>
+      </c>
+      <c r="I417" t="str">
+        <v>Thursday</v>
+      </c>
+      <c r="J417" t="str">
+        <v>10:23:44</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>1778659312652_674</v>
+        <v>1778659312652_270</v>
       </c>
       <c r="B418" t="str">
-        <v>675</v>
+        <v>271</v>
       </c>
       <c r="C418" t="str">
-        <v>126</v>
+        <v>773</v>
       </c>
       <c r="D418" t="str">
-        <v>Taiyebali bhai Alihusain bhai Khajuri</v>
+        <v>Husain bhai Alihusain bhai Nanuji</v>
       </c>
       <c r="E418" t="str">
-        <v>20406912</v>
+        <v>20318485</v>
       </c>
       <c r="F418" t="str">
         <v>Given</v>
       </c>
       <c r="G418" t="str">
-        <v>Ammar bhai damri</v>
+        <v>Zainab ben Khandi</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>1778659312652_676</v>
+        <v>1778659312652_674</v>
       </c>
       <c r="B419" t="str">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C419" t="str">
-        <v/>
+        <v>126</v>
       </c>
       <c r="D419" t="str">
-        <v>Talib bhai Abdeali bhai Rangwala</v>
+        <v>Taiyebali bhai Alihusain bhai Khajuri</v>
       </c>
       <c r="E419" t="str">
-        <v>20438605</v>
+        <v>20406912</v>
       </c>
       <c r="F419" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G419" t="str">
-        <v/>
+        <v>Ammar bhai damri</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>1778659312652_677</v>
+        <v>1778659312652_676</v>
       </c>
       <c r="B420" t="str">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C420" t="str">
-        <v>1198</v>
+        <v/>
       </c>
       <c r="D420" t="str">
-        <v>Talib bhai Mohamed bhai Gheewala</v>
+        <v>Talib bhai Abdeali bhai Rangwala</v>
       </c>
       <c r="E420" t="str">
-        <v>30140026</v>
+        <v>20438605</v>
       </c>
       <c r="F420" t="str">
         <v>Pending</v>
@@ -11042,83 +11231,74 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>1778659312652_679</v>
+        <v>1778659312652_677</v>
       </c>
       <c r="B421" t="str">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C421" t="str">
-        <v>1056</v>
+        <v>1198</v>
       </c>
       <c r="D421" t="str">
-        <v>Tasneem bai Abedin bhai Jiger</v>
+        <v>Talib bhai Mohamed bhai Gheewala</v>
       </c>
       <c r="E421" t="str">
-        <v>60446474</v>
+        <v>30140026</v>
       </c>
       <c r="F421" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G421" t="str">
-        <v>Abbas obri</v>
-      </c>
-      <c r="H421" t="str">
-        <v>22/05/2026</v>
-      </c>
-      <c r="I421" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J421" t="str">
-        <v>11:58:32</v>
+        <v/>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>1778659312652_694</v>
+        <v>1778659312652_679</v>
       </c>
       <c r="B422" t="str">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="C422" t="str">
-        <v>164</v>
+        <v>1056</v>
       </c>
       <c r="D422" t="str">
-        <v>Tasneem bai Saifuddin bhai Obri</v>
+        <v>Tasneem bai Abedin bhai Jiger</v>
       </c>
       <c r="E422" t="str">
-        <v>30488804</v>
+        <v>60446474</v>
       </c>
       <c r="F422" t="str">
         <v>Given</v>
       </c>
       <c r="G422" t="str">
-        <v/>
+        <v>Abbas obri</v>
       </c>
       <c r="H422" t="str">
-        <v>23/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="I422" t="str">
-        <v>Saturday</v>
+        <v>Friday</v>
       </c>
       <c r="J422" t="str">
-        <v>10:42:58</v>
+        <v>11:58:32</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>1778659312652_675</v>
+        <v>1778659312652_694</v>
       </c>
       <c r="B423" t="str">
-        <v>676</v>
+        <v>695</v>
       </c>
       <c r="C423" t="str">
-        <v>606</v>
+        <v>164</v>
       </c>
       <c r="D423" t="str">
-        <v>Taiyebali bhai Haiderali bhai Lohagadwala</v>
+        <v>Tasneem bai Saifuddin bhai Obri</v>
       </c>
       <c r="E423" t="str">
-        <v>20364757</v>
+        <v>30488804</v>
       </c>
       <c r="F423" t="str">
         <v>Given</v>
@@ -11133,24 +11313,24 @@
         <v>Saturday</v>
       </c>
       <c r="J423" t="str">
-        <v>11:04:13</v>
+        <v>10:42:58</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>1778659312652_684</v>
+        <v>1778659312652_675</v>
       </c>
       <c r="B424" t="str">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="C424" t="str">
-        <v>1172</v>
+        <v>606</v>
       </c>
       <c r="D424" t="str">
-        <v>Tasneem bai Mohammed bhai Fata</v>
+        <v>Taiyebali bhai Haiderali bhai Lohagadwala</v>
       </c>
       <c r="E424" t="str">
-        <v>30366542</v>
+        <v>20364757</v>
       </c>
       <c r="F424" t="str">
         <v>Given</v>
@@ -11165,47 +11345,56 @@
         <v>Saturday</v>
       </c>
       <c r="J424" t="str">
-        <v>11:26:39</v>
+        <v>11:04:13</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>1778659312652_678</v>
+        <v>1778659312652_684</v>
       </c>
       <c r="B425" t="str">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="C425" t="str">
-        <v>1</v>
+        <v>1172</v>
       </c>
       <c r="D425" t="str">
-        <v>Tasneem bai Abdemanaf bhai Sagir</v>
+        <v>Tasneem bai Mohammed bhai Fata</v>
       </c>
       <c r="E425" t="str">
-        <v>30360101</v>
+        <v>30366542</v>
       </c>
       <c r="F425" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G425" t="str">
         <v/>
+      </c>
+      <c r="H425" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I425" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J425" t="str">
+        <v>11:26:39</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>1778659312652_67</v>
+        <v>1778659312652_678</v>
       </c>
       <c r="B426" t="str">
-        <v>68</v>
+        <v>679</v>
       </c>
       <c r="C426" t="str">
-        <v>589</v>
+        <v>1</v>
       </c>
       <c r="D426" t="str">
-        <v>Arwa bai Huseini bhai Tutawala</v>
+        <v>Tasneem bai Abdemanaf bhai Sagir</v>
       </c>
       <c r="E426" t="str">
-        <v>20318775</v>
+        <v>30360101</v>
       </c>
       <c r="F426" t="str">
         <v>Pending</v>
@@ -11216,19 +11405,19 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>1778659312652_682</v>
+        <v>1778659312652_67</v>
       </c>
       <c r="B427" t="str">
-        <v>683</v>
+        <v>68</v>
       </c>
       <c r="C427" t="str">
-        <v>430</v>
+        <v>589</v>
       </c>
       <c r="D427" t="str">
-        <v>Tasneem bai Ibrahim bhai Peeth wala</v>
+        <v>Arwa bai Huseini bhai Tutawala</v>
       </c>
       <c r="E427" t="str">
-        <v>20318268</v>
+        <v>20318775</v>
       </c>
       <c r="F427" t="str">
         <v>Pending</v>
@@ -11239,19 +11428,19 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>1778659312652_683</v>
+        <v>1778659312652_682</v>
       </c>
       <c r="B428" t="str">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C428" t="str">
-        <v>1297</v>
+        <v>430</v>
       </c>
       <c r="D428" t="str">
-        <v>Tasneem bai Juzer bhai Daliwala</v>
+        <v>Tasneem bai Ibrahim bhai Peeth wala</v>
       </c>
       <c r="E428" t="str">
-        <v>30461063</v>
+        <v>20318268</v>
       </c>
       <c r="F428" t="str">
         <v>Pending</v>
@@ -11262,19 +11451,19 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>1778659312652_685</v>
+        <v>1778659312652_683</v>
       </c>
       <c r="B429" t="str">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C429" t="str">
-        <v>257</v>
+        <v>1297</v>
       </c>
       <c r="D429" t="str">
-        <v>Tasneem bai Mohammed bhai Ramkada</v>
+        <v>Tasneem bai Juzer bhai Daliwala</v>
       </c>
       <c r="E429" t="str">
-        <v>30366509</v>
+        <v>30461063</v>
       </c>
       <c r="F429" t="str">
         <v>Pending</v>
@@ -11285,19 +11474,19 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>1778659312652_686</v>
+        <v>1778659312652_685</v>
       </c>
       <c r="B430" t="str">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C430" t="str">
-        <v>433</v>
+        <v>257</v>
       </c>
       <c r="D430" t="str">
-        <v>Tasneem bai Munavar bhai Obriwala</v>
+        <v>Tasneem bai Mohammed bhai Ramkada</v>
       </c>
       <c r="E430" t="str">
-        <v>30367289</v>
+        <v>30366509</v>
       </c>
       <c r="F430" t="str">
         <v>Pending</v>
@@ -11308,19 +11497,19 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>1778659312652_687</v>
+        <v>1778659312652_686</v>
       </c>
       <c r="B431" t="str">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C431" t="str">
-        <v>1494</v>
+        <v>433</v>
       </c>
       <c r="D431" t="str">
-        <v>Tasneem bai Murtaza bhai Daya</v>
+        <v>Tasneem bai Munavar bhai Obriwala</v>
       </c>
       <c r="E431" t="str">
-        <v>30367339</v>
+        <v>30367289</v>
       </c>
       <c r="F431" t="str">
         <v>Pending</v>
@@ -11331,120 +11520,120 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>1778659312652_688</v>
+        <v>1778659312652_687</v>
       </c>
       <c r="B432" t="str">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C432" t="str">
-        <v>438</v>
+        <v>1494</v>
       </c>
       <c r="D432" t="str">
-        <v>Tasneem bai Nooruddin bhai Miyaji</v>
+        <v>Tasneem bai Murtaza bhai Daya</v>
       </c>
       <c r="E432" t="str">
-        <v>30366859</v>
+        <v>30367339</v>
       </c>
       <c r="F432" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G432" t="str">
-        <v>Nasa bhai</v>
+        <v/>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>1778659312652_68</v>
+        <v>1778659312652_688</v>
       </c>
       <c r="B433" t="str">
-        <v>69</v>
+        <v>689</v>
       </c>
       <c r="C433" t="str">
-        <v>1320</v>
+        <v>438</v>
       </c>
       <c r="D433" t="str">
-        <v>Arwa bai Qutbuddin bhai Varda</v>
+        <v>Tasneem bai Nooruddin bhai Miyaji</v>
       </c>
       <c r="E433" t="str">
-        <v>30496926</v>
+        <v>30366859</v>
       </c>
       <c r="F433" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G433" t="str">
-        <v/>
+        <v>Nasa bhai</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>1778659312652_689</v>
+        <v>1778659312652_68</v>
       </c>
       <c r="B434" t="str">
-        <v>690</v>
+        <v>69</v>
       </c>
       <c r="C434" t="str">
-        <v>354</v>
+        <v>1320</v>
       </c>
       <c r="D434" t="str">
-        <v>Tasneem bai Quaidjohar bhai Burhani (Natak)</v>
+        <v>Arwa bai Qutbuddin bhai Varda</v>
       </c>
       <c r="E434" t="str">
-        <v>20318206</v>
+        <v>30496926</v>
       </c>
       <c r="F434" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G434" t="str">
         <v/>
-      </c>
-      <c r="H434" t="str">
-        <v>16/05/2026</v>
-      </c>
-      <c r="I434" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="J434" t="str">
-        <v>12:50:34</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>1778659312652_690</v>
+        <v>1778659312652_689</v>
       </c>
       <c r="B435" t="str">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C435" t="str">
-        <v>279</v>
+        <v>354</v>
       </c>
       <c r="D435" t="str">
-        <v>Tasneem bai Qutbuddin bhai Miyaji</v>
+        <v>Tasneem bai Quaidjohar bhai Burhani (Natak)</v>
       </c>
       <c r="E435" t="str">
-        <v>30366529</v>
+        <v>20318206</v>
       </c>
       <c r="F435" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G435" t="str">
         <v/>
+      </c>
+      <c r="H435" t="str">
+        <v>16/05/2026</v>
+      </c>
+      <c r="I435" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J435" t="str">
+        <v>12:50:34</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>1778659312652_692</v>
+        <v>1778659312652_690</v>
       </c>
       <c r="B436" t="str">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C436" t="str">
-        <v>1447</v>
+        <v>279</v>
       </c>
       <c r="D436" t="str">
-        <v>Tasneem bai Qutubkhan bhai Firangi</v>
+        <v>Tasneem bai Qutbuddin bhai Miyaji</v>
       </c>
       <c r="E436" t="str">
-        <v>30490387</v>
+        <v>30366529</v>
       </c>
       <c r="F436" t="str">
         <v>Pending</v>
@@ -11455,19 +11644,19 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>1778659312652_693</v>
+        <v>1778659312652_692</v>
       </c>
       <c r="B437" t="str">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C437" t="str">
-        <v>875</v>
+        <v>1447</v>
       </c>
       <c r="D437" t="str">
-        <v>Tasneem bai Saifuddin bhai Geyoriwala</v>
+        <v>Tasneem bai Qutubkhan bhai Firangi</v>
       </c>
       <c r="E437" t="str">
-        <v>20318696</v>
+        <v>30490387</v>
       </c>
       <c r="F437" t="str">
         <v>Pending</v>
@@ -11703,57 +11892,66 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>1778659312652_441</v>
+        <v>1778659312652_425</v>
       </c>
       <c r="B447" t="str">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="C447" t="str">
-        <v>1020</v>
+        <v>211</v>
       </c>
       <c r="D447" t="str">
-        <v>Nisreen bai Abbas bhai Pachlasa</v>
+        <v>Nafisa bai Husain bhai Patra</v>
       </c>
       <c r="E447" t="str">
-        <v>30487054</v>
+        <v>20318710</v>
       </c>
       <c r="F447" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G447" t="str">
         <v/>
+      </c>
+      <c r="H447" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I447" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J447" t="str">
+        <v>11:33:26</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>1778659312652_425</v>
+        <v>1778659312652_441</v>
       </c>
       <c r="B448" t="str">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="C448" t="str">
-        <v>211</v>
+        <v>1020</v>
       </c>
       <c r="D448" t="str">
-        <v>Nafisa bai Husain bhai Patra</v>
+        <v>Nisreen bai Abbas bhai Pachlasa</v>
       </c>
       <c r="E448" t="str">
-        <v>20318710</v>
+        <v>30487054</v>
       </c>
       <c r="F448" t="str">
         <v>Given</v>
       </c>
       <c r="G448" t="str">
-        <v/>
+        <v>Hussain bhai hathai</v>
       </c>
       <c r="H448" t="str">
-        <v>23/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="I448" t="str">
-        <v>Saturday</v>
+        <v>Monday</v>
       </c>
       <c r="J448" t="str">
-        <v>11:33:26</v>
+        <v>11:10:04</v>
       </c>
     </row>
     <row r="449">
@@ -11914,45 +12112,54 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>1778659312652_503</v>
+        <v>1778659312652_501</v>
       </c>
       <c r="B455" t="str">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C455" t="str">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="D455" t="str">
-        <v>Saifuddin bhai Shaikh Mohammed bhai Peethwala</v>
+        <v>Saifuddin bhai Qurbanhusain bhai Hathai</v>
       </c>
       <c r="E455" t="str">
-        <v>20318773</v>
+        <v>20318735</v>
       </c>
       <c r="F455" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G455" t="str">
         <v/>
+      </c>
+      <c r="H455" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I455" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J455" t="str">
+        <v>10:35:36</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>1778659312652_504</v>
+        <v>1778659312652_503</v>
       </c>
       <c r="B456" t="str">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C456" t="str">
-        <v>552</v>
+        <v>141</v>
       </c>
       <c r="D456" t="str">
-        <v>Saifuddin bhai Taiyebali bhai Rangwala</v>
+        <v>Saifuddin bhai Shaikh Mohammed bhai Peethwala</v>
       </c>
       <c r="E456" t="str">
-        <v>20437020</v>
+        <v>20318773</v>
       </c>
       <c r="F456" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G456" t="str">
         <v/>
@@ -11960,22 +12167,22 @@
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>1778659312652_505</v>
+        <v>1778659312652_504</v>
       </c>
       <c r="B457" t="str">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C457" t="str">
-        <v>909</v>
+        <v>552</v>
       </c>
       <c r="D457" t="str">
-        <v>Sajjad bhai Fakhruddin bhai Obri</v>
+        <v>Saifuddin bhai Taiyebali bhai Rangwala</v>
       </c>
       <c r="E457" t="str">
-        <v>20318579</v>
+        <v>20437020</v>
       </c>
       <c r="F457" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G457" t="str">
         <v/>
@@ -11983,19 +12190,19 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>1778659312652_506</v>
+        <v>1778659312652_505</v>
       </c>
       <c r="B458" t="str">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C458" t="str">
-        <v>695</v>
+        <v>909</v>
       </c>
       <c r="D458" t="str">
-        <v>Sajjad bhai Ismail bhai Kothi</v>
+        <v>Sajjad bhai Fakhruddin bhai Obri</v>
       </c>
       <c r="E458" t="str">
-        <v>20318694</v>
+        <v>20318579</v>
       </c>
       <c r="F458" t="str">
         <v>Pending</v>
@@ -12006,19 +12213,19 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>1778659312652_507</v>
+        <v>1778659312652_506</v>
       </c>
       <c r="B459" t="str">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C459" t="str">
-        <v>93</v>
+        <v>695</v>
       </c>
       <c r="D459" t="str">
-        <v>Sakina bai Aashiqhusain bhai Ujjain</v>
+        <v>Sajjad bhai Ismail bhai Kothi</v>
       </c>
       <c r="E459" t="str">
-        <v>30368104</v>
+        <v>20318694</v>
       </c>
       <c r="F459" t="str">
         <v>Pending</v>
@@ -12029,19 +12236,19 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>1778659312652_508</v>
+        <v>1778659312652_507</v>
       </c>
       <c r="B460" t="str">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C460" t="str">
-        <v>748</v>
+        <v>93</v>
       </c>
       <c r="D460" t="str">
-        <v>Sakina bai Abbas bhai Kallu</v>
+        <v>Sakina bai Aashiqhusain bhai Ujjain</v>
       </c>
       <c r="E460" t="str">
-        <v>30367368</v>
+        <v>30368104</v>
       </c>
       <c r="F460" t="str">
         <v>Pending</v>
@@ -12052,19 +12259,19 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>1778659312652_50</v>
+        <v>1778659312652_508</v>
       </c>
       <c r="B461" t="str">
-        <v>51</v>
+        <v>509</v>
       </c>
       <c r="C461" t="str">
-        <v>1191</v>
+        <v>748</v>
       </c>
       <c r="D461" t="str">
-        <v>Alefiyah bai Moiz bhai Obriwala</v>
+        <v>Sakina bai Abbas bhai Kallu</v>
       </c>
       <c r="E461" t="str">
-        <v>20318797</v>
+        <v>30367368</v>
       </c>
       <c r="F461" t="str">
         <v>Pending</v>
@@ -12075,19 +12282,19 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>1778659312652_509</v>
+        <v>1778659312652_50</v>
       </c>
       <c r="B462" t="str">
-        <v>510</v>
+        <v>51</v>
       </c>
       <c r="C462" t="str">
-        <v>941</v>
+        <v>1191</v>
       </c>
       <c r="D462" t="str">
-        <v>Sakina bai Abbas bhai Kothari</v>
+        <v>Alefiyah bai Moiz bhai Obriwala</v>
       </c>
       <c r="E462" t="str">
-        <v>20318481</v>
+        <v>20318797</v>
       </c>
       <c r="F462" t="str">
         <v>Pending</v>
@@ -12098,19 +12305,19 @@
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>1778659312652_510</v>
+        <v>1778659312652_509</v>
       </c>
       <c r="B463" t="str">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C463" t="str">
-        <v>1240</v>
+        <v>941</v>
       </c>
       <c r="D463" t="str">
-        <v>Sakina bai Abbas bhai Sidhpurwala</v>
+        <v>Sakina bai Abbas bhai Kothari</v>
       </c>
       <c r="E463" t="str">
-        <v>30368306</v>
+        <v>20318481</v>
       </c>
       <c r="F463" t="str">
         <v>Pending</v>
@@ -12121,19 +12328,19 @@
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>1778659312652_511</v>
+        <v>1778659312652_510</v>
       </c>
       <c r="B464" t="str">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C464" t="str">
-        <v>994</v>
+        <v>1240</v>
       </c>
       <c r="D464" t="str">
-        <v>Sakina bai Abbasali bhai Topiwala</v>
+        <v>Sakina bai Abbas bhai Sidhpurwala</v>
       </c>
       <c r="E464" t="str">
-        <v>20318782</v>
+        <v>30368306</v>
       </c>
       <c r="F464" t="str">
         <v>Pending</v>
@@ -12144,19 +12351,19 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>1778659312652_512</v>
+        <v>1778659312652_511</v>
       </c>
       <c r="B465" t="str">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C465" t="str">
-        <v>158</v>
+        <v>994</v>
       </c>
       <c r="D465" t="str">
-        <v>Sakina bai Abdulhusain bhai Pachlasa</v>
+        <v>Sakina bai Abbasali bhai Topiwala</v>
       </c>
       <c r="E465" t="str">
-        <v>20318107</v>
+        <v>20318782</v>
       </c>
       <c r="F465" t="str">
         <v>Pending</v>
@@ -12167,19 +12374,19 @@
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>1778659312652_514</v>
+        <v>1778659312652_512</v>
       </c>
       <c r="B466" t="str">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C466" t="str">
-        <v>1219</v>
+        <v>158</v>
       </c>
       <c r="D466" t="str">
-        <v>Sakina bai Abdullah bhai Teen</v>
+        <v>Sakina bai Abdulhusain bhai Pachlasa</v>
       </c>
       <c r="E466" t="str">
-        <v>30368243</v>
+        <v>20318107</v>
       </c>
       <c r="F466" t="str">
         <v>Pending</v>
@@ -12190,120 +12397,120 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>1778659312652_516</v>
+        <v>1778659312652_514</v>
       </c>
       <c r="B467" t="str">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C467" t="str">
-        <v>1431</v>
+        <v>1219</v>
       </c>
       <c r="D467" t="str">
-        <v>Sakina bai Ahmedali bhai Pachlasawala</v>
+        <v>Sakina bai Abdullah bhai Teen</v>
       </c>
       <c r="E467" t="str">
-        <v>30360123</v>
+        <v>30368243</v>
       </c>
       <c r="F467" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G467" t="str">
         <v/>
-      </c>
-      <c r="H467" t="str">
-        <v>19/05/2026</v>
-      </c>
-      <c r="I467" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="J467" t="str">
-        <v>12:22:36</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>1778659312652_4</v>
+        <v>1778659312652_516</v>
       </c>
       <c r="B468" t="str">
-        <v>5</v>
+        <v>517</v>
       </c>
       <c r="C468" t="str">
-        <v>73</v>
+        <v>1431</v>
       </c>
       <c r="D468" t="str">
-        <v>Abbas bhai Alihusain bhai Kabriwala</v>
+        <v>Sakina bai Ahmedali bhai Pachlasawala</v>
       </c>
       <c r="E468" t="str">
-        <v>20438305</v>
+        <v>30360123</v>
       </c>
       <c r="F468" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G468" t="str">
         <v/>
+      </c>
+      <c r="H468" t="str">
+        <v>19/05/2026</v>
+      </c>
+      <c r="I468" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="J468" t="str">
+        <v>12:22:36</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>1778659312652_49</v>
+        <v>1778659312652_4</v>
       </c>
       <c r="B469" t="str">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="C469" t="str">
-        <v>923</v>
+        <v>73</v>
       </c>
       <c r="D469" t="str">
-        <v>Alefiyah bai Huzaifa bhai Dadabhai</v>
+        <v>Abbas bhai Alihusain bhai Kabriwala</v>
       </c>
       <c r="E469" t="str">
-        <v>30366812</v>
+        <v>20438305</v>
       </c>
       <c r="F469" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G469" t="str">
-        <v>Fatema ben barkat</v>
+        <v/>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>1778659312652_499</v>
+        <v>1778659312652_49</v>
       </c>
       <c r="B470" t="str">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C470" t="str">
-        <v>1061</v>
+        <v>923</v>
       </c>
       <c r="D470" t="str">
-        <v>Saifuddin bhai Mohammedhusain bhai Kothari</v>
+        <v>Alefiyah bai Huzaifa bhai Dadabhai</v>
       </c>
       <c r="E470" t="str">
-        <v>20348048</v>
+        <v>30366812</v>
       </c>
       <c r="F470" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G470" t="str">
-        <v/>
+        <v>Fatema ben barkat</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>1778659312652_500</v>
+        <v>1778659312652_499</v>
       </c>
       <c r="B471" t="str">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C471" t="str">
-        <v>6</v>
+        <v>1061</v>
       </c>
       <c r="D471" t="str">
-        <v>Saifuddin bhai Qadir bhai Kabri</v>
+        <v>Saifuddin bhai Mohammedhusain bhai Kothari</v>
       </c>
       <c r="E471" t="str">
-        <v>20318006</v>
+        <v>20348048</v>
       </c>
       <c r="F471" t="str">
         <v>Pending</v>
@@ -12314,19 +12521,19 @@
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>1778659312652_501</v>
+        <v>1778659312652_500</v>
       </c>
       <c r="B472" t="str">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C472" t="str">
-        <v>189</v>
+        <v>6</v>
       </c>
       <c r="D472" t="str">
-        <v>Saifuddin bhai Qurbanhusain bhai Hathai</v>
+        <v>Saifuddin bhai Qadir bhai Kabri</v>
       </c>
       <c r="E472" t="str">
-        <v>20318735</v>
+        <v>20318006</v>
       </c>
       <c r="F472" t="str">
         <v>Pending</v>
@@ -12967,10 +13174,19 @@
         <v>30360215</v>
       </c>
       <c r="F497" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G497" t="str">
-        <v/>
+        <v>Fatema ben Mulla Hakimuddin bhai sageer</v>
+      </c>
+      <c r="H497" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I497" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J497" t="str">
+        <v>10:53:51</v>
       </c>
     </row>
     <row r="498">
@@ -13296,143 +13512,179 @@
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>1778659312652_535</v>
+        <v>1778659312652_527</v>
       </c>
       <c r="B510" t="str">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="C510" t="str">
-        <v>443</v>
+        <v>1217</v>
       </c>
       <c r="D510" t="str">
-        <v>Sakina bai Fakhruddin bhai Tarawala</v>
+        <v>Sakina bai Fakhruddin bhai Javadiya</v>
       </c>
       <c r="E510" t="str">
-        <v>20318284</v>
+        <v>20371456</v>
       </c>
       <c r="F510" t="str">
         <v>Given</v>
       </c>
       <c r="G510" t="str">
-        <v>shkh fakhruddin badi</v>
+        <v/>
       </c>
       <c r="H510" t="str">
-        <v>23/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="I510" t="str">
-        <v>Saturday</v>
+        <v>Monday</v>
       </c>
       <c r="J510" t="str">
-        <v>10:59:06</v>
+        <v>10:49:34</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>1778659312652_525</v>
+        <v>1778659312652_526</v>
       </c>
       <c r="B511" t="str">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C511" t="str">
-        <v>59</v>
+        <v>1230</v>
       </c>
       <c r="D511" t="str">
-        <v>Sakina bai Fakhruddin bhai Bhura</v>
+        <v>Sakina bai Fakhruddin bhai Gadi</v>
       </c>
       <c r="E511" t="str">
-        <v>20318079</v>
+        <v>20318804</v>
       </c>
       <c r="F511" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G511" t="str">
-        <v/>
+        <v>Hussain bhai dada</v>
+      </c>
+      <c r="H511" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I511" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J511" t="str">
+        <v>11:06:07</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>1778659312652_526</v>
+        <v>1778659312652_529</v>
       </c>
       <c r="B512" t="str">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C512" t="str">
-        <v>1230</v>
+        <v>1488</v>
       </c>
       <c r="D512" t="str">
-        <v>Sakina bai Fakhruddin bhai Gadi</v>
+        <v>Sakina bai Fakhruddin bhai Kotwal</v>
       </c>
       <c r="E512" t="str">
-        <v>20318804</v>
+        <v>30368038</v>
       </c>
       <c r="F512" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G512" t="str">
         <v/>
+      </c>
+      <c r="H512" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I512" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J512" t="str">
+        <v>11:24:53</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>1778659312652_527</v>
+        <v>1778659312652_52</v>
       </c>
       <c r="B513" t="str">
-        <v>528</v>
+        <v>53</v>
       </c>
       <c r="C513" t="str">
-        <v>1217</v>
+        <v>1247</v>
       </c>
       <c r="D513" t="str">
-        <v>Sakina bai Fakhruddin bhai Javadiya</v>
+        <v>Alefiyah bai Saifuddin bhai Badshah</v>
       </c>
       <c r="E513" t="str">
-        <v>20371456</v>
+        <v>30360143</v>
       </c>
       <c r="F513" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G513" t="str">
-        <v/>
+        <v>Kutub bhai Gaba</v>
+      </c>
+      <c r="H513" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I513" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J513" t="str">
+        <v>12:04:47</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>1778659312652_528</v>
+        <v>1778659312652_535</v>
       </c>
       <c r="B514" t="str">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="C514" t="str">
-        <v>1487</v>
+        <v>443</v>
       </c>
       <c r="D514" t="str">
-        <v>Sakina bai Fakhruddin bhai Jigar</v>
+        <v>Sakina bai Fakhruddin bhai Tarawala</v>
       </c>
       <c r="E514" t="str">
-        <v>30360190</v>
+        <v>20318284</v>
       </c>
       <c r="F514" t="str">
         <v>Given</v>
       </c>
       <c r="G514" t="str">
-        <v>Kutbuddin bhai Jigar</v>
+        <v>shkh fakhruddin badi</v>
+      </c>
+      <c r="H514" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I514" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J514" t="str">
+        <v>10:59:06</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>1778659312652_52</v>
+        <v>1778659312652_525</v>
       </c>
       <c r="B515" t="str">
-        <v>53</v>
+        <v>526</v>
       </c>
       <c r="C515" t="str">
-        <v>1247</v>
+        <v>59</v>
       </c>
       <c r="D515" t="str">
-        <v>Alefiyah bai Saifuddin bhai Badshah</v>
+        <v>Sakina bai Fakhruddin bhai Bhura</v>
       </c>
       <c r="E515" t="str">
-        <v>30360143</v>
+        <v>20318079</v>
       </c>
       <c r="F515" t="str">
         <v>Pending</v>
@@ -13443,25 +13695,25 @@
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>1778659312652_529</v>
+        <v>1778659312652_528</v>
       </c>
       <c r="B516" t="str">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C516" t="str">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="D516" t="str">
-        <v>Sakina bai Fakhruddin bhai Kotwal</v>
+        <v>Sakina bai Fakhruddin bhai Jigar</v>
       </c>
       <c r="E516" t="str">
-        <v>30368038</v>
+        <v>30360190</v>
       </c>
       <c r="F516" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G516" t="str">
-        <v/>
+        <v>Kutbuddin bhai Jigar</v>
       </c>
     </row>
     <row r="517">
@@ -14109,97 +14361,106 @@
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>1778659312652_579</v>
+        <v>1778659312652_539</v>
       </c>
       <c r="B543" t="str">
-        <v>580</v>
+        <v>540</v>
       </c>
       <c r="C543" t="str">
-        <v>409</v>
+        <v>1123</v>
       </c>
       <c r="D543" t="str">
-        <v>Sarrah bai Fakhruddin bhai Kadwa</v>
+        <v>Sakina bai Husain bhai Bhurimuch</v>
       </c>
       <c r="E543" t="str">
-        <v>20318254</v>
+        <v>30367120</v>
       </c>
       <c r="F543" t="str">
         <v>Given</v>
       </c>
       <c r="G543" t="str">
-        <v>Fatema ben barkat</v>
+        <v/>
+      </c>
+      <c r="H543" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I543" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J543" t="str">
+        <v>10:41:26</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>1778659312652_580</v>
+        <v>1778659312652_549</v>
       </c>
       <c r="B544" t="str">
-        <v>581</v>
+        <v>550</v>
       </c>
       <c r="C544" t="str">
-        <v>661</v>
+        <v>737</v>
       </c>
       <c r="D544" t="str">
-        <v>Shabbir bhai Abdulqadir bhai Maudi</v>
+        <v>Sakina bai Mohammadhussain bhai Lokawala</v>
       </c>
       <c r="E544" t="str">
-        <v>20437739</v>
+        <v>30367336</v>
       </c>
       <c r="F544" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G544" t="str">
-        <v/>
+        <v>Zahra ben Dhilawala</v>
+      </c>
+      <c r="H544" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I544" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J544" t="str">
+        <v>10:59:04</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>1778659312652_581</v>
+        <v>1778659312652_579</v>
       </c>
       <c r="B545" t="str">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C545" t="str">
-        <v>355</v>
+        <v>409</v>
       </c>
       <c r="D545" t="str">
-        <v>Shabbir bhai Alihusain bhai Murga</v>
+        <v>Sarrah bai Fakhruddin bhai Kadwa</v>
       </c>
       <c r="E545" t="str">
-        <v>20318211</v>
+        <v>20318254</v>
       </c>
       <c r="F545" t="str">
         <v>Given</v>
       </c>
       <c r="G545" t="str">
-        <v/>
-      </c>
-      <c r="H545" t="str">
-        <v>19/05/2026</v>
-      </c>
-      <c r="I545" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="J545" t="str">
-        <v>11:33:34</v>
+        <v>Fatema ben barkat</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>1778659312652_582</v>
+        <v>1778659312652_580</v>
       </c>
       <c r="B546" t="str">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C546" t="str">
-        <v/>
+        <v>661</v>
       </c>
       <c r="D546" t="str">
-        <v>Shabbir bhai Asgarali bhai Partapur</v>
+        <v>Shabbir bhai Abdulqadir bhai Maudi</v>
       </c>
       <c r="E546" t="str">
-        <v>30142372</v>
+        <v>20437739</v>
       </c>
       <c r="F546" t="str">
         <v>Pending</v>
@@ -14210,42 +14471,51 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>1778659312652_583</v>
+        <v>1778659312652_581</v>
       </c>
       <c r="B547" t="str">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C547" t="str">
-        <v>1244</v>
+        <v>355</v>
       </c>
       <c r="D547" t="str">
-        <v>Shabbir bhai Jafar bhai Talaja</v>
+        <v>Shabbir bhai Alihusain bhai Murga</v>
       </c>
       <c r="E547" t="str">
-        <v>20318818</v>
+        <v>20318211</v>
       </c>
       <c r="F547" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G547" t="str">
         <v/>
+      </c>
+      <c r="H547" t="str">
+        <v>19/05/2026</v>
+      </c>
+      <c r="I547" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="J547" t="str">
+        <v>11:33:34</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>1778659312652_584</v>
+        <v>1778659312652_582</v>
       </c>
       <c r="B548" t="str">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C548" t="str">
-        <v>1158</v>
+        <v/>
       </c>
       <c r="D548" t="str">
-        <v>Shabbir bhai Jivaji bhai Alikaka</v>
+        <v>Shabbir bhai Asgarali bhai Partapur</v>
       </c>
       <c r="E548" t="str">
-        <v>30704206</v>
+        <v>30142372</v>
       </c>
       <c r="F548" t="str">
         <v>Pending</v>
@@ -14256,19 +14526,19 @@
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>1778659312652_585</v>
+        <v>1778659312652_583</v>
       </c>
       <c r="B549" t="str">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C549" t="str">
-        <v>212</v>
+        <v>1244</v>
       </c>
       <c r="D549" t="str">
-        <v>Shabbir bhai Qurbanhusain bhai Billa</v>
+        <v>Shabbir bhai Jafar bhai Talaja</v>
       </c>
       <c r="E549" t="str">
-        <v>20318209</v>
+        <v>20318818</v>
       </c>
       <c r="F549" t="str">
         <v>Pending</v>
@@ -14279,129 +14549,129 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>1778659312652_536</v>
+        <v>1778659312652_584</v>
       </c>
       <c r="B550" t="str">
-        <v>537</v>
+        <v>585</v>
       </c>
       <c r="C550" t="str">
-        <v>1084</v>
+        <v>1158</v>
       </c>
       <c r="D550" t="str">
-        <v>Sakina bai Fakhruddin bhai Thepadiya</v>
+        <v>Shabbir bhai Jivaji bhai Alikaka</v>
       </c>
       <c r="E550" t="str">
-        <v>20318653</v>
+        <v>30704206</v>
       </c>
       <c r="F550" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G550" t="str">
-        <v>Mubarak ben Rail</v>
-      </c>
-      <c r="H550" t="str">
-        <v>16/05/2026</v>
-      </c>
-      <c r="I550" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="J550" t="str">
-        <v>11:11:25</v>
+        <v/>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>1778659312652_537</v>
+        <v>1778659312652_585</v>
       </c>
       <c r="B551" t="str">
-        <v>538</v>
+        <v>586</v>
       </c>
       <c r="C551" t="str">
-        <v>1153</v>
+        <v>212</v>
       </c>
       <c r="D551" t="str">
-        <v>Sakina bai Hakimuddin bhai Mahudiwala</v>
+        <v>Shabbir bhai Qurbanhusain bhai Billa</v>
       </c>
       <c r="E551" t="str">
-        <v>30368023</v>
+        <v>20318209</v>
       </c>
       <c r="F551" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G551" t="str">
         <v/>
-      </c>
-      <c r="H551" t="str">
-        <v>19/05/2026</v>
-      </c>
-      <c r="I551" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="J551" t="str">
-        <v>10:34:35</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>1778659312652_538</v>
+        <v>1778659312652_536</v>
       </c>
       <c r="B552" t="str">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C552" t="str">
-        <v>1027</v>
+        <v>1084</v>
       </c>
       <c r="D552" t="str">
-        <v>Sakina bai Hatim bhai Jamali</v>
+        <v>Sakina bai Fakhruddin bhai Thepadiya</v>
       </c>
       <c r="E552" t="str">
-        <v>20318701</v>
+        <v>20318653</v>
       </c>
       <c r="F552" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G552" t="str">
-        <v/>
+        <v>Mubarak ben Rail</v>
+      </c>
+      <c r="H552" t="str">
+        <v>16/05/2026</v>
+      </c>
+      <c r="I552" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J552" t="str">
+        <v>11:11:25</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>1778659312652_539</v>
+        <v>1778659312652_537</v>
       </c>
       <c r="B553" t="str">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C553" t="str">
-        <v>1123</v>
+        <v>1153</v>
       </c>
       <c r="D553" t="str">
-        <v>Sakina bai Husain bhai Bhurimuch</v>
+        <v>Sakina bai Hakimuddin bhai Mahudiwala</v>
       </c>
       <c r="E553" t="str">
-        <v>30367120</v>
+        <v>30368023</v>
       </c>
       <c r="F553" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G553" t="str">
         <v/>
+      </c>
+      <c r="H553" t="str">
+        <v>19/05/2026</v>
+      </c>
+      <c r="I553" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="J553" t="str">
+        <v>10:34:35</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>1778659312652_54</v>
+        <v>1778659312652_538</v>
       </c>
       <c r="B554" t="str">
-        <v>55</v>
+        <v>539</v>
       </c>
       <c r="C554" t="str">
-        <v>278</v>
+        <v>1027</v>
       </c>
       <c r="D554" t="str">
-        <v>Aliakbar bhai Alihusain bhai Obri</v>
+        <v>Sakina bai Hatim bhai Jamali</v>
       </c>
       <c r="E554" t="str">
-        <v>30366528</v>
+        <v>20318701</v>
       </c>
       <c r="F554" t="str">
         <v>Pending</v>
@@ -14412,19 +14682,19 @@
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>1778659312652_549</v>
+        <v>1778659312652_54</v>
       </c>
       <c r="B555" t="str">
-        <v>550</v>
+        <v>55</v>
       </c>
       <c r="C555" t="str">
-        <v>737</v>
+        <v>278</v>
       </c>
       <c r="D555" t="str">
-        <v>Sakina bai Mohammadhussain bhai Lokawala</v>
+        <v>Aliakbar bhai Alihusain bhai Obri</v>
       </c>
       <c r="E555" t="str">
-        <v>30367336</v>
+        <v>30366528</v>
       </c>
       <c r="F555" t="str">
         <v>Pending</v>
@@ -14605,19 +14875,19 @@
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>1778659312652_751</v>
+        <v>1778659312652_752</v>
       </c>
       <c r="B563" t="str">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C563" t="str">
-        <v>577</v>
+        <v>1377</v>
       </c>
       <c r="D563" t="str">
-        <v>Zainab bai Qaidjoher bhai Shakir</v>
+        <v>Zainab bai Qurbanhusain bhai Obri</v>
       </c>
       <c r="E563" t="str">
-        <v>20318349</v>
+        <v>30367046</v>
       </c>
       <c r="F563" t="str">
         <v>Pending</v>
@@ -14628,25 +14898,34 @@
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>1778659312652_752</v>
+        <v>1778659312652_751</v>
       </c>
       <c r="B564" t="str">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C564" t="str">
-        <v>1377</v>
+        <v>577</v>
       </c>
       <c r="D564" t="str">
-        <v>Zainab bai Qurbanhusain bhai Obri</v>
+        <v>Zainab bai Qaidjoher bhai Shakir</v>
       </c>
       <c r="E564" t="str">
-        <v>30367046</v>
+        <v>20318349</v>
       </c>
       <c r="F564" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G564" t="str">
         <v/>
+      </c>
+      <c r="H564" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I564" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J564" t="str">
+        <v>11:22:11</v>
       </c>
     </row>
     <row r="565">
@@ -15129,22 +15408,22 @@
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>1778659312652_309</v>
+        <v>1778659312652_310</v>
       </c>
       <c r="B585" t="str">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C585" t="str">
-        <v>1146</v>
+        <v>1227</v>
       </c>
       <c r="D585" t="str">
-        <v>Ismail bhai Alihusain bhai Damdi</v>
+        <v>Ismail bhai Qurbanhusain bhai Billa</v>
       </c>
       <c r="E585" t="str">
-        <v>30366733</v>
+        <v>20318051</v>
       </c>
       <c r="F585" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G585" t="str">
         <v/>
@@ -15152,22 +15431,22 @@
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>1778659312652_310</v>
+        <v>1778659312652_311</v>
       </c>
       <c r="B586" t="str">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C586" t="str">
-        <v>1227</v>
+        <v>1438</v>
       </c>
       <c r="D586" t="str">
-        <v>Ismail bhai Qurbanhusain bhai Billa</v>
+        <v>Ismail bhai Saifuddin bhai Patrawala</v>
       </c>
       <c r="E586" t="str">
-        <v>20318051</v>
+        <v>30904442</v>
       </c>
       <c r="F586" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G586" t="str">
         <v/>
@@ -15175,19 +15454,19 @@
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>1778659312652_311</v>
+        <v>1778659312652_313</v>
       </c>
       <c r="B587" t="str">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C587" t="str">
-        <v>1438</v>
+        <v>316</v>
       </c>
       <c r="D587" t="str">
-        <v>Ismail bhai Saifuddin bhai Patrawala</v>
+        <v>Jamila bai Ahmedali bhai Tara</v>
       </c>
       <c r="E587" t="str">
-        <v>30904442</v>
+        <v>20318246</v>
       </c>
       <c r="F587" t="str">
         <v>Pending</v>
@@ -15198,22 +15477,22 @@
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>1778659312652_313</v>
+        <v>1778659312652_315</v>
       </c>
       <c r="B588" t="str">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C588" t="str">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="D588" t="str">
-        <v>Jamila bai Ahmedali bhai Tara</v>
+        <v>Jumana bai Burhanuddin bhai Gabruwala</v>
       </c>
       <c r="E588" t="str">
-        <v>20318246</v>
+        <v>30366585</v>
       </c>
       <c r="F588" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G588" t="str">
         <v/>
@@ -15221,19 +15500,19 @@
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>1778659312652_314</v>
+        <v>1778659312652_317</v>
       </c>
       <c r="B589" t="str">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C589" t="str">
-        <v>494</v>
+        <v>1181</v>
       </c>
       <c r="D589" t="str">
-        <v>Jamila bai Najmuddin bhai Gadhiwala</v>
+        <v>Jumana bai Hakimuddin bhai Dhambola</v>
       </c>
       <c r="E589" t="str">
-        <v>30368526</v>
+        <v>30367995</v>
       </c>
       <c r="F589" t="str">
         <v>Pending</v>
@@ -15244,22 +15523,22 @@
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>1778659312652_315</v>
+        <v>1778659312652_318</v>
       </c>
       <c r="B590" t="str">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C590" t="str">
-        <v>304</v>
+        <v>196</v>
       </c>
       <c r="D590" t="str">
-        <v>Jumana bai Burhanuddin bhai Gabruwala</v>
+        <v>Jumana bai Husain bhai Badshah</v>
       </c>
       <c r="E590" t="str">
-        <v>30366585</v>
+        <v>30368195</v>
       </c>
       <c r="F590" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G590" t="str">
         <v/>
@@ -15267,19 +15546,19 @@
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>1778659312652_317</v>
+        <v>1778659312652_31</v>
       </c>
       <c r="B591" t="str">
-        <v>318</v>
+        <v>32</v>
       </c>
       <c r="C591" t="str">
-        <v>1181</v>
+        <v/>
       </c>
       <c r="D591" t="str">
-        <v>Jumana bai Hakimuddin bhai Dhambola</v>
+        <v>Ajab bai Mulla Burhanuddin bhai Mohib</v>
       </c>
       <c r="E591" t="str">
-        <v>30367995</v>
+        <v>30391898</v>
       </c>
       <c r="F591" t="str">
         <v>Pending</v>
@@ -15290,135 +15569,162 @@
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>1778659312652_318</v>
+        <v>1778659312652_312</v>
       </c>
       <c r="B592" t="str">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C592" t="str">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="D592" t="str">
-        <v>Jumana bai Husain bhai Badshah</v>
+        <v>Jamila bai Abdullah bhai Patwari</v>
       </c>
       <c r="E592" t="str">
-        <v>30368195</v>
+        <v>30366400</v>
       </c>
       <c r="F592" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G592" t="str">
         <v/>
+      </c>
+      <c r="H592" t="str">
+        <v>21/05/2026</v>
+      </c>
+      <c r="I592" t="str">
+        <v>Thursday</v>
+      </c>
+      <c r="J592" t="str">
+        <v>11:02:18</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>1778659312652_31</v>
+        <v>1778659312652_30</v>
       </c>
       <c r="B593" t="str">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C593" t="str">
-        <v/>
+        <v>101</v>
       </c>
       <c r="D593" t="str">
-        <v>Ajab bai Mulla Burhanuddin bhai Mohib</v>
+        <v>Ajab bai Mufaddal bhai Bangali</v>
       </c>
       <c r="E593" t="str">
-        <v>30391898</v>
+        <v>30368206</v>
       </c>
       <c r="F593" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G593" t="str">
-        <v/>
+        <v>Insiya ben pachlasa</v>
+      </c>
+      <c r="H593" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I593" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J593" t="str">
+        <v>12:14:22</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>1778659312652_312</v>
+        <v>1778659312652_316</v>
       </c>
       <c r="B594" t="str">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C594" t="str">
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="D594" t="str">
-        <v>Jamila bai Abdullah bhai Patwari</v>
+        <v>Jumana bai Fakhruddin bhai Tarawala</v>
       </c>
       <c r="E594" t="str">
-        <v>30366400</v>
+        <v>30367675</v>
       </c>
       <c r="F594" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G594" t="str">
         <v/>
       </c>
       <c r="H594" t="str">
-        <v>21/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="I594" t="str">
-        <v>Thursday</v>
+        <v>Monday</v>
       </c>
       <c r="J594" t="str">
-        <v>11:02:18</v>
+        <v>03:35:08</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>1778659312652_316</v>
+        <v>1778659312652_314</v>
       </c>
       <c r="B595" t="str">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C595" t="str">
-        <v>235</v>
+        <v>494</v>
       </c>
       <c r="D595" t="str">
-        <v>Jumana bai Fakhruddin bhai Tarawala</v>
+        <v>Jamila bai Najmuddin bhai Gadhiwala</v>
       </c>
       <c r="E595" t="str">
-        <v>30367675</v>
+        <v>30368526</v>
       </c>
       <c r="F595" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G595" t="str">
-        <v/>
+        <v>Murtaza bhai Baroda</v>
+      </c>
+      <c r="H595" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I595" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J595" t="str">
+        <v>10:59:46</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>1778659312652_30</v>
+        <v>1778659312652_309</v>
       </c>
       <c r="B596" t="str">
-        <v>31</v>
+        <v>310</v>
       </c>
       <c r="C596" t="str">
-        <v>101</v>
+        <v>1146</v>
       </c>
       <c r="D596" t="str">
-        <v>Ajab bai Mufaddal bhai Bangali</v>
+        <v>Ismail bhai Alihusain bhai Damdi</v>
       </c>
       <c r="E596" t="str">
-        <v>30368206</v>
+        <v>30366733</v>
       </c>
       <c r="F596" t="str">
         <v>Given</v>
       </c>
       <c r="G596" t="str">
-        <v>Insiya ben pachlasa</v>
+        <v/>
       </c>
       <c r="H596" t="str">
-        <v>23/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="I596" t="str">
-        <v>Saturday</v>
+        <v>Monday</v>
       </c>
       <c r="J596" t="str">
-        <v>12:14:22</v>
+        <v>11:11:35</v>
       </c>
     </row>
     <row r="597">
@@ -15530,10 +15836,19 @@
         <v>20348450</v>
       </c>
       <c r="F601" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G601" t="str">
         <v/>
+      </c>
+      <c r="H601" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I601" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J601" t="str">
+        <v>11:10:15</v>
       </c>
     </row>
     <row r="602">
@@ -16355,121 +16670,130 @@
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>1778659312652_721</v>
+        <v>1778659312652_720</v>
       </c>
       <c r="B634" t="str">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C634" t="str">
-        <v>1412</v>
+        <v>971</v>
       </c>
       <c r="D634" t="str">
-        <v>Zahra bai Mufaddal bhai Dhilawala</v>
+        <v>Zahra bai Mohammed bhai Amarji</v>
       </c>
       <c r="E634" t="str">
-        <v>30367337</v>
+        <v>30367711</v>
       </c>
       <c r="F634" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G634" t="str">
-        <v/>
+        <v>shkh fakhruddin badi</v>
+      </c>
+      <c r="H634" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I634" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J634" t="str">
+        <v>12:24:51</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>1778659312652_720</v>
+        <v>1778659312652_717</v>
       </c>
       <c r="B635" t="str">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C635" t="str">
-        <v>971</v>
+        <v>1354</v>
       </c>
       <c r="D635" t="str">
-        <v>Zahra bai Mohammed bhai Amarji</v>
+        <v>Zahra bai Fakhruddin bhai Badshah</v>
       </c>
       <c r="E635" t="str">
-        <v>30367711</v>
+        <v>30366808</v>
       </c>
       <c r="F635" t="str">
         <v>Given</v>
       </c>
       <c r="G635" t="str">
-        <v>shkh fakhruddin badi</v>
+        <v>Aliasgar bhai Mulla</v>
       </c>
       <c r="H635" t="str">
-        <v>23/05/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="I635" t="str">
-        <v>Saturday</v>
+        <v>Thursday</v>
       </c>
       <c r="J635" t="str">
-        <v>12:24:51</v>
+        <v>12:47:31</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>1778659312652_717</v>
+        <v>1778659312652_70</v>
       </c>
       <c r="B636" t="str">
-        <v>718</v>
+        <v>71</v>
       </c>
       <c r="C636" t="str">
-        <v>1354</v>
+        <v>436</v>
       </c>
       <c r="D636" t="str">
-        <v>Zahra bai Fakhruddin bhai Badshah</v>
+        <v>Arwa bai Sajjadhusain bhai Peeth</v>
       </c>
       <c r="E636" t="str">
-        <v>30366808</v>
+        <v>30368012</v>
       </c>
       <c r="F636" t="str">
         <v>Given</v>
       </c>
       <c r="G636" t="str">
-        <v>Aliasgar bhai Mulla</v>
+        <v>Sakina anwar</v>
       </c>
       <c r="H636" t="str">
-        <v>21/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="I636" t="str">
-        <v>Thursday</v>
+        <v>Saturday</v>
       </c>
       <c r="J636" t="str">
-        <v>12:47:31</v>
+        <v>12:38:07</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>1778659312652_70</v>
+        <v>1778659312652_721</v>
       </c>
       <c r="B637" t="str">
-        <v>71</v>
+        <v>722</v>
       </c>
       <c r="C637" t="str">
-        <v>436</v>
+        <v>1412</v>
       </c>
       <c r="D637" t="str">
-        <v>Arwa bai Sajjadhusain bhai Peeth</v>
+        <v>Zahra bai Mufaddal bhai Dhilawala</v>
       </c>
       <c r="E637" t="str">
-        <v>30368012</v>
+        <v>30367337</v>
       </c>
       <c r="F637" t="str">
         <v>Given</v>
       </c>
       <c r="G637" t="str">
-        <v>Sakina anwar</v>
+        <v>Zahra ben Dhilawala</v>
       </c>
       <c r="H637" t="str">
-        <v>23/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="I637" t="str">
-        <v>Saturday</v>
+        <v>Monday</v>
       </c>
       <c r="J637" t="str">
-        <v>12:38:07</v>
+        <v>10:59:04</v>
       </c>
     </row>
     <row r="638">
@@ -16598,42 +16922,51 @@
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>1778659312652_337</v>
+        <v>1778659312652_590</v>
       </c>
       <c r="B643" t="str">
-        <v>338</v>
+        <v>591</v>
       </c>
       <c r="C643" t="str">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="D643" t="str">
-        <v>Kubra bai Abbas bhai Gotha</v>
+        <v>Shabbirhusain bhai Qurbanhusain bhai Ezzy</v>
       </c>
       <c r="E643" t="str">
-        <v>30366917</v>
+        <v>20318695</v>
       </c>
       <c r="F643" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G643" t="str">
         <v/>
+      </c>
+      <c r="H643" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I643" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J643" t="str">
+        <v>10:46:06</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>1778659312652_588</v>
+        <v>1778659312652_337</v>
       </c>
       <c r="B644" t="str">
-        <v>589</v>
+        <v>338</v>
       </c>
       <c r="C644" t="str">
-        <v>711</v>
+        <v>502</v>
       </c>
       <c r="D644" t="str">
-        <v>Shabbirhusain bhai Ahmed bhai Galal</v>
+        <v>Kubra bai Abbas bhai Gotha</v>
       </c>
       <c r="E644" t="str">
-        <v>20318438</v>
+        <v>30366917</v>
       </c>
       <c r="F644" t="str">
         <v>Pending</v>
@@ -16644,71 +16977,71 @@
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>1778659312652_58</v>
+        <v>1778659312652_588</v>
       </c>
       <c r="B645" t="str">
-        <v>59</v>
+        <v>589</v>
       </c>
       <c r="C645" t="str">
-        <v>1237</v>
+        <v>711</v>
       </c>
       <c r="D645" t="str">
-        <v xml:space="preserve">Aliasgar bhai Simalwara </v>
+        <v>Shabbirhusain bhai Ahmed bhai Galal</v>
       </c>
       <c r="E645" t="str">
-        <v/>
+        <v>20318438</v>
       </c>
       <c r="F645" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G645" t="str">
-        <v>Taher bhai Abbas bhai Tuta</v>
+        <v/>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>1778659312652_589</v>
+        <v>1778659312652_58</v>
       </c>
       <c r="B646" t="str">
-        <v>590</v>
+        <v>59</v>
       </c>
       <c r="C646" t="str">
-        <v>930</v>
+        <v>1237</v>
       </c>
       <c r="D646" t="str">
-        <v>Shabbirhusain bhai Mulla Alihusain bhai Badri</v>
+        <v xml:space="preserve">Aliasgar bhai Simalwara </v>
       </c>
       <c r="E646" t="str">
-        <v>20348009</v>
+        <v/>
       </c>
       <c r="F646" t="str">
         <v>Given</v>
       </c>
       <c r="G646" t="str">
-        <v>Shabbir hussain bhai Thakarda</v>
+        <v>Taher bhai Abbas bhai Tuta</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>1778659312652_590</v>
+        <v>1778659312652_589</v>
       </c>
       <c r="B647" t="str">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C647" t="str">
-        <v>509</v>
+        <v>930</v>
       </c>
       <c r="D647" t="str">
-        <v>Shabbirhusain bhai Qurbanhusain bhai Ezzy</v>
+        <v>Shabbirhusain bhai Mulla Alihusain bhai Badri</v>
       </c>
       <c r="E647" t="str">
-        <v>20318695</v>
+        <v>20348009</v>
       </c>
       <c r="F647" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G647" t="str">
-        <v/>
+        <v>Shabbir hussain bhai Thakarda</v>
       </c>
     </row>
     <row r="648">
@@ -17094,42 +17427,51 @@
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>1778659312652_174</v>
+        <v>1778659312652_177</v>
       </c>
       <c r="B663" t="str">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C663" t="str">
-        <v>375</v>
+        <v>198</v>
       </c>
       <c r="D663" t="str">
-        <v>Fatema bai Alihusain bhai Damdi</v>
+        <v>Fatema bai Alihusain bhai Naerli</v>
       </c>
       <c r="E663" t="str">
-        <v>30366732</v>
+        <v>20318017</v>
       </c>
       <c r="F663" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G663" t="str">
         <v/>
+      </c>
+      <c r="H663" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I663" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J663" t="str">
+        <v>12:05:33</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>1778659312652_175</v>
+        <v>1778659312652_174</v>
       </c>
       <c r="B664" t="str">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C664" t="str">
-        <v>953</v>
+        <v>375</v>
       </c>
       <c r="D664" t="str">
-        <v>Fatema bai Alihusain bhai Kabir</v>
+        <v>Fatema bai Alihusain bhai Damdi</v>
       </c>
       <c r="E664" t="str">
-        <v>30367752</v>
+        <v>30366732</v>
       </c>
       <c r="F664" t="str">
         <v>Pending</v>
@@ -17140,19 +17482,19 @@
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>1778659312652_176</v>
+        <v>1778659312652_175</v>
       </c>
       <c r="B665" t="str">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C665" t="str">
-        <v>434</v>
+        <v>953</v>
       </c>
       <c r="D665" t="str">
-        <v>Fatema bai Alihusain bhai Mandav</v>
+        <v>Fatema bai Alihusain bhai Kabir</v>
       </c>
       <c r="E665" t="str">
-        <v>20318275</v>
+        <v>30367752</v>
       </c>
       <c r="F665" t="str">
         <v>Pending</v>
@@ -17163,19 +17505,19 @@
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>1778659312652_177</v>
+        <v>1778659312652_176</v>
       </c>
       <c r="B666" t="str">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C666" t="str">
-        <v>198</v>
+        <v>434</v>
       </c>
       <c r="D666" t="str">
-        <v>Fatema bai Alihusain bhai Naerli</v>
+        <v>Fatema bai Alihusain bhai Mandav</v>
       </c>
       <c r="E666" t="str">
-        <v>20318017</v>
+        <v>20318275</v>
       </c>
       <c r="F666" t="str">
         <v>Pending</v>
@@ -17636,45 +17978,54 @@
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>1778659312652_373</v>
+        <v>1778659312652_367</v>
       </c>
       <c r="B685" t="str">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C685" t="str">
-        <v>853</v>
+        <v>619</v>
       </c>
       <c r="D685" t="str">
-        <v>Mohsin bhai Ahmedali bhai Baroda</v>
+        <v>Mohammed bhai Kala bhai Bhurimuch</v>
       </c>
       <c r="E685" t="str">
-        <v>20434975</v>
+        <v>20318374</v>
       </c>
       <c r="F685" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G685" t="str">
-        <v/>
+        <v>Sakina ben bhurimuch</v>
+      </c>
+      <c r="H685" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I685" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J685" t="str">
+        <v>10:43:37</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>1778659312652_374</v>
+        <v>1778659312652_373</v>
       </c>
       <c r="B686" t="str">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C686" t="str">
-        <v>1229</v>
+        <v>853</v>
       </c>
       <c r="D686" t="str">
-        <v>Moiz bhai Fazleabbas bhai Ujjain</v>
+        <v>Mohsin bhai Ahmedali bhai Baroda</v>
       </c>
       <c r="E686" t="str">
-        <v>20318687</v>
+        <v>20434975</v>
       </c>
       <c r="F686" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G686" t="str">
         <v/>
@@ -17682,22 +18033,22 @@
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>1778659312652_375</v>
+        <v>1778659312652_374</v>
       </c>
       <c r="B687" t="str">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C687" t="str">
-        <v>231</v>
+        <v>1229</v>
       </c>
       <c r="D687" t="str">
-        <v>Moiz bhai Mohammedhusain bhai Damdiwala</v>
+        <v>Moiz bhai Fazleabbas bhai Ujjain</v>
       </c>
       <c r="E687" t="str">
-        <v>20356176</v>
+        <v>20318687</v>
       </c>
       <c r="F687" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G687" t="str">
         <v/>
@@ -17760,57 +18111,57 @@
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>1778659312652_365</v>
+        <v>1778659312652_375</v>
       </c>
       <c r="B690" t="str">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="C690" t="str">
-        <v>1052</v>
+        <v>231</v>
       </c>
       <c r="D690" t="str">
-        <v>Mohammed bhai Alihusain bhai Lodal</v>
+        <v>Moiz bhai Mohammedhusain bhai Damdiwala</v>
       </c>
       <c r="E690" t="str">
-        <v>20318607</v>
+        <v>20356176</v>
       </c>
       <c r="F690" t="str">
         <v>Given</v>
       </c>
       <c r="G690" t="str">
-        <v>Munira ben gunjwala</v>
+        <v/>
       </c>
       <c r="H690" t="str">
-        <v>23/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="I690" t="str">
-        <v>Saturday</v>
+        <v>Monday</v>
       </c>
       <c r="J690" t="str">
-        <v>11:04:48</v>
+        <v>11:15:26</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>1778659312652_368</v>
+        <v>1778659312652_365</v>
       </c>
       <c r="B691" t="str">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C691" t="str">
-        <v>719</v>
+        <v>1052</v>
       </c>
       <c r="D691" t="str">
-        <v>Mohammed bhai Mulla Ismail bhai Tarawala</v>
+        <v>Mohammed bhai Alihusain bhai Lodal</v>
       </c>
       <c r="E691" t="str">
-        <v>20318443</v>
+        <v>20318607</v>
       </c>
       <c r="F691" t="str">
         <v>Given</v>
       </c>
       <c r="G691" t="str">
-        <v/>
+        <v>Munira ben gunjwala</v>
       </c>
       <c r="H691" t="str">
         <v>23/05/2026</v>
@@ -17819,47 +18170,56 @@
         <v>Saturday</v>
       </c>
       <c r="J691" t="str">
-        <v>11:30:12</v>
+        <v>11:04:48</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>1778659312652_364</v>
+        <v>1778659312652_368</v>
       </c>
       <c r="B692" t="str">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C692" t="str">
-        <v>816</v>
+        <v>719</v>
       </c>
       <c r="D692" t="str">
-        <v>Mohammed bhai Abdulhusain bhai Khand</v>
+        <v>Mohammed bhai Mulla Ismail bhai Tarawala</v>
       </c>
       <c r="E692" t="str">
-        <v>20352854</v>
+        <v>20318443</v>
       </c>
       <c r="F692" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G692" t="str">
         <v/>
+      </c>
+      <c r="H692" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I692" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J692" t="str">
+        <v>11:30:12</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>1778659312652_366</v>
+        <v>1778659312652_364</v>
       </c>
       <c r="B693" t="str">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C693" t="str">
-        <v>523</v>
+        <v>816</v>
       </c>
       <c r="D693" t="str">
-        <v>Mohammed bhai Fakhruddin bhai Antri</v>
+        <v>Mohammed bhai Abdulhusain bhai Khand</v>
       </c>
       <c r="E693" t="str">
-        <v>20348379</v>
+        <v>20352854</v>
       </c>
       <c r="F693" t="str">
         <v>Pending</v>
@@ -17870,19 +18230,19 @@
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>1778659312652_367</v>
+        <v>1778659312652_366</v>
       </c>
       <c r="B694" t="str">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C694" t="str">
-        <v>619</v>
+        <v>523</v>
       </c>
       <c r="D694" t="str">
-        <v>Mohammed bhai Kala bhai Bhurimuch</v>
+        <v>Mohammed bhai Fakhruddin bhai Antri</v>
       </c>
       <c r="E694" t="str">
-        <v>20318374</v>
+        <v>20348379</v>
       </c>
       <c r="F694" t="str">
         <v>Pending</v>
@@ -18132,19 +18492,19 @@
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>1778659312652_205</v>
+        <v>1778659312652_206</v>
       </c>
       <c r="B705" t="str">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C705" t="str">
-        <v>1112</v>
+        <v>992</v>
       </c>
       <c r="D705" t="str">
-        <v>Fatema bai Mohammed bhai Khandwala</v>
+        <v>Fatema bai Mohammedhusain bhai Obri</v>
       </c>
       <c r="E705" t="str">
-        <v>30367516</v>
+        <v>30367902</v>
       </c>
       <c r="F705" t="str">
         <v>Pending</v>
@@ -18155,22 +18515,22 @@
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>1778659312652_206</v>
+        <v>1778659312652_207</v>
       </c>
       <c r="B706" t="str">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C706" t="str">
-        <v>992</v>
+        <v>1410</v>
       </c>
       <c r="D706" t="str">
-        <v>Fatema bai Mohammedhusain bhai Obri</v>
+        <v>Fatema bai Mohsin bhai Shakir</v>
       </c>
       <c r="E706" t="str">
-        <v>30367902</v>
+        <v>20306365</v>
       </c>
       <c r="F706" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G706" t="str">
         <v/>
@@ -18178,22 +18538,22 @@
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>1778659312652_207</v>
+        <v>1778659312652_208</v>
       </c>
       <c r="B707" t="str">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C707" t="str">
-        <v>1410</v>
+        <v>1046</v>
       </c>
       <c r="D707" t="str">
-        <v>Fatema bai Mohsin bhai Shakir</v>
+        <v>Fatema bai Moiz bhai Lodal</v>
       </c>
       <c r="E707" t="str">
-        <v>20306365</v>
+        <v>20318638</v>
       </c>
       <c r="F707" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G707" t="str">
         <v/>
@@ -18201,19 +18561,19 @@
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>1778659312652_208</v>
+        <v>1778659312652_20</v>
       </c>
       <c r="B708" t="str">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="C708" t="str">
-        <v>1046</v>
+        <v>626</v>
       </c>
       <c r="D708" t="str">
-        <v>Fatema bai Moiz bhai Lodal</v>
+        <v>Ajab bai Alihusain bhai Bakri</v>
       </c>
       <c r="E708" t="str">
-        <v>20318638</v>
+        <v>30367128</v>
       </c>
       <c r="F708" t="str">
         <v>Pending</v>
@@ -18224,19 +18584,19 @@
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>1778659312652_20</v>
+        <v>1778659312652_209</v>
       </c>
       <c r="B709" t="str">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="C709" t="str">
-        <v>626</v>
+        <v>277</v>
       </c>
       <c r="D709" t="str">
-        <v>Ajab bai Alihusain bhai Bakri</v>
+        <v>Fatema bai Murtaza bhai Damri</v>
       </c>
       <c r="E709" t="str">
-        <v>30367128</v>
+        <v>30360157</v>
       </c>
       <c r="F709" t="str">
         <v>Pending</v>
@@ -18247,77 +18607,77 @@
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>1778659312652_209</v>
+        <v>1778659312652_210</v>
       </c>
       <c r="B710" t="str">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C710" t="str">
-        <v>277</v>
+        <v>1200</v>
       </c>
       <c r="D710" t="str">
-        <v>Fatema bai Murtaza bhai Damri</v>
+        <v>Fatema bai Murtaza bhai Gababhaiwala</v>
       </c>
       <c r="E710" t="str">
-        <v>30360157</v>
+        <v>30366452</v>
       </c>
       <c r="F710" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G710" t="str">
         <v/>
+      </c>
+      <c r="H710" t="str">
+        <v>19/05/2026</v>
+      </c>
+      <c r="I710" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="J710" t="str">
+        <v>11:55:00</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>1778659312652_210</v>
+        <v>1778659312652_211</v>
       </c>
       <c r="B711" t="str">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C711" t="str">
-        <v>1200</v>
+        <v>1031</v>
       </c>
       <c r="D711" t="str">
-        <v>Fatema bai Murtaza bhai Gababhaiwala</v>
+        <v>Fatema bai Mustafa bhai Bhai saheb</v>
       </c>
       <c r="E711" t="str">
-        <v>30366452</v>
+        <v>30367135</v>
       </c>
       <c r="F711" t="str">
         <v>Given</v>
       </c>
       <c r="G711" t="str">
         <v/>
-      </c>
-      <c r="H711" t="str">
-        <v>19/05/2026</v>
-      </c>
-      <c r="I711" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="J711" t="str">
-        <v>11:55:00</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>1778659312652_211</v>
+        <v>1778659312652_212</v>
       </c>
       <c r="B712" t="str">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C712" t="str">
-        <v>1031</v>
+        <v>578</v>
       </c>
       <c r="D712" t="str">
-        <v>Fatema bai Mustafa bhai Bhai saheb</v>
+        <v>Fatema bai Najmuddin bhai Mulla</v>
       </c>
       <c r="E712" t="str">
-        <v>30367135</v>
+        <v>30367060</v>
       </c>
       <c r="F712" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G712" t="str">
         <v/>
@@ -18325,25 +18685,34 @@
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>1778659312652_212</v>
+        <v>1778659312652_205</v>
       </c>
       <c r="B713" t="str">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C713" t="str">
-        <v>578</v>
+        <v>1112</v>
       </c>
       <c r="D713" t="str">
-        <v>Fatema bai Najmuddin bhai Mulla</v>
+        <v>Fatema bai Mohammed bhai Khandwala</v>
       </c>
       <c r="E713" t="str">
-        <v>30367060</v>
+        <v>30367516</v>
       </c>
       <c r="F713" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G713" t="str">
         <v/>
+      </c>
+      <c r="H713" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I713" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J713" t="str">
+        <v>10:34:41</v>
       </c>
     </row>
     <row r="714">
@@ -18380,65 +18749,83 @@
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>1778659312652_29</v>
+        <v>1778659312652_473</v>
       </c>
       <c r="B715" t="str">
-        <v>30</v>
+        <v>474</v>
       </c>
       <c r="C715" t="str">
-        <v>386</v>
+        <v>985</v>
       </c>
       <c r="D715" t="str">
-        <v>Ajab bai Mohammed bhai Daya</v>
+        <v>Rashida bai Shaikh Abbas bhai Jaan</v>
       </c>
       <c r="E715" t="str">
-        <v>30366758</v>
+        <v>30493100</v>
       </c>
       <c r="F715" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G715" t="str">
         <v/>
+      </c>
+      <c r="H715" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I715" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J715" t="str">
+        <v>10:54:40</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>1778659312652_468</v>
+        <v>1778659312652_29</v>
       </c>
       <c r="B716" t="str">
-        <v>469</v>
+        <v>30</v>
       </c>
       <c r="C716" t="str">
-        <v>569</v>
+        <v>386</v>
       </c>
       <c r="D716" t="str">
-        <v>Rashida bai Ibrahim bhai Khumanpur</v>
+        <v>Ajab bai Mohammed bhai Daya</v>
       </c>
       <c r="E716" t="str">
-        <v>30485607</v>
+        <v>30366758</v>
       </c>
       <c r="F716" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G716" t="str">
-        <v/>
+        <v>Shkh fakhruddin khedapa</v>
+      </c>
+      <c r="H716" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I716" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J716" t="str">
+        <v>12:37:46</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>1778659312652_46</v>
+        <v>1778659312652_468</v>
       </c>
       <c r="B717" t="str">
-        <v>47</v>
+        <v>469</v>
       </c>
       <c r="C717" t="str">
-        <v>809</v>
+        <v>569</v>
       </c>
       <c r="D717" t="str">
-        <v>Alefiyah bai Alihusain bhai Bankoda</v>
+        <v>Rashida bai Ibrahim bhai Khumanpur</v>
       </c>
       <c r="E717" t="str">
-        <v>60446432</v>
+        <v>30485607</v>
       </c>
       <c r="F717" t="str">
         <v>Pending</v>
@@ -18449,103 +18836,103 @@
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>1778659312652_469</v>
+        <v>1778659312652_46</v>
       </c>
       <c r="B718" t="str">
-        <v>470</v>
+        <v>47</v>
       </c>
       <c r="C718" t="str">
-        <v>741</v>
+        <v>809</v>
       </c>
       <c r="D718" t="str">
-        <v>Rashida bai Mohammadhussain bhai Antri</v>
+        <v>Alefiyah bai Alihusain bhai Bankoda</v>
       </c>
       <c r="E718" t="str">
-        <v>20318460</v>
+        <v>60446432</v>
       </c>
       <c r="F718" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G718" t="str">
-        <v>Shkh fakhruddin khedapa</v>
+        <v/>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>1778659312652_470</v>
+        <v>1778659312652_469</v>
       </c>
       <c r="B719" t="str">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C719" t="str">
-        <v>629</v>
+        <v>741</v>
       </c>
       <c r="D719" t="str">
-        <v>Rashida bai Mohammed bhai Fasarjya</v>
+        <v>Rashida bai Mohammadhussain bhai Antri</v>
       </c>
       <c r="E719" t="str">
-        <v>30367131</v>
+        <v>20318460</v>
       </c>
       <c r="F719" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G719" t="str">
-        <v/>
+        <v>Shkh fakhruddin khedapa</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>1778659312652_472</v>
+        <v>1778659312652_470</v>
       </c>
       <c r="B720" t="str">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C720" t="str">
-        <v>1201</v>
+        <v>629</v>
       </c>
       <c r="D720" t="str">
-        <v>Rashida bai Sajjad bhai Sagir</v>
+        <v>Rashida bai Mohammed bhai Fasarjya</v>
       </c>
       <c r="E720" t="str">
-        <v>30367457</v>
+        <v>30367131</v>
       </c>
       <c r="F720" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G720" t="str">
-        <v>Rehena ben Kawja</v>
-      </c>
-      <c r="H720" t="str">
-        <v>18/05/2026</v>
-      </c>
-      <c r="I720" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="J720" t="str">
-        <v>11:37:40</v>
+        <v/>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>1778659312652_473</v>
+        <v>1778659312652_472</v>
       </c>
       <c r="B721" t="str">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C721" t="str">
-        <v>985</v>
+        <v>1201</v>
       </c>
       <c r="D721" t="str">
-        <v>Rashida bai Shaikh Abbas bhai Jaan</v>
+        <v>Rashida bai Sajjad bhai Sagir</v>
       </c>
       <c r="E721" t="str">
-        <v>30493100</v>
+        <v>30367457</v>
       </c>
       <c r="F721" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G721" t="str">
-        <v/>
+        <v>Rehena ben Kawja</v>
+      </c>
+      <c r="H721" t="str">
+        <v>18/05/2026</v>
+      </c>
+      <c r="I721" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J721" t="str">
+        <v>11:37:40</v>
       </c>
     </row>
     <row r="722">
@@ -18880,74 +19267,83 @@
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>1778659312652_732</v>
+        <v>1778659312652_733</v>
       </c>
       <c r="B734" t="str">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C734" t="str">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D734" t="str">
-        <v>Zainab bai Aliakbar bhai Popat</v>
+        <v>Zainab bai Aliasgar bhai Kamruddin</v>
       </c>
       <c r="E734" t="str">
-        <v>30368105</v>
+        <v>40443705</v>
       </c>
       <c r="F734" t="str">
         <v>Given</v>
       </c>
       <c r="G734" t="str">
-        <v>Insiya ben pachlasa</v>
+        <v>Kutub bhai Gaba</v>
       </c>
       <c r="H734" t="str">
-        <v>23/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="I734" t="str">
-        <v>Saturday</v>
+        <v>Monday</v>
       </c>
       <c r="J734" t="str">
-        <v>12:14:01</v>
+        <v>12:04:47</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>1778659312652_576</v>
+        <v>1778659312652_732</v>
       </c>
       <c r="B735" t="str">
-        <v>577</v>
+        <v>733</v>
       </c>
       <c r="C735" t="str">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="D735" t="str">
-        <v>Sarrah bai Abbas bhai Obri</v>
+        <v>Zainab bai Aliakbar bhai Popat</v>
       </c>
       <c r="E735" t="str">
-        <v>30366374</v>
+        <v>30368105</v>
       </c>
       <c r="F735" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G735" t="str">
-        <v/>
+        <v>Insiya ben pachlasa</v>
+      </c>
+      <c r="H735" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I735" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J735" t="str">
+        <v>12:14:01</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>1778659312652_72</v>
+        <v>1778659312652_576</v>
       </c>
       <c r="B736" t="str">
-        <v>73</v>
+        <v>577</v>
       </c>
       <c r="C736" t="str">
-        <v>529</v>
+        <v>128</v>
       </c>
       <c r="D736" t="str">
-        <v>Asgarali bhai Abbas bhai Bhabhrana</v>
+        <v>Sarrah bai Abbas bhai Obri</v>
       </c>
       <c r="E736" t="str">
-        <v>30802469</v>
+        <v>30366374</v>
       </c>
       <c r="F736" t="str">
         <v>Pending</v>
@@ -18958,19 +19354,19 @@
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>1778659312652_729</v>
+        <v>1778659312652_72</v>
       </c>
       <c r="B737" t="str">
-        <v>730</v>
+        <v>73</v>
       </c>
       <c r="C737" t="str">
-        <v>557</v>
+        <v>529</v>
       </c>
       <c r="D737" t="str">
-        <v>Zainab bai Abid bhai Peethwala</v>
+        <v>Asgarali bhai Abbas bhai Bhabhrana</v>
       </c>
       <c r="E737" t="str">
-        <v>20318337</v>
+        <v>30802469</v>
       </c>
       <c r="F737" t="str">
         <v>Pending</v>
@@ -18981,19 +19377,19 @@
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>1778659312652_731</v>
+        <v>1778659312652_729</v>
       </c>
       <c r="B738" t="str">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C738" t="str">
-        <v>1413</v>
+        <v>557</v>
       </c>
       <c r="D738" t="str">
-        <v>Zainab bai Ali bhai Alikaka</v>
+        <v>Zainab bai Abid bhai Peethwala</v>
       </c>
       <c r="E738" t="str">
-        <v>30368043</v>
+        <v>20318337</v>
       </c>
       <c r="F738" t="str">
         <v>Pending</v>
@@ -19004,19 +19400,19 @@
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>1778659312652_733</v>
+        <v>1778659312652_731</v>
       </c>
       <c r="B739" t="str">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C739" t="str">
-        <v>112</v>
+        <v>1413</v>
       </c>
       <c r="D739" t="str">
-        <v>Zainab bai Aliasgar bhai Kamruddin</v>
+        <v>Zainab bai Ali bhai Alikaka</v>
       </c>
       <c r="E739" t="str">
-        <v>40443705</v>
+        <v>30368043</v>
       </c>
       <c r="F739" t="str">
         <v>Pending</v>

--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -7059,74 +7059,83 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>1778659312652_100</v>
+        <v>1778659312652_99</v>
       </c>
       <c r="B258" t="str">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C258" t="str">
-        <v>117</v>
+        <v>236</v>
       </c>
       <c r="D258" t="str">
-        <v>Batul bai Mohammadhussain bhai Bankoda</v>
+        <v>Batul bai Johar bhai Saroda</v>
       </c>
       <c r="E258" t="str">
-        <v>30360295</v>
+        <v>30488741</v>
       </c>
       <c r="F258" t="str">
         <v>Given</v>
       </c>
       <c r="G258" t="str">
-        <v/>
+        <v>Ilyas</v>
       </c>
       <c r="H258" t="str">
-        <v>22/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="I258" t="str">
-        <v>Friday</v>
+        <v>Monday</v>
       </c>
       <c r="J258" t="str">
-        <v>12:19:42</v>
+        <v>16:05:11</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>1778659312652_101</v>
+        <v>1778659312652_100</v>
       </c>
       <c r="B259" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C259" t="str">
-        <v>254</v>
+        <v>117</v>
       </c>
       <c r="D259" t="str">
-        <v>Batul bai Mohammadhussain bhai Patra</v>
+        <v>Batul bai Mohammadhussain bhai Bankoda</v>
       </c>
       <c r="E259" t="str">
-        <v>20318132</v>
+        <v>30360295</v>
       </c>
       <c r="F259" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G259" t="str">
         <v/>
+      </c>
+      <c r="H259" t="str">
+        <v>22/05/2026</v>
+      </c>
+      <c r="I259" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="J259" t="str">
+        <v>12:19:42</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>1778659312652_103</v>
+        <v>1778659312652_101</v>
       </c>
       <c r="B260" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C260" t="str">
-        <v>1303</v>
+        <v>254</v>
       </c>
       <c r="D260" t="str">
-        <v>Batul bai Qutbuddin bhai Rustam</v>
+        <v>Batul bai Mohammadhussain bhai Patra</v>
       </c>
       <c r="E260" t="str">
-        <v>30366656</v>
+        <v>20318132</v>
       </c>
       <c r="F260" t="str">
         <v>Pending</v>
@@ -7137,19 +7146,19 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>1778659312652_104</v>
+        <v>1778659312652_103</v>
       </c>
       <c r="B261" t="str">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C261" t="str">
-        <v>76</v>
+        <v>1303</v>
       </c>
       <c r="D261" t="str">
-        <v>Batul bai Saifuddin bhai Doodhbhai</v>
+        <v>Batul bai Qutbuddin bhai Rustam</v>
       </c>
       <c r="E261" t="str">
-        <v>30368616</v>
+        <v>30366656</v>
       </c>
       <c r="F261" t="str">
         <v>Pending</v>
@@ -7160,19 +7169,19 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>1778659312652_105</v>
+        <v>1778659312652_104</v>
       </c>
       <c r="B262" t="str">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C262" t="str">
-        <v>744</v>
+        <v>76</v>
       </c>
       <c r="D262" t="str">
-        <v>Batul bai Shaikh Akbarhusain bhai Rampurwala</v>
+        <v>Batul bai Saifuddin bhai Doodhbhai</v>
       </c>
       <c r="E262" t="str">
-        <v>30367359</v>
+        <v>30368616</v>
       </c>
       <c r="F262" t="str">
         <v>Pending</v>
@@ -7183,89 +7192,80 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>1778659312652_106</v>
+        <v>1778659312652_105</v>
       </c>
       <c r="B263" t="str">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C263" t="str">
-        <v>807</v>
+        <v>744</v>
       </c>
       <c r="D263" t="str">
-        <v>Batul bai Taiyebali bhai Bankoda</v>
+        <v>Batul bai Shaikh Akbarhusain bhai Rampurwala</v>
       </c>
       <c r="E263" t="str">
-        <v>30367508</v>
+        <v>30367359</v>
       </c>
       <c r="F263" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G263" t="str">
-        <v>zainab ben antri</v>
-      </c>
-      <c r="H263" t="str">
-        <v>18/05/2026</v>
-      </c>
-      <c r="I263" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="J263" t="str">
-        <v>11:50:34</v>
+        <v/>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>1778659312652_6</v>
+        <v>1778659312652_106</v>
       </c>
       <c r="B264" t="str">
-        <v>7</v>
+        <v>107</v>
       </c>
       <c r="C264" t="str">
-        <v>7</v>
+        <v>807</v>
       </c>
       <c r="D264" t="str">
-        <v>Abbas bhai Alihusain bhai Sihjee</v>
+        <v>Batul bai Taiyebali bhai Bankoda</v>
       </c>
       <c r="E264" t="str">
-        <v>20435003</v>
+        <v>30367508</v>
       </c>
       <c r="F264" t="str">
         <v>Given</v>
       </c>
       <c r="G264" t="str">
-        <v>Ajab ben Khand</v>
+        <v>zainab ben antri</v>
       </c>
       <c r="H264" t="str">
-        <v>21/05/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="I264" t="str">
-        <v>Thursday</v>
+        <v>Monday</v>
       </c>
       <c r="J264" t="str">
-        <v>10:25:43</v>
+        <v>11:50:34</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>1778659312652_335</v>
+        <v>1778659312652_6</v>
       </c>
       <c r="B265" t="str">
-        <v>336</v>
+        <v>7</v>
       </c>
       <c r="C265" t="str">
-        <v>1197</v>
+        <v>7</v>
       </c>
       <c r="D265" t="str">
-        <v>Khanali bhai Mohammadhussain bhai Hedari</v>
+        <v>Abbas bhai Alihusain bhai Sihjee</v>
       </c>
       <c r="E265" t="str">
-        <v>20414120</v>
+        <v>20435003</v>
       </c>
       <c r="F265" t="str">
         <v>Given</v>
       </c>
       <c r="G265" t="str">
-        <v/>
+        <v>Ajab ben Khand</v>
       </c>
       <c r="H265" t="str">
         <v>21/05/2026</v>
@@ -7274,47 +7274,56 @@
         <v>Thursday</v>
       </c>
       <c r="J265" t="str">
-        <v>11:08:30</v>
+        <v>10:25:43</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>1778659312652_108</v>
+        <v>1778659312652_335</v>
       </c>
       <c r="B266" t="str">
-        <v>109</v>
+        <v>336</v>
       </c>
       <c r="C266" t="str">
-        <v>588</v>
+        <v>1197</v>
       </c>
       <c r="D266" t="str">
-        <v>Bilqis bai Husain bhai Gadi</v>
+        <v>Khanali bhai Mohammadhussain bhai Hedari</v>
       </c>
       <c r="E266" t="str">
-        <v>20318760</v>
+        <v>20414120</v>
       </c>
       <c r="F266" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G266" t="str">
         <v/>
+      </c>
+      <c r="H266" t="str">
+        <v>21/05/2026</v>
+      </c>
+      <c r="I266" t="str">
+        <v>Thursday</v>
+      </c>
+      <c r="J266" t="str">
+        <v>11:08:30</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>1778659312652_326</v>
+        <v>1778659312652_108</v>
       </c>
       <c r="B267" t="str">
-        <v>327</v>
+        <v>109</v>
       </c>
       <c r="C267" t="str">
-        <v>431</v>
+        <v>588</v>
       </c>
       <c r="D267" t="str">
-        <v>Khadija bai Fakhruddin bhai Peeth</v>
+        <v>Bilqis bai Husain bhai Gadi</v>
       </c>
       <c r="E267" t="str">
-        <v>30366840</v>
+        <v>20318760</v>
       </c>
       <c r="F267" t="str">
         <v>Pending</v>
@@ -7325,19 +7334,19 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>1778659312652_327</v>
+        <v>1778659312652_326</v>
       </c>
       <c r="B268" t="str">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C268" t="str">
-        <v>822</v>
+        <v>431</v>
       </c>
       <c r="D268" t="str">
-        <v>Khadija bai Ghulamhusain bhai Dudhwala</v>
+        <v>Khadija bai Fakhruddin bhai Peeth</v>
       </c>
       <c r="E268" t="str">
-        <v>30367535</v>
+        <v>30366840</v>
       </c>
       <c r="F268" t="str">
         <v>Pending</v>
@@ -7348,19 +7357,19 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>1778659312652_328</v>
+        <v>1778659312652_327</v>
       </c>
       <c r="B269" t="str">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C269" t="str">
-        <v>684</v>
+        <v>822</v>
       </c>
       <c r="D269" t="str">
-        <v>Khadija bai Haiderali bhai Maudi wala</v>
+        <v>Khadija bai Ghulamhusain bhai Dudhwala</v>
       </c>
       <c r="E269" t="str">
-        <v>30367251</v>
+        <v>30367535</v>
       </c>
       <c r="F269" t="str">
         <v>Pending</v>
@@ -7371,97 +7380,97 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>1778659312652_102</v>
+        <v>1778659312652_328</v>
       </c>
       <c r="B270" t="str">
-        <v>103</v>
+        <v>329</v>
       </c>
       <c r="C270" t="str">
-        <v>637</v>
+        <v>684</v>
       </c>
       <c r="D270" t="str">
-        <v>Batul bai Mufaddal bhai Jaan</v>
+        <v>Khadija bai Haiderali bhai Maudi wala</v>
       </c>
       <c r="E270" t="str">
-        <v>30367654</v>
+        <v>30367251</v>
       </c>
       <c r="F270" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G270" t="str">
-        <v>mulla jivaji</v>
-      </c>
-      <c r="H270" t="str">
-        <v>22/05/2026</v>
-      </c>
-      <c r="I270" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J270" t="str">
-        <v>11:47:31</v>
+        <v/>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>1778659312652_330</v>
+        <v>1778659312652_102</v>
       </c>
       <c r="B271" t="str">
-        <v>331</v>
+        <v>103</v>
       </c>
       <c r="C271" t="str">
-        <v>1356</v>
+        <v>637</v>
       </c>
       <c r="D271" t="str">
-        <v>Khadija bai Murtaza bhai Ratawala</v>
+        <v>Batul bai Mufaddal bhai Jaan</v>
       </c>
       <c r="E271" t="str">
-        <v>30367899</v>
+        <v>30367654</v>
       </c>
       <c r="F271" t="str">
         <v>Given</v>
       </c>
       <c r="G271" t="str">
-        <v>Fakhruddin kawja</v>
+        <v>mulla jivaji</v>
+      </c>
+      <c r="H271" t="str">
+        <v>22/05/2026</v>
+      </c>
+      <c r="I271" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="J271" t="str">
+        <v>11:47:31</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>1778659312652_331</v>
+        <v>1778659312652_330</v>
       </c>
       <c r="B272" t="str">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C272" t="str">
-        <v>388</v>
+        <v>1356</v>
       </c>
       <c r="D272" t="str">
-        <v>Khadija bai Qutbuddin bhai Tara</v>
+        <v>Khadija bai Murtaza bhai Ratawala</v>
       </c>
       <c r="E272" t="str">
-        <v>30366583</v>
+        <v>30367899</v>
       </c>
       <c r="F272" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G272" t="str">
-        <v/>
+        <v>Fakhruddin kawja</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>1778659312652_332</v>
+        <v>1778659312652_331</v>
       </c>
       <c r="B273" t="str">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C273" t="str">
-        <v>310</v>
+        <v>388</v>
       </c>
       <c r="D273" t="str">
-        <v>Khadija bai Saifuddin bhai Ezzi</v>
+        <v>Khadija bai Qutbuddin bhai Tara</v>
       </c>
       <c r="E273" t="str">
-        <v>30366643</v>
+        <v>30366583</v>
       </c>
       <c r="F273" t="str">
         <v>Pending</v>
@@ -7472,80 +7481,71 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>1778659312652_333</v>
+        <v>1778659312652_332</v>
       </c>
       <c r="B274" t="str">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C274" t="str">
-        <v>1029</v>
+        <v>310</v>
       </c>
       <c r="D274" t="str">
-        <v>Khadija bai Shaikh Mohammed bhai Khumanpur</v>
+        <v>Khadija bai Saifuddin bhai Ezzi</v>
       </c>
       <c r="E274" t="str">
-        <v>30367849</v>
+        <v>30366643</v>
       </c>
       <c r="F274" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G274" t="str">
-        <v>yakut bhai gaba</v>
+        <v/>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>1778659312652_334</v>
+        <v>1778659312652_333</v>
       </c>
       <c r="B275" t="str">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C275" t="str">
-        <v>138</v>
+        <v>1029</v>
       </c>
       <c r="D275" t="str">
-        <v>Khadija bai Tayyeb bhai Gadi</v>
+        <v>Khadija bai Shaikh Mohammed bhai Khumanpur</v>
       </c>
       <c r="E275" t="str">
-        <v>30366336</v>
+        <v>30367849</v>
       </c>
       <c r="F275" t="str">
         <v>Given</v>
       </c>
       <c r="G275" t="str">
-        <v>shkh fakhruddin badi</v>
+        <v>yakut bhai gaba</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>1778659312652_99</v>
+        <v>1778659312652_334</v>
       </c>
       <c r="B276" t="str">
-        <v>100</v>
+        <v>335</v>
       </c>
       <c r="C276" t="str">
-        <v>236</v>
+        <v>138</v>
       </c>
       <c r="D276" t="str">
-        <v>Batul bai Johar bhai Saroda</v>
+        <v>Khadija bai Tayyeb bhai Gadi</v>
       </c>
       <c r="E276" t="str">
-        <v>30488741</v>
+        <v>30366336</v>
       </c>
       <c r="F276" t="str">
         <v>Given</v>
       </c>
       <c r="G276" t="str">
-        <v>Ilyas</v>
-      </c>
-      <c r="H276" t="str">
-        <v>25/05/2026</v>
-      </c>
-      <c r="I276" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="J276" t="str">
-        <v>03:34:44</v>
+        <v>shkh fakhruddin badi</v>
       </c>
     </row>
     <row r="277">
@@ -15601,66 +15601,57 @@
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>1778659312652_30</v>
+        <v>1778659312652_316</v>
       </c>
       <c r="B593" t="str">
-        <v>31</v>
+        <v>317</v>
       </c>
       <c r="C593" t="str">
-        <v>101</v>
+        <v>235</v>
       </c>
       <c r="D593" t="str">
-        <v>Ajab bai Mufaddal bhai Bangali</v>
+        <v>Jumana bai Fakhruddin bhai Tarawala</v>
       </c>
       <c r="E593" t="str">
-        <v>30368206</v>
+        <v>30367675</v>
       </c>
       <c r="F593" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G593" t="str">
-        <v>Insiya ben pachlasa</v>
-      </c>
-      <c r="H593" t="str">
-        <v>23/05/2026</v>
-      </c>
-      <c r="I593" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="J593" t="str">
-        <v>12:14:22</v>
+        <v/>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>1778659312652_316</v>
+        <v>1778659312652_30</v>
       </c>
       <c r="B594" t="str">
-        <v>317</v>
+        <v>31</v>
       </c>
       <c r="C594" t="str">
-        <v>235</v>
+        <v>101</v>
       </c>
       <c r="D594" t="str">
-        <v>Jumana bai Fakhruddin bhai Tarawala</v>
+        <v>Ajab bai Mufaddal bhai Bangali</v>
       </c>
       <c r="E594" t="str">
-        <v>30367675</v>
+        <v>30368206</v>
       </c>
       <c r="F594" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G594" t="str">
-        <v/>
+        <v>Insiya ben pachlasa</v>
       </c>
       <c r="H594" t="str">
-        <v>25/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="I594" t="str">
-        <v>Monday</v>
+        <v>Saturday</v>
       </c>
       <c r="J594" t="str">
-        <v>03:35:08</v>
+        <v>12:14:22</v>
       </c>
     </row>
     <row r="595">

--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -7059,66 +7059,57 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>1778659312652_99</v>
+        <v>1778659312652_100</v>
       </c>
       <c r="B258" t="str">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C258" t="str">
-        <v>236</v>
+        <v>117</v>
       </c>
       <c r="D258" t="str">
-        <v>Batul bai Johar bhai Saroda</v>
+        <v>Batul bai Mohammadhussain bhai Bankoda</v>
       </c>
       <c r="E258" t="str">
-        <v>30488741</v>
+        <v>30360295</v>
       </c>
       <c r="F258" t="str">
         <v>Given</v>
       </c>
       <c r="G258" t="str">
-        <v>Ilyas</v>
+        <v/>
       </c>
       <c r="H258" t="str">
-        <v>25/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="I258" t="str">
-        <v>Monday</v>
+        <v>Friday</v>
       </c>
       <c r="J258" t="str">
-        <v>16:05:11</v>
+        <v>12:19:42</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>1778659312652_100</v>
+        <v>1778659312652_99</v>
       </c>
       <c r="B259" t="str">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C259" t="str">
-        <v>117</v>
+        <v>236</v>
       </c>
       <c r="D259" t="str">
-        <v>Batul bai Mohammadhussain bhai Bankoda</v>
+        <v>Batul bai Johar bhai Saroda</v>
       </c>
       <c r="E259" t="str">
-        <v>30360295</v>
+        <v>30488741</v>
       </c>
       <c r="F259" t="str">
         <v>Given</v>
       </c>
       <c r="G259" t="str">
-        <v/>
-      </c>
-      <c r="H259" t="str">
-        <v>22/05/2026</v>
-      </c>
-      <c r="I259" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J259" t="str">
-        <v>12:19:42</v>
+        <v>Ilyas</v>
       </c>
     </row>
     <row r="260">

--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -15183,97 +15183,106 @@
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>1778659312652_603</v>
+        <v>1778659312652_592</v>
       </c>
       <c r="B576" t="str">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="C576" t="str">
-        <v>323</v>
+        <v>380</v>
       </c>
       <c r="D576" t="str">
-        <v>Shaikh Asgarali bhai Ahmedali bhai Khajoori</v>
+        <v>Shabbirhusain bhai Qurbanhusain bhai Thakerdawala</v>
       </c>
       <c r="E576" t="str">
-        <v>20352038</v>
+        <v>20436086</v>
       </c>
       <c r="F576" t="str">
-        <v>Not Allowed</v>
+        <v>Given</v>
       </c>
       <c r="G576" t="str">
         <v/>
+      </c>
+      <c r="H576" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I576" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J576" t="str">
+        <v>11:07:15</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>1778659312652_592</v>
+        <v>1778659312652_603</v>
       </c>
       <c r="B577" t="str">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="C577" t="str">
-        <v>380</v>
+        <v>323</v>
       </c>
       <c r="D577" t="str">
-        <v>Shabbirhusain bhai Qurbanhusain bhai Thakerdawala</v>
+        <v>Shaikh Asgarali bhai Ahmedali bhai Khajoori</v>
       </c>
       <c r="E577" t="str">
-        <v>20436086</v>
+        <v>20352038</v>
       </c>
       <c r="F577" t="str">
-        <v>Given</v>
+        <v>Not Allowed</v>
       </c>
       <c r="G577" t="str">
         <v/>
-      </c>
-      <c r="H577" t="str">
-        <v>23/05/2026</v>
-      </c>
-      <c r="I577" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="J577" t="str">
-        <v>11:07:15</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>1778659312652_586</v>
+        <v>1778659312652_596</v>
       </c>
       <c r="B578" t="str">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="C578" t="str">
-        <v>1476</v>
+        <v>70</v>
       </c>
       <c r="D578" t="str">
-        <v>Shabbir bhai Taiyebali bhai Sukhsar</v>
+        <v>Shaikh Abbas bhai Mulla Baqir bhai Damriwala</v>
       </c>
       <c r="E578" t="str">
-        <v>20406259</v>
+        <v>20407514</v>
       </c>
       <c r="F578" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G578" t="str">
-        <v/>
+        <v>Hakimuddin bhai popat</v>
+      </c>
+      <c r="H578" t="str">
+        <v>28/05/2026</v>
+      </c>
+      <c r="I578" t="str">
+        <v>Thursday</v>
+      </c>
+      <c r="J578" t="str">
+        <v>11:55:25</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>1778659312652_591</v>
+        <v>1778659312652_586</v>
       </c>
       <c r="B579" t="str">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C579" t="str">
-        <v>54</v>
+        <v>1476</v>
       </c>
       <c r="D579" t="str">
-        <v>Shabbirhusain bhai Qurbanhusain bhai Pachlasa</v>
+        <v>Shabbir bhai Taiyebali bhai Sukhsar</v>
       </c>
       <c r="E579" t="str">
-        <v>20402355</v>
+        <v>20406259</v>
       </c>
       <c r="F579" t="str">
         <v>Pending</v>
@@ -15284,19 +15293,19 @@
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>1778659312652_593</v>
+        <v>1778659312652_591</v>
       </c>
       <c r="B580" t="str">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C580" t="str">
-        <v>472</v>
+        <v>54</v>
       </c>
       <c r="D580" t="str">
-        <v>Shabbirhusain bhai Taherali bhai Munshi</v>
+        <v>Shabbirhusain bhai Qurbanhusain bhai Pachlasa</v>
       </c>
       <c r="E580" t="str">
-        <v>20318697</v>
+        <v>20402355</v>
       </c>
       <c r="F580" t="str">
         <v>Pending</v>
@@ -15307,19 +15316,19 @@
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>1778659312652_594</v>
+        <v>1778659312652_593</v>
       </c>
       <c r="B581" t="str">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C581" t="str">
-        <v>1111</v>
+        <v>472</v>
       </c>
       <c r="D581" t="str">
-        <v>Shaikh Abbas bhai Ali bhai Kika bhai</v>
+        <v>Shabbirhusain bhai Taherali bhai Munshi</v>
       </c>
       <c r="E581" t="str">
-        <v>20387729</v>
+        <v>20318697</v>
       </c>
       <c r="F581" t="str">
         <v>Pending</v>
@@ -15330,19 +15339,19 @@
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>1778659312652_595</v>
+        <v>1778659312652_594</v>
       </c>
       <c r="B582" t="str">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C582" t="str">
-        <v>1260</v>
+        <v>1111</v>
       </c>
       <c r="D582" t="str">
-        <v>Shaikh Abbas bhai Mohammadhussain bhai Jamali</v>
+        <v>Shaikh Abbas bhai Ali bhai Kika bhai</v>
       </c>
       <c r="E582" t="str">
-        <v>20352092</v>
+        <v>20387729</v>
       </c>
       <c r="F582" t="str">
         <v>Pending</v>
@@ -15353,22 +15362,22 @@
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>1778659312652_596</v>
+        <v>1778659312652_595</v>
       </c>
       <c r="B583" t="str">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C583" t="str">
-        <v>70</v>
+        <v>1260</v>
       </c>
       <c r="D583" t="str">
-        <v>Shaikh Abbas bhai Mulla Baqir bhai Damriwala</v>
+        <v>Shaikh Abbas bhai Mohammadhussain bhai Jamali</v>
       </c>
       <c r="E583" t="str">
-        <v>20407514</v>
+        <v>20352092</v>
       </c>
       <c r="F583" t="str">
-        <v>Not Allowed</v>
+        <v>Pending</v>
       </c>
       <c r="G583" t="str">
         <v/>

--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -7091,48 +7091,48 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>1778659312652_99</v>
+        <v>1778659312652_101</v>
       </c>
       <c r="B259" t="str">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C259" t="str">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="D259" t="str">
-        <v>Batul bai Johar bhai Saroda</v>
+        <v>Batul bai Mohammadhussain bhai Patra</v>
       </c>
       <c r="E259" t="str">
-        <v>30488741</v>
+        <v>20318132</v>
       </c>
       <c r="F259" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G259" t="str">
-        <v>Ilyas</v>
+        <v/>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>1778659312652_101</v>
+        <v>1778659312652_99</v>
       </c>
       <c r="B260" t="str">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C260" t="str">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="D260" t="str">
-        <v>Batul bai Mohammadhussain bhai Patra</v>
+        <v>Batul bai Johar bhai Saroda</v>
       </c>
       <c r="E260" t="str">
-        <v>20318132</v>
+        <v>30488741</v>
       </c>
       <c r="F260" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G260" t="str">
-        <v/>
+        <v>Ilyas</v>
       </c>
     </row>
     <row r="261">
@@ -15601,57 +15601,66 @@
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>1778659312652_316</v>
+        <v>1778659312652_30</v>
       </c>
       <c r="B593" t="str">
-        <v>317</v>
+        <v>31</v>
       </c>
       <c r="C593" t="str">
-        <v>235</v>
+        <v>101</v>
       </c>
       <c r="D593" t="str">
-        <v>Jumana bai Fakhruddin bhai Tarawala</v>
+        <v>Ajab bai Mufaddal bhai Bangali</v>
       </c>
       <c r="E593" t="str">
-        <v>30367675</v>
+        <v>30368206</v>
       </c>
       <c r="F593" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G593" t="str">
-        <v/>
+        <v>Insiya ben pachlasa</v>
+      </c>
+      <c r="H593" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="I593" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="J593" t="str">
+        <v>12:14:22</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>1778659312652_30</v>
+        <v>1778659312652_316</v>
       </c>
       <c r="B594" t="str">
-        <v>31</v>
+        <v>317</v>
       </c>
       <c r="C594" t="str">
-        <v>101</v>
+        <v>235</v>
       </c>
       <c r="D594" t="str">
-        <v>Ajab bai Mufaddal bhai Bangali</v>
+        <v>Jumana bai Fakhruddin bhai Tarawala</v>
       </c>
       <c r="E594" t="str">
-        <v>30368206</v>
+        <v>30367675</v>
       </c>
       <c r="F594" t="str">
         <v>Given</v>
       </c>
       <c r="G594" t="str">
-        <v>Insiya ben pachlasa</v>
+        <v>Ilyas</v>
       </c>
       <c r="H594" t="str">
-        <v>23/05/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="I594" t="str">
-        <v>Saturday</v>
+        <v>Thursday</v>
       </c>
       <c r="J594" t="str">
-        <v>12:14:22</v>
+        <v>15:17:53</v>
       </c>
     </row>
     <row r="595">

--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -15648,19 +15648,10 @@
         <v>30367675</v>
       </c>
       <c r="F594" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G594" t="str">
-        <v>Ilyas</v>
-      </c>
-      <c r="H594" t="str">
-        <v>28/05/2026</v>
-      </c>
-      <c r="I594" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="J594" t="str">
-        <v>15:17:53</v>
+        <v/>
       </c>
     </row>
     <row r="595">

--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J781"/>
+  <dimension ref="A1:K781"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,6 +430,9 @@
       <c r="J1" t="str">
         <v>Update_Time</v>
       </c>
+      <c r="K1" t="str">
+        <v>Given_To</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -7129,9 +7132,21 @@
         <v>30488741</v>
       </c>
       <c r="F260" t="str">
-        <v>Given</v>
+        <v>Given to Ilyas</v>
       </c>
       <c r="G260" t="str">
+        <v>Ilyas</v>
+      </c>
+      <c r="H260" t="str">
+        <v>29/05/2026</v>
+      </c>
+      <c r="I260" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="J260" t="str">
+        <v>02:04:49</v>
+      </c>
+      <c r="K260" t="str">
         <v>Ilyas</v>
       </c>
     </row>
@@ -15653,6 +15668,18 @@
       <c r="G594" t="str">
         <v/>
       </c>
+      <c r="H594" t="str">
+        <v>29/05/2026</v>
+      </c>
+      <c r="I594" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="J594" t="str">
+        <v>02:05:22</v>
+      </c>
+      <c r="K594" t="str">
+        <v/>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
@@ -20488,7 +20515,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J781"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K781"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K781"/>
+  <dimension ref="A1:J781"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,9 +430,6 @@
       <c r="J1" t="str">
         <v>Update_Time</v>
       </c>
-      <c r="K1" t="str">
-        <v>Given_To</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -7117,54 +7114,42 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>1778659312652_99</v>
+        <v>1778659312652_103</v>
       </c>
       <c r="B260" t="str">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C260" t="str">
-        <v>236</v>
+        <v>1303</v>
       </c>
       <c r="D260" t="str">
-        <v>Batul bai Johar bhai Saroda</v>
+        <v>Batul bai Qutbuddin bhai Rustam</v>
       </c>
       <c r="E260" t="str">
-        <v>30488741</v>
+        <v>30366656</v>
       </c>
       <c r="F260" t="str">
-        <v>Given to Ilyas</v>
+        <v>Pending</v>
       </c>
       <c r="G260" t="str">
-        <v>Ilyas</v>
-      </c>
-      <c r="H260" t="str">
-        <v>29/05/2026</v>
-      </c>
-      <c r="I260" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J260" t="str">
-        <v>02:04:49</v>
-      </c>
-      <c r="K260" t="str">
-        <v>Ilyas</v>
+        <v/>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>1778659312652_103</v>
+        <v>1778659312652_104</v>
       </c>
       <c r="B261" t="str">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C261" t="str">
-        <v>1303</v>
+        <v>76</v>
       </c>
       <c r="D261" t="str">
-        <v>Batul bai Qutbuddin bhai Rustam</v>
+        <v>Batul bai Saifuddin bhai Doodhbhai</v>
       </c>
       <c r="E261" t="str">
-        <v>30366656</v>
+        <v>30368616</v>
       </c>
       <c r="F261" t="str">
         <v>Pending</v>
@@ -7175,19 +7160,19 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>1778659312652_104</v>
+        <v>1778659312652_105</v>
       </c>
       <c r="B262" t="str">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C262" t="str">
-        <v>76</v>
+        <v>744</v>
       </c>
       <c r="D262" t="str">
-        <v>Batul bai Saifuddin bhai Doodhbhai</v>
+        <v>Batul bai Shaikh Akbarhusain bhai Rampurwala</v>
       </c>
       <c r="E262" t="str">
-        <v>30368616</v>
+        <v>30367359</v>
       </c>
       <c r="F262" t="str">
         <v>Pending</v>
@@ -7198,80 +7183,89 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>1778659312652_105</v>
+        <v>1778659312652_106</v>
       </c>
       <c r="B263" t="str">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C263" t="str">
-        <v>744</v>
+        <v>807</v>
       </c>
       <c r="D263" t="str">
-        <v>Batul bai Shaikh Akbarhusain bhai Rampurwala</v>
+        <v>Batul bai Taiyebali bhai Bankoda</v>
       </c>
       <c r="E263" t="str">
-        <v>30367359</v>
+        <v>30367508</v>
       </c>
       <c r="F263" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G263" t="str">
-        <v/>
+        <v>zainab ben antri</v>
+      </c>
+      <c r="H263" t="str">
+        <v>18/05/2026</v>
+      </c>
+      <c r="I263" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J263" t="str">
+        <v>11:50:34</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>1778659312652_106</v>
+        <v>1778659312652_6</v>
       </c>
       <c r="B264" t="str">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="C264" t="str">
-        <v>807</v>
+        <v>7</v>
       </c>
       <c r="D264" t="str">
-        <v>Batul bai Taiyebali bhai Bankoda</v>
+        <v>Abbas bhai Alihusain bhai Sihjee</v>
       </c>
       <c r="E264" t="str">
-        <v>30367508</v>
+        <v>20435003</v>
       </c>
       <c r="F264" t="str">
         <v>Given</v>
       </c>
       <c r="G264" t="str">
-        <v>zainab ben antri</v>
+        <v>Ajab ben Khand</v>
       </c>
       <c r="H264" t="str">
-        <v>18/05/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="I264" t="str">
-        <v>Monday</v>
+        <v>Thursday</v>
       </c>
       <c r="J264" t="str">
-        <v>11:50:34</v>
+        <v>10:25:43</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>1778659312652_6</v>
+        <v>1778659312652_335</v>
       </c>
       <c r="B265" t="str">
-        <v>7</v>
+        <v>336</v>
       </c>
       <c r="C265" t="str">
-        <v>7</v>
+        <v>1197</v>
       </c>
       <c r="D265" t="str">
-        <v>Abbas bhai Alihusain bhai Sihjee</v>
+        <v>Khanali bhai Mohammadhussain bhai Hedari</v>
       </c>
       <c r="E265" t="str">
-        <v>20435003</v>
+        <v>20414120</v>
       </c>
       <c r="F265" t="str">
         <v>Given</v>
       </c>
       <c r="G265" t="str">
-        <v>Ajab ben Khand</v>
+        <v/>
       </c>
       <c r="H265" t="str">
         <v>21/05/2026</v>
@@ -7280,39 +7274,30 @@
         <v>Thursday</v>
       </c>
       <c r="J265" t="str">
-        <v>10:25:43</v>
+        <v>11:08:30</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>1778659312652_335</v>
+        <v>1778659312652_99</v>
       </c>
       <c r="B266" t="str">
-        <v>336</v>
+        <v>100</v>
       </c>
       <c r="C266" t="str">
-        <v>1197</v>
+        <v>236</v>
       </c>
       <c r="D266" t="str">
-        <v>Khanali bhai Mohammadhussain bhai Hedari</v>
+        <v>Batul bai Johar bhai Saroda</v>
       </c>
       <c r="E266" t="str">
-        <v>20414120</v>
+        <v>30488741</v>
       </c>
       <c r="F266" t="str">
         <v>Given</v>
       </c>
       <c r="G266" t="str">
-        <v/>
-      </c>
-      <c r="H266" t="str">
-        <v>21/05/2026</v>
-      </c>
-      <c r="I266" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="J266" t="str">
-        <v>11:08:30</v>
+        <v>Ilyas</v>
       </c>
     </row>
     <row r="267">
@@ -15668,18 +15653,6 @@
       <c r="G594" t="str">
         <v/>
       </c>
-      <c r="H594" t="str">
-        <v>29/05/2026</v>
-      </c>
-      <c r="I594" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="J594" t="str">
-        <v>02:05:22</v>
-      </c>
-      <c r="K594" t="str">
-        <v/>
-      </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
@@ -20515,7 +20488,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K781"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J781"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/distribution_live_backup.xlsx
+++ b/backend/distribution_live_backup.xlsx
@@ -7784,19 +7784,19 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>1778659312652_10</v>
+        <v>1778659312652_109</v>
       </c>
       <c r="B286" t="str">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="C286" t="str">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="D286" t="str">
-        <v>Abbas bhai Sadiqali bhai Badshah</v>
+        <v>Bilqis bai Mohammadhussain bhai Kamruddinwala</v>
       </c>
       <c r="E286" t="str">
-        <v>20342313</v>
+        <v>20318061</v>
       </c>
       <c r="F286" t="str">
         <v>Pending</v>
@@ -7807,19 +7807,19 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>1778659312652_109</v>
+        <v>1778659312652_110</v>
       </c>
       <c r="B287" t="str">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C287" t="str">
-        <v>111</v>
+        <v>826</v>
       </c>
       <c r="D287" t="str">
-        <v>Bilqis bai Mohammadhussain bhai Kamruddinwala</v>
+        <v>Bilqis bai Qutbuddin bhai Kikabhai</v>
       </c>
       <c r="E287" t="str">
-        <v>20318061</v>
+        <v>30367538</v>
       </c>
       <c r="F287" t="str">
         <v>Pending</v>
@@ -7830,19 +7830,19 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>1778659312652_110</v>
+        <v>1778659312652_111</v>
       </c>
       <c r="B288" t="str">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C288" t="str">
-        <v>826</v>
+        <v/>
       </c>
       <c r="D288" t="str">
-        <v>Bilqis bai Qutbuddin bhai Kikabhai</v>
+        <v>Burhanuddin bhai Kutbuddin bhai Peeth</v>
       </c>
       <c r="E288" t="str">
-        <v>30367538</v>
+        <v>30366845</v>
       </c>
       <c r="F288" t="str">
         <v>Pending</v>
@@ -7853,19 +7853,19 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>1778659312652_111</v>
+        <v>1778659312652_112</v>
       </c>
       <c r="B289" t="str">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C289" t="str">
         <v/>
       </c>
       <c r="D289" t="str">
-        <v>Burhanuddin bhai Kutbuddin bhai Peeth</v>
+        <v>Burhanuddin bhai Saifuddin bhai Tuta</v>
       </c>
       <c r="E289" t="str">
-        <v>30366845</v>
+        <v>30367203</v>
       </c>
       <c r="F289" t="str">
         <v>Pending</v>
@@ -7876,65 +7876,65 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>1778659312652_112</v>
+        <v>1778659312652_113</v>
       </c>
       <c r="B290" t="str">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C290" t="str">
-        <v/>
+        <v>1050</v>
       </c>
       <c r="D290" t="str">
-        <v>Burhanuddin bhai Saifuddin bhai Tuta</v>
+        <v>Dawood bhai Ahmedali bhai Najra</v>
       </c>
       <c r="E290" t="str">
-        <v>30367203</v>
+        <v>20387950</v>
       </c>
       <c r="F290" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G290" t="str">
-        <v/>
+        <v>Taher bhai Abbas bhai Tuta</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>1778659312652_113</v>
+        <v>1778659312652_242</v>
       </c>
       <c r="B291" t="str">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="C291" t="str">
-        <v>1050</v>
+        <v>282</v>
       </c>
       <c r="D291" t="str">
-        <v>Dawood bhai Ahmedali bhai Najra</v>
+        <v>Habib bhai Fakhruddin bhai Fata</v>
       </c>
       <c r="E291" t="str">
-        <v>20387950</v>
+        <v>20438486</v>
       </c>
       <c r="F291" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G291" t="str">
-        <v>Taher bhai Abbas bhai Tuta</v>
+        <v/>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>1778659312652_242</v>
+        <v>1778659312652_243</v>
       </c>
       <c r="B292" t="str">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C292" t="str">
-        <v>282</v>
+        <v>3</v>
       </c>
       <c r="D292" t="str">
-        <v>Habib bhai Fakhruddin bhai Fata</v>
+        <v>Habib bhai Fakhruddin bhai Sagir</v>
       </c>
       <c r="E292" t="str">
-        <v>20438486</v>
+        <v>20352546</v>
       </c>
       <c r="F292" t="str">
         <v>Pending</v>
@@ -7945,74 +7945,74 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>1778659312652_243</v>
+        <v>1778659312652_0</v>
       </c>
       <c r="B293" t="str">
-        <v>244</v>
+        <v>1</v>
       </c>
       <c r="C293" t="str">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D293" t="str">
-        <v>Habib bhai Fakhruddin bhai Sagir</v>
+        <v>Aashiqhusain bhai Fakhruddin bhai Sultiwala</v>
       </c>
       <c r="E293" t="str">
-        <v>20352546</v>
+        <v>30704209</v>
       </c>
       <c r="F293" t="str">
-        <v>Pending</v>
+        <v>Given</v>
       </c>
       <c r="G293" t="str">
-        <v/>
+        <v>Abbas bhai</v>
+      </c>
+      <c r="H293" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="I293" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="J293" t="str">
+        <v>11:09:46</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>1778659312652_0</v>
+        <v>1778659312652_244</v>
       </c>
       <c r="B294" t="str">
-        <v>1</v>
+        <v>245</v>
       </c>
       <c r="C294" t="str">
-        <v>16</v>
+        <v>962</v>
       </c>
       <c r="D294" t="str">
-        <v>Aashiqhusain bhai Fakhruddin bhai Sultiwala</v>
+        <v>Habib bhai Jivaji bhai Pachlasa</v>
       </c>
       <c r="E294" t="str">
-        <v>30704209</v>
+        <v>20318592</v>
       </c>
       <c r="F294" t="str">
-        <v>Given</v>
+        <v>Pending</v>
       </c>
       <c r="G294" t="str">
-        <v>Abbas bhai</v>
-      </c>
-      <c r="H294" t="str">
-        <v>25/05/2026</v>
-      </c>
-      <c r="I294" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="J294" t="str">
-        <v>11:09:46</v>
+        <v/>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>1778659312652_244</v>
+        <v>1778659312652_245</v>
       </c>
       <c r="B295" t="str">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C295" t="str">
-        <v>962</v>
+        <v>421</v>
       </c>
       <c r="D295" t="str">
-        <v>Habib bhai Jivaji bhai Pachlasa</v>
+        <v>Habib bhai Shaikh Fakhruddin bhai Daya</v>
       </c>
       <c r="E295" t="str">
-        <v>20318592</v>
+        <v>20435822</v>
       </c>
       <c r="F295" t="str">
         <v>Pending</v>
@@ -8023,19 +8023,19 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>1778659312652_245</v>
+        <v>1778659312652_247</v>
       </c>
       <c r="B296" t="str">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C296" t="str">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D296" t="str">
-        <v>Habib bhai Shaikh Fakhruddin bhai Daya</v>
+        <v>Haider bhai Akberali bhai Tutawala</v>
       </c>
       <c r="E296" t="str">
-        <v>20435822</v>
+        <v>20318260</v>
       </c>
       <c r="F296" t="str">
         <v>Pending</v>
@@ -8046,19 +8046,19 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>1778659312652_247</v>
+        <v>1778659312652_248</v>
       </c>
       <c r="B297" t="str">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C297" t="str">
-        <v>416</v>
+        <v>634</v>
       </c>
       <c r="D297" t="str">
-        <v>Haider bhai Akberali bhai Tutawala</v>
+        <v>Hajera bai Fakhruddin bhai Vakil</v>
       </c>
       <c r="E297" t="str">
-        <v>20318260</v>
+        <v>20318382</v>
       </c>
       <c r="F297" t="str">
         <v>Pending</v>
@@ -8069,19 +8069,19 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>1778659312652_248</v>
+        <v>1778659312652_249</v>
       </c>
       <c r="B298" t="str">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C298" t="str">
-        <v>634</v>
+        <v>611</v>
       </c>
       <c r="D298" t="str">
-        <v>Hajera bai Fakhruddin bhai Vakil</v>
+        <v>Hakimuddin bhai Abbas bhai Barkat</v>
       </c>
       <c r="E298" t="str">
-        <v>20318382</v>
+        <v>30805002</v>
       </c>
       <c r="F298" t="str">
         <v>Pending</v>
@@ -8092,19 +8092,19 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>1778659312652_249</v>
+        <v>1778659312652_250</v>
       </c>
       <c r="B299" t="str">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C299" t="str">
-        <v>611</v>
+        <v>1179</v>
       </c>
       <c r="D299" t="str">
-        <v>Hakimuddin bhai Abbas bhai Barkat</v>
+        <v>Hakimuddin bhai Abdullah bhai Lodal</v>
       </c>
       <c r="E299" t="str">
-        <v>30805002</v>
+        <v>20352764</v>
       </c>
       <c r="F299" t="str">
         <v>Pending</v>
@@ -8115,19 +8115,19 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>1778659312652_250</v>
+        <v>1778659312652_251</v>
       </c>
       <c r="B300" t="str">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C300" t="str">
-        <v>1179</v>
+        <v>845</v>
       </c>
       <c r="D300" t="str">
-        <v>Hakimuddin bhai Abdullah bhai Lodal</v>
+        <v>Hakimuddin bhai Fakhruddin bhai Bakri</v>
       </c>
       <c r="E300" t="str">
-        <v>20352764</v>
+        <v>20318532</v>
       </c>
       <c r="F300" t="str">
         <v>Pending</v>
@@ -8138,19 +8138,19 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>1778659312652_251</v>
+        <v>1778659312652_252</v>
       </c>
       <c r="B301" t="str">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C301" t="str">
-        <v>845</v>
+        <v>467</v>
       </c>
       <c r="D301" t="str">
-        <v>Hakimuddin bhai Fakhruddin bhai Bakri</v>
+        <v>Hakimuddin bhai Ibrahim bhai Electricwala</v>
       </c>
       <c r="E301" t="str">
-        <v>20318532</v>
+        <v>20318280</v>
       </c>
       <c r="F301" t="str">
         <v>Pending</v>
@@ -8161,19 +8161,19 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>1778659312652_252</v>
+        <v>1778659312652_253</v>
       </c>
       <c r="B302" t="str">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C302" t="str">
-        <v>467</v>
+        <v>1473</v>
       </c>
       <c r="D302" t="str">
-        <v>Hakimuddin bhai Ibrahim bhai Electricwala</v>
+        <v>Hakimuddin bhai Mohammadhussain bhai Hamed (godichand)</v>
       </c>
       <c r="E302" t="str">
-        <v>20318280</v>
+        <v>30360130</v>
       </c>
       <c r="F302" t="str">
         <v>Pending</v>
@@ -8184,19 +8184,19 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>1778659312652_253</v>
+        <v>1778659312652_254</v>
       </c>
       <c r="B303" t="str">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C303" t="str">
-        <v>1473</v>
+        <v>43</v>
       </c>
       <c r="D303" t="str">
-        <v>Hakimuddin bhai Mohammadhussain bhai Hamed (godichand)</v>
+        <v>Hakimuddin bhai Mohammedali bhai Kabri</v>
       </c>
       <c r="E303" t="str">
-        <v>30360130</v>
+        <v>20318046</v>
       </c>
       <c r="F303" t="str">
         <v>Pending</v>
@@ -8207,19 +8207,19 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>1778659312652_254</v>
+        <v>1778659312652_10</v>
       </c>
       <c r="B304" t="str">
-        <v>255</v>
+        <v>11</v>
       </c>
       <c r="C304" t="str">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="D304" t="str">
-        <v>Hakimuddin bhai Mohammedali bhai Kabri</v>
+        <v>Abbas bhai Sadiqali bhai Badshah</v>
       </c>
       <c r="E304" t="str">
-        <v>20318046</v>
+        <v>20342313</v>
       </c>
       <c r="F304" t="str">
         <v>Pending</v>
